--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -34,28 +34,6 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-VIP升级需要的金额</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="F1" authorId="0">
       <text>
         <r>
@@ -210,10 +188,10 @@
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
-    <t>map&lt;int{_}long&gt;{;}</t>
-  </si>
-  <si>
-    <t>map&lt;int{_}int&gt;{;}</t>
+    <t>map&lt;int{_}long&gt;{|}</t>
+  </si>
+  <si>
+    <t>map&lt;int{_}int&gt;{|}</t>
   </si>
   <si>
     <t>viplevel</t>
@@ -267,7 +245,7 @@
     <t>1990000_500000</t>
   </si>
   <si>
-    <t>1_1001;4_4001;5_5001;6_6001</t>
+    <t>1_1001|4_4001|5_5001|6_6001</t>
   </si>
   <si>
     <t>4320_10000</t>
@@ -276,7 +254,7 @@
     <t>4320_50000</t>
   </si>
   <si>
-    <t>1_1002;4_4002;5_5002;6_6002</t>
+    <t>1_1002|4_4002|5_5002|6_6002</t>
   </si>
   <si>
     <t>-1_0</t>
@@ -285,16 +263,16 @@
     <t>1_500</t>
   </si>
   <si>
-    <t>1_1003;4_4003;5_5003;6_6003</t>
-  </si>
-  <si>
-    <t>1_1004;4_4004;5_5004;6_6004</t>
-  </si>
-  <si>
-    <t>1_500;2_30</t>
-  </si>
-  <si>
-    <t>1_1005;4_4005;5_5005;6_6005</t>
+    <t>1_1003|4_4003|5_5003|6_6003</t>
+  </si>
+  <si>
+    <t>1_1004|4_4004|5_5004|6_6004</t>
+  </si>
+  <si>
+    <t>1_500|2_30</t>
+  </si>
+  <si>
+    <t>1_1005|4_4005|5_5005|6_6005</t>
   </si>
 </sst>
 </file>
@@ -460,23 +438,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -818,7 +802,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -842,16 +826,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -860,89 +844,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -971,6 +955,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1">
@@ -1287,7 +1274,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -1339,7 +1326,7 @@
       <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1427,7 +1414,7 @@
       <c r="N3" t="s">
         <v>30</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="10" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1437,7 +1424,7 @@
       <c r="C4" s="4"/>
       <c r="D4" s="3"/>
       <c r="E4" s="4"/>
-      <c r="O4" s="8"/>
+      <c r="O4" s="10"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5">
@@ -1482,7 +1469,7 @@
       <c r="N5" t="s">
         <v>36</v>
       </c>
-      <c r="O5" s="8"/>
+      <c r="O5" s="10"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6">
@@ -1524,7 +1511,7 @@
       <c r="M6" t="s">
         <v>35</v>
       </c>
-      <c r="O6" s="8"/>
+      <c r="O6" s="10"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7">
@@ -1569,7 +1556,7 @@
       <c r="N7" t="s">
         <v>39</v>
       </c>
-      <c r="O7" s="8"/>
+      <c r="O7" s="10"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8">
@@ -1585,7 +1572,7 @@
       <c r="E8">
         <v>19004</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G8">
@@ -1611,7 +1598,7 @@
       <c r="M8" t="s">
         <v>35</v>
       </c>
-      <c r="O8" s="8" t="s">
+      <c r="O8" s="10" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1631,7 +1618,7 @@
       <c r="E9">
         <v>19005</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G9">
@@ -1660,7 +1647,7 @@
       <c r="N9" t="s">
         <v>42</v>
       </c>
-      <c r="O9" s="8"/>
+      <c r="O9" s="10"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10">
@@ -1678,7 +1665,7 @@
       <c r="E10">
         <v>19006</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G10">
@@ -1704,7 +1691,7 @@
       <c r="M10" t="s">
         <v>35</v>
       </c>
-      <c r="O10" s="8"/>
+      <c r="O10" s="10"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11">
@@ -1722,7 +1709,7 @@
       <c r="E11">
         <v>19007</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G11">
@@ -1751,7 +1738,7 @@
       <c r="N11" t="s">
         <v>43</v>
       </c>
-      <c r="O11" s="8" t="s">
+      <c r="O11" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1771,7 +1758,7 @@
       <c r="E12">
         <v>19008</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G12">
@@ -1797,7 +1784,7 @@
       <c r="M12" t="s">
         <v>35</v>
       </c>
-      <c r="O12" s="8"/>
+      <c r="O12" s="10"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13">
@@ -1815,7 +1802,7 @@
       <c r="E13">
         <v>19009</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G13">
@@ -1844,7 +1831,7 @@
       <c r="N13" t="s">
         <v>45</v>
       </c>
-      <c r="O13" s="8"/>
+      <c r="O13" s="10"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14">
@@ -1857,7 +1844,7 @@
       <c r="E14">
         <v>19010</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G14">
@@ -1883,10 +1870,7 @@
       <c r="M14" t="s">
         <v>35</v>
       </c>
-      <c r="O14" s="8"/>
-    </row>
-    <row r="15" spans="4:4">
-      <c r="D15" s="8"/>
+      <c r="O14" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -100,6 +100,28 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+avatar表中类型_avatar表中ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 特权类型_特权参数（万分比）
 1. 摇钱树
 2. 充值返利</t>
@@ -135,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="52">
   <si>
     <t>id</t>
   </si>
@@ -176,6 +198,9 @@
     <t>新解锁装扮</t>
   </si>
   <si>
+    <t>服务器解锁装扮</t>
+  </si>
+  <si>
     <t>特权功能</t>
   </si>
   <si>
@@ -194,6 +219,9 @@
     <t>map&lt;int{_}int&gt;{|}</t>
   </si>
   <si>
+    <t>list&lt;int&gt;{|}</t>
+  </si>
+  <si>
     <t>viplevel</t>
   </si>
   <si>
@@ -230,9 +258,15 @@
     <t>avatarType</t>
   </si>
   <si>
+    <t>serverAvatarType</t>
+  </si>
+  <si>
     <t>privilegedFunctions</t>
   </si>
   <si>
+    <t>client</t>
+  </si>
+  <si>
     <t>4320_1000</t>
   </si>
   <si>
@@ -245,7 +279,7 @@
     <t>1990000_500000</t>
   </si>
   <si>
-    <t>1_1001|4_4001|5_5001|6_6001</t>
+    <t>1|2|3|4|5|6|7|8|9|10|11</t>
   </si>
   <si>
     <t>4320_10000</t>
@@ -254,25 +288,31 @@
     <t>4320_50000</t>
   </si>
   <si>
-    <t>1_1002|4_4002|5_5002|6_6002</t>
-  </si>
-  <si>
     <t>-1_0</t>
   </si>
   <si>
+    <t>3_3001|4_4001|5_5001|6_6001</t>
+  </si>
+  <si>
+    <t>3001|4001|5001|6001</t>
+  </si>
+  <si>
     <t>1_500</t>
   </si>
   <si>
-    <t>1_1003|4_4003|5_5003|6_6003</t>
-  </si>
-  <si>
-    <t>1_1004|4_4004|5_5004|6_6004</t>
+    <t>3_3002|4_4002|5_5002|6_6002</t>
+  </si>
+  <si>
+    <t>3002|4002|5002|6002</t>
   </si>
   <si>
     <t>1_500|2_30</t>
   </si>
   <si>
-    <t>1_1005|4_4005|5_5005|6_6005</t>
+    <t>3_3003|4_4003|5_5003|6_6003</t>
+  </si>
+  <si>
+    <t>3003|4003|5003|6003</t>
   </si>
 </sst>
 </file>
@@ -1274,7 +1314,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -1282,11 +1322,12 @@
     <col min="6" max="6" width="17.375" customWidth="1"/>
     <col min="7" max="8" width="21.25" customWidth="1"/>
     <col min="9" max="13" width="20.375" customWidth="1"/>
-    <col min="14" max="14" width="30.375" customWidth="1"/>
-    <col min="15" max="15" width="20.375" customWidth="1"/>
+    <col min="14" max="14" width="26.6166666666667" customWidth="1"/>
+    <col min="15" max="15" width="21.7666666666667" customWidth="1"/>
+    <col min="16" max="16" width="20.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1326,107 +1367,119 @@
       <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
+      <c r="P1" s="10" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N2" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="O3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:16">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="3"/>
       <c r="E4" s="4"/>
-      <c r="O4" s="10"/>
+      <c r="N4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" s="10"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1441,7 +1494,7 @@
         <v>19001</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G5">
         <v>1000</v>
@@ -1450,10 +1503,10 @@
         <v>10000</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K5" t="str">
         <f>"1990000_"&amp;L5</f>
@@ -1464,14 +1517,15 @@
         <v>10000</v>
       </c>
       <c r="M5" t="s">
-        <v>35</v>
-      </c>
-      <c r="N5" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="N5"/>
+      <c r="O5" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" s="10"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>2</v>
       </c>
@@ -1486,7 +1540,7 @@
         <v>19002</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G6">
         <v>1000</v>
@@ -1495,10 +1549,10 @@
         <v>10000</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K24" si="1">"1990000_"&amp;L6</f>
@@ -1509,11 +1563,12 @@
         <v>20000</v>
       </c>
       <c r="M6" t="s">
-        <v>35</v>
-      </c>
-      <c r="O6" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="N6"/>
+      <c r="P6" s="10"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>3</v>
       </c>
@@ -1528,7 +1583,7 @@
         <v>19003</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G7">
         <v>1000</v>
@@ -1537,10 +1592,10 @@
         <v>10000</v>
       </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="1"/>
@@ -1551,14 +1606,12 @@
         <v>30000</v>
       </c>
       <c r="M7" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7" t="s">
         <v>39</v>
       </c>
-      <c r="O7" s="10"/>
+      <c r="N7"/>
+      <c r="P7" s="10"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>4</v>
       </c>
@@ -1573,7 +1626,7 @@
         <v>19004</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1582,10 +1635,10 @@
         <v>10000</v>
       </c>
       <c r="I8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="1"/>
@@ -1596,13 +1649,19 @@
         <v>40000</v>
       </c>
       <c r="M8" t="s">
-        <v>35</v>
-      </c>
-      <c r="O8" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="N8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O8" t="s">
+        <v>45</v>
+      </c>
+      <c r="P8" s="10" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>5</v>
       </c>
@@ -1619,7 +1678,7 @@
         <v>19005</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1628,10 +1687,10 @@
         <v>10000</v>
       </c>
       <c r="I9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" si="1"/>
@@ -1642,14 +1701,12 @@
         <v>50000</v>
       </c>
       <c r="M9" t="s">
-        <v>35</v>
-      </c>
-      <c r="N9" t="s">
-        <v>42</v>
-      </c>
-      <c r="O9" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="N9"/>
+      <c r="P9" s="10"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>6</v>
       </c>
@@ -1666,7 +1723,7 @@
         <v>19006</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1675,10 +1732,10 @@
         <v>10000</v>
       </c>
       <c r="I10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="1"/>
@@ -1689,11 +1746,12 @@
         <v>60000</v>
       </c>
       <c r="M10" t="s">
-        <v>35</v>
-      </c>
-      <c r="O10" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="N10"/>
+      <c r="P10" s="10"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>7</v>
       </c>
@@ -1710,7 +1768,7 @@
         <v>19007</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1719,10 +1777,10 @@
         <v>10000</v>
       </c>
       <c r="I11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="1"/>
@@ -1733,16 +1791,19 @@
         <v>70000</v>
       </c>
       <c r="M11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N11" t="s">
-        <v>43</v>
-      </c>
-      <c r="O11" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="O11" t="s">
+        <v>48</v>
+      </c>
+      <c r="P11" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>8</v>
       </c>
@@ -1759,7 +1820,7 @@
         <v>19008</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1768,10 +1829,10 @@
         <v>10000</v>
       </c>
       <c r="I12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="1"/>
@@ -1782,11 +1843,12 @@
         <v>80000</v>
       </c>
       <c r="M12" t="s">
-        <v>35</v>
-      </c>
-      <c r="O12" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="N12"/>
+      <c r="P12" s="10"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>9</v>
       </c>
@@ -1803,7 +1865,7 @@
         <v>19009</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1812,10 +1874,10 @@
         <v>10000</v>
       </c>
       <c r="I13" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J13" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="1"/>
@@ -1826,14 +1888,12 @@
         <v>90000</v>
       </c>
       <c r="M13" t="s">
-        <v>35</v>
-      </c>
-      <c r="N13" t="s">
-        <v>45</v>
-      </c>
-      <c r="O13" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="N13"/>
+      <c r="P13" s="10"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>10</v>
       </c>
@@ -1845,7 +1905,7 @@
         <v>19010</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1854,10 +1914,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="1"/>
@@ -1868,9 +1928,15 @@
         <v>100000</v>
       </c>
       <c r="M14" t="s">
-        <v>35</v>
-      </c>
-      <c r="O14" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="N14" t="s">
+        <v>50</v>
+      </c>
+      <c r="O14" t="s">
+        <v>51</v>
+      </c>
+      <c r="P14" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -60,6 +60,28 @@
         </r>
       </text>
     </comment>
+    <comment ref="M1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+avatar表中类型_avatar表中ID</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="N1" authorId="0">
       <text>
         <r>
@@ -83,28 +105,6 @@
       </text>
     </comment>
     <comment ref="O1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-avatar表中类型_avatar表中ID</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="90">
   <si>
     <t>id</t>
   </si>
@@ -267,46 +267,160 @@
     <t>client</t>
   </si>
   <si>
-    <t>4320_1000</t>
+    <t>4320_164800</t>
+  </si>
+  <si>
+    <t>1990000_1400000</t>
+  </si>
+  <si>
+    <t>1990000_20000</t>
+  </si>
+  <si>
+    <t>1990000_600000</t>
+  </si>
+  <si>
+    <t>1990000_880000</t>
+  </si>
+  <si>
+    <t>1|2|3|4|5|6|7|8|9|10|11</t>
+  </si>
+  <si>
+    <t>4320_928500</t>
+  </si>
+  <si>
+    <t>1990000_2800000</t>
+  </si>
+  <si>
+    <t>1990000_40000</t>
+  </si>
+  <si>
+    <t>1990000_1200000</t>
+  </si>
+  <si>
+    <t>1990000_1760000</t>
+  </si>
+  <si>
+    <t>4320_5200000</t>
+  </si>
+  <si>
+    <t>1990000_4200000</t>
+  </si>
+  <si>
+    <t>1990000_60000</t>
+  </si>
+  <si>
+    <t>1990000_1800000</t>
+  </si>
+  <si>
+    <t>1990000_2640000</t>
+  </si>
+  <si>
+    <t>4320_40000000</t>
+  </si>
+  <si>
+    <t>1990000_7000000</t>
+  </si>
+  <si>
+    <t>1990000_100000</t>
+  </si>
+  <si>
+    <t>1990000_3000000</t>
+  </si>
+  <si>
+    <t>1990000_4400000</t>
+  </si>
+  <si>
+    <t>3_3001|4_4001|5_5001|6_6001</t>
+  </si>
+  <si>
+    <t>3001|4001|5001|6001</t>
+  </si>
+  <si>
+    <t>1_500</t>
+  </si>
+  <si>
+    <t>-1_0</t>
+  </si>
+  <si>
+    <t>1990000_21000000</t>
+  </si>
+  <si>
+    <t>1990000_300000</t>
+  </si>
+  <si>
+    <t>1990000_9000000</t>
+  </si>
+  <si>
+    <t>1990000_13200000</t>
+  </si>
+  <si>
+    <t>1990000_28000000</t>
+  </si>
+  <si>
+    <t>1990000_400000</t>
+  </si>
+  <si>
+    <t>1990000_12000000</t>
+  </si>
+  <si>
+    <t>1990000_17600000</t>
+  </si>
+  <si>
+    <t>1990000_35000000</t>
+  </si>
+  <si>
+    <t>1990000_500000</t>
+  </si>
+  <si>
+    <t>1990000_15000000</t>
+  </si>
+  <si>
+    <t>1990000_22000000</t>
+  </si>
+  <si>
+    <t>3_3002|4_4002|5_5002|6_6002</t>
+  </si>
+  <si>
+    <t>3002|4002|5002|6002</t>
+  </si>
+  <si>
+    <t>1_500|2_30</t>
+  </si>
+  <si>
+    <t>1990000_70000000</t>
   </si>
   <si>
     <t>1990000_1000000</t>
   </si>
   <si>
-    <t>1990000_20000</t>
-  </si>
-  <si>
-    <t>1990000_500000</t>
-  </si>
-  <si>
-    <t>1|2|3|4|5|6|7|8|9|10|11</t>
-  </si>
-  <si>
-    <t>4320_10000</t>
-  </si>
-  <si>
-    <t>4320_50000</t>
-  </si>
-  <si>
-    <t>-1_0</t>
-  </si>
-  <si>
-    <t>3_3001|4_4001|5_5001|6_6001</t>
-  </si>
-  <si>
-    <t>3001|4001|5001|6001</t>
-  </si>
-  <si>
-    <t>1_500</t>
-  </si>
-  <si>
-    <t>3_3002|4_4002|5_5002|6_6002</t>
-  </si>
-  <si>
-    <t>3002|4002|5002|6002</t>
-  </si>
-  <si>
-    <t>1_500|2_30</t>
+    <t>1990000_30000000</t>
+  </si>
+  <si>
+    <t>1990000_44000000</t>
+  </si>
+  <si>
+    <t>1990000_140000000</t>
+  </si>
+  <si>
+    <t>1990000_2000000</t>
+  </si>
+  <si>
+    <t>1990000_60000000</t>
+  </si>
+  <si>
+    <t>1990000_88000000</t>
+  </si>
+  <si>
+    <t>1990000_350000000</t>
+  </si>
+  <si>
+    <t>1990000_5000000</t>
+  </si>
+  <si>
+    <t>1990000_150000000</t>
+  </si>
+  <si>
+    <t>1990000_220000000</t>
   </si>
   <si>
     <t>3_3003|4_4003|5_5003|6_6003</t>
@@ -319,11 +433,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -966,7 +1081,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -995,6 +1110,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
@@ -1314,20 +1432,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
+    <col min="1" max="1" width="10.625" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="5" width="14.875" customWidth="1"/>
     <col min="6" max="6" width="17.375" customWidth="1"/>
     <col min="7" max="8" width="21.25" customWidth="1"/>
-    <col min="9" max="13" width="20.375" customWidth="1"/>
-    <col min="14" max="14" width="26.6166666666667" customWidth="1"/>
-    <col min="15" max="15" width="21.7666666666667" customWidth="1"/>
-    <col min="16" max="16" width="20.375" customWidth="1"/>
+    <col min="9" max="12" width="20.375" customWidth="1"/>
+    <col min="13" max="13" width="26.6166666666667" customWidth="1"/>
+    <col min="14" max="14" width="21.7666666666667" customWidth="1"/>
+    <col min="15" max="15" width="20.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1361,20 +1480,20 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="O1" s="11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -1408,20 +1527,20 @@
       <c r="K2" t="s">
         <v>18</v>
       </c>
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
       <c r="M2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="P2" t="s">
+      <c r="O2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1455,31 +1574,31 @@
       <c r="K3" t="s">
         <v>30</v>
       </c>
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
       <c r="M3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N3" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="O3" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:15">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="4"/>
       <c r="D4" s="3"/>
       <c r="E4" s="4"/>
-      <c r="N4" t="s">
+      <c r="M4" t="s">
         <v>35</v>
       </c>
-      <c r="P4" s="10"/>
+      <c r="O4" s="11"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1487,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>10000</v>
+        <v>1648000</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5">
@@ -1508,24 +1627,18 @@
       <c r="J5" t="s">
         <v>38</v>
       </c>
-      <c r="K5" t="str">
-        <f>"1990000_"&amp;L5</f>
-        <v>1990000_10000</v>
-      </c>
-      <c r="L5">
-        <f t="shared" ref="L5:L14" si="0">10000*A5</f>
-        <v>10000</v>
-      </c>
-      <c r="M5" t="s">
+      <c r="K5" t="s">
         <v>39</v>
       </c>
-      <c r="N5"/>
-      <c r="O5" t="s">
+      <c r="L5" t="s">
         <v>40</v>
       </c>
-      <c r="P5" s="10"/>
+      <c r="N5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O5" s="11"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>2</v>
       </c>
@@ -1533,14 +1646,14 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>100000</v>
+        <v>18570000</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6">
         <v>19002</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G6">
         <v>1000</v>
@@ -1549,26 +1662,20 @@
         <v>10000</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J6" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" t="str">
-        <f t="shared" ref="K6:K24" si="1">"1990000_"&amp;L6</f>
-        <v>1990000_20000</v>
-      </c>
-      <c r="L6">
-        <f t="shared" si="0"/>
-        <v>20000</v>
-      </c>
-      <c r="M6" t="s">
-        <v>39</v>
-      </c>
-      <c r="N6"/>
-      <c r="P6" s="10"/>
+        <v>44</v>
+      </c>
+      <c r="K6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" t="s">
+        <v>46</v>
+      </c>
+      <c r="O6" s="11"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>3</v>
       </c>
@@ -1576,14 +1683,14 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>500000</v>
+        <v>156972500</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7">
         <v>19003</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G7">
         <v>1000</v>
@@ -1592,26 +1699,20 @@
         <v>10000</v>
       </c>
       <c r="I7" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="J7" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="1"/>
-        <v>1990000_30000</v>
-      </c>
-      <c r="L7">
-        <f t="shared" si="0"/>
-        <v>30000</v>
-      </c>
-      <c r="M7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N7"/>
-      <c r="P7" s="10"/>
+        <v>49</v>
+      </c>
+      <c r="K7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" t="s">
+        <v>51</v>
+      </c>
+      <c r="O7" s="11"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>4</v>
       </c>
@@ -1619,14 +1720,14 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>1500000</v>
+        <v>1604677500</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8">
         <v>19004</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>43</v>
+      <c r="F8" t="s">
+        <v>52</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1635,33 +1736,28 @@
         <v>10000</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="J8" t="s">
-        <v>38</v>
-      </c>
-      <c r="K8" t="str">
-        <f t="shared" si="1"/>
-        <v>1990000_40000</v>
-      </c>
-      <c r="L8">
-        <f t="shared" si="0"/>
-        <v>40000</v>
+        <v>54</v>
+      </c>
+      <c r="K8" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8" t="s">
+        <v>56</v>
       </c>
       <c r="M8" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="N8" t="s">
-        <v>44</v>
-      </c>
-      <c r="O8" t="s">
-        <v>45</v>
-      </c>
-      <c r="P8" s="10" t="s">
-        <v>46</v>
+        <v>58</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>5</v>
       </c>
@@ -1677,8 +1773,8 @@
       <c r="E9">
         <v>19005</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>43</v>
+      <c r="F9" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1687,26 +1783,20 @@
         <v>10000</v>
       </c>
       <c r="I9" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="J9" t="s">
-        <v>38</v>
-      </c>
-      <c r="K9" t="str">
-        <f t="shared" si="1"/>
-        <v>1990000_50000</v>
-      </c>
-      <c r="L9">
-        <f t="shared" si="0"/>
-        <v>50000</v>
-      </c>
-      <c r="M9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N9"/>
-      <c r="P9" s="10"/>
+        <v>62</v>
+      </c>
+      <c r="K9" t="s">
+        <v>63</v>
+      </c>
+      <c r="L9" t="s">
+        <v>64</v>
+      </c>
+      <c r="O9" s="11"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>6</v>
       </c>
@@ -1722,8 +1812,8 @@
       <c r="E10">
         <v>19006</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>43</v>
+      <c r="F10" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1732,26 +1822,20 @@
         <v>10000</v>
       </c>
       <c r="I10" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="J10" t="s">
-        <v>38</v>
-      </c>
-      <c r="K10" t="str">
-        <f t="shared" si="1"/>
-        <v>1990000_60000</v>
-      </c>
-      <c r="L10">
-        <f t="shared" si="0"/>
-        <v>60000</v>
-      </c>
-      <c r="M10" t="s">
-        <v>39</v>
-      </c>
-      <c r="N10"/>
-      <c r="P10" s="10"/>
+        <v>66</v>
+      </c>
+      <c r="K10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L10" t="s">
+        <v>68</v>
+      </c>
+      <c r="O10" s="11"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>7</v>
       </c>
@@ -1767,8 +1851,8 @@
       <c r="E11">
         <v>19007</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>43</v>
+      <c r="F11" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1777,33 +1861,28 @@
         <v>10000</v>
       </c>
       <c r="I11" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="J11" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" t="str">
-        <f t="shared" si="1"/>
-        <v>1990000_70000</v>
-      </c>
-      <c r="L11">
-        <f t="shared" si="0"/>
-        <v>70000</v>
+        <v>70</v>
+      </c>
+      <c r="K11" t="s">
+        <v>71</v>
+      </c>
+      <c r="L11" t="s">
+        <v>72</v>
       </c>
       <c r="M11" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="N11" t="s">
-        <v>47</v>
-      </c>
-      <c r="O11" t="s">
-        <v>48</v>
-      </c>
-      <c r="P11" s="10" t="s">
-        <v>49</v>
+        <v>74</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>8</v>
       </c>
@@ -1819,8 +1898,8 @@
       <c r="E12">
         <v>19008</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>43</v>
+      <c r="F12" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1829,26 +1908,20 @@
         <v>10000</v>
       </c>
       <c r="I12" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="J12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12" t="str">
-        <f t="shared" si="1"/>
-        <v>1990000_80000</v>
-      </c>
-      <c r="L12">
-        <f t="shared" si="0"/>
-        <v>80000</v>
-      </c>
-      <c r="M12" t="s">
-        <v>39</v>
-      </c>
-      <c r="N12"/>
-      <c r="P12" s="10"/>
+        <v>77</v>
+      </c>
+      <c r="K12" t="s">
+        <v>78</v>
+      </c>
+      <c r="L12" t="s">
+        <v>79</v>
+      </c>
+      <c r="O12" s="11"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>9</v>
       </c>
@@ -1864,8 +1937,8 @@
       <c r="E13">
         <v>19009</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>43</v>
+      <c r="F13" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1874,26 +1947,20 @@
         <v>10000</v>
       </c>
       <c r="I13" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="J13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K13" t="str">
-        <f t="shared" si="1"/>
-        <v>1990000_90000</v>
-      </c>
-      <c r="L13">
-        <f t="shared" si="0"/>
-        <v>90000</v>
-      </c>
-      <c r="M13" t="s">
-        <v>39</v>
-      </c>
-      <c r="N13"/>
-      <c r="P13" s="10"/>
+        <v>81</v>
+      </c>
+      <c r="K13" t="s">
+        <v>82</v>
+      </c>
+      <c r="L13" t="s">
+        <v>83</v>
+      </c>
+      <c r="O13" s="11"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>10</v>
       </c>
@@ -1904,8 +1971,8 @@
       <c r="E14">
         <v>19010</v>
       </c>
-      <c r="F14" s="11" t="s">
-        <v>43</v>
+      <c r="F14" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1914,29 +1981,36 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="J14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K14" t="str">
-        <f t="shared" si="1"/>
-        <v>1990000_100000</v>
-      </c>
-      <c r="L14">
-        <f t="shared" si="0"/>
-        <v>100000</v>
+        <v>85</v>
+      </c>
+      <c r="K14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L14" t="s">
+        <v>87</v>
       </c>
       <c r="M14" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="N14" t="s">
-        <v>50</v>
-      </c>
-      <c r="O14" t="s">
-        <v>51</v>
-      </c>
-      <c r="P14" s="10"/>
+        <v>89</v>
+      </c>
+      <c r="O14" s="11"/>
+    </row>
+    <row r="23" spans="7:7">
+      <c r="G23" s="10"/>
+    </row>
+    <row r="24" spans="7:7">
+      <c r="G24" s="10"/>
+    </row>
+    <row r="25" spans="7:7">
+      <c r="G25" s="10"/>
+    </row>
+    <row r="26" spans="7:7">
+      <c r="G26" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="viplevel" sheetId="1" r:id="rId1"/>
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="89">
   <si>
     <t>id</t>
   </si>
@@ -270,16 +270,16 @@
     <t>4320_164800</t>
   </si>
   <si>
-    <t>1990000_1400000</t>
-  </si>
-  <si>
-    <t>1990000_20000</t>
-  </si>
-  <si>
-    <t>1990000_600000</t>
-  </si>
-  <si>
-    <t>1990000_880000</t>
+    <t>1990000_9800000</t>
+  </si>
+  <si>
+    <t>1990000_140000</t>
+  </si>
+  <si>
+    <t>1990000_4200000</t>
+  </si>
+  <si>
+    <t>1990000_6160000</t>
   </si>
   <si>
     <t>1|2|3|4|5|6|7|8|9|10|11</t>
@@ -288,139 +288,136 @@
     <t>4320_928500</t>
   </si>
   <si>
+    <t>1990000_19600000</t>
+  </si>
+  <si>
+    <t>1990000_280000</t>
+  </si>
+  <si>
+    <t>1990000_8400000</t>
+  </si>
+  <si>
+    <t>1990000_12320000</t>
+  </si>
+  <si>
+    <t>4320_5200000</t>
+  </si>
+  <si>
+    <t>1990000_29400000</t>
+  </si>
+  <si>
+    <t>1990000_420000</t>
+  </si>
+  <si>
+    <t>1990000_12600000</t>
+  </si>
+  <si>
+    <t>1990000_18480000</t>
+  </si>
+  <si>
+    <t>4320_40000000</t>
+  </si>
+  <si>
+    <t>1990000_49000000</t>
+  </si>
+  <si>
+    <t>1990000_700000</t>
+  </si>
+  <si>
+    <t>1990000_21000000</t>
+  </si>
+  <si>
+    <t>1990000_30800000</t>
+  </si>
+  <si>
+    <t>3_3001</t>
+  </si>
+  <si>
+    <t>1_500</t>
+  </si>
+  <si>
+    <t>-1_0</t>
+  </si>
+  <si>
+    <t>1990000_147000000</t>
+  </si>
+  <si>
+    <t>1990000_2100000</t>
+  </si>
+  <si>
+    <t>1990000_63000000</t>
+  </si>
+  <si>
+    <t>1990000_92400000</t>
+  </si>
+  <si>
+    <t>1990000_196000000</t>
+  </si>
+  <si>
     <t>1990000_2800000</t>
   </si>
   <si>
-    <t>1990000_40000</t>
-  </si>
-  <si>
-    <t>1990000_1200000</t>
-  </si>
-  <si>
-    <t>1990000_1760000</t>
-  </si>
-  <si>
-    <t>4320_5200000</t>
-  </si>
-  <si>
-    <t>1990000_4200000</t>
-  </si>
-  <si>
-    <t>1990000_60000</t>
-  </si>
-  <si>
-    <t>1990000_1800000</t>
-  </si>
-  <si>
-    <t>1990000_2640000</t>
-  </si>
-  <si>
-    <t>4320_40000000</t>
+    <t>1990000_84000000</t>
+  </si>
+  <si>
+    <t>1990000_123200000</t>
+  </si>
+  <si>
+    <t>1990000_245000000</t>
+  </si>
+  <si>
+    <t>1990000_3500000</t>
+  </si>
+  <si>
+    <t>1990000_105000000</t>
+  </si>
+  <si>
+    <t>1990000_154000000</t>
+  </si>
+  <si>
+    <t>3_3002|4_4002|5_5002|6_6002</t>
+  </si>
+  <si>
+    <t>3002|4002|5002|6002</t>
+  </si>
+  <si>
+    <t>1_500|2_30</t>
+  </si>
+  <si>
+    <t>1990000_490000000</t>
   </si>
   <si>
     <t>1990000_7000000</t>
   </si>
   <si>
-    <t>1990000_100000</t>
-  </si>
-  <si>
-    <t>1990000_3000000</t>
-  </si>
-  <si>
-    <t>1990000_4400000</t>
-  </si>
-  <si>
-    <t>3_3001|4_4001|5_5001|6_6001</t>
-  </si>
-  <si>
-    <t>3001|4001|5001|6001</t>
-  </si>
-  <si>
-    <t>1_500</t>
-  </si>
-  <si>
-    <t>-1_0</t>
-  </si>
-  <si>
-    <t>1990000_21000000</t>
-  </si>
-  <si>
-    <t>1990000_300000</t>
-  </si>
-  <si>
-    <t>1990000_9000000</t>
-  </si>
-  <si>
-    <t>1990000_13200000</t>
-  </si>
-  <si>
-    <t>1990000_28000000</t>
-  </si>
-  <si>
-    <t>1990000_400000</t>
-  </si>
-  <si>
-    <t>1990000_12000000</t>
-  </si>
-  <si>
-    <t>1990000_17600000</t>
+    <t>1990000_210000000</t>
+  </si>
+  <si>
+    <t>1990000_308000000</t>
+  </si>
+  <si>
+    <t>1990000_980000000</t>
+  </si>
+  <si>
+    <t>1990000_14000000</t>
+  </si>
+  <si>
+    <t>1990000_420000000</t>
+  </si>
+  <si>
+    <t>1990000_616000000</t>
+  </si>
+  <si>
+    <t>1990000_2450000000</t>
   </si>
   <si>
     <t>1990000_35000000</t>
   </si>
   <si>
-    <t>1990000_500000</t>
-  </si>
-  <si>
-    <t>1990000_15000000</t>
-  </si>
-  <si>
-    <t>1990000_22000000</t>
-  </si>
-  <si>
-    <t>3_3002|4_4002|5_5002|6_6002</t>
-  </si>
-  <si>
-    <t>3002|4002|5002|6002</t>
-  </si>
-  <si>
-    <t>1_500|2_30</t>
-  </si>
-  <si>
-    <t>1990000_70000000</t>
-  </si>
-  <si>
-    <t>1990000_1000000</t>
-  </si>
-  <si>
-    <t>1990000_30000000</t>
-  </si>
-  <si>
-    <t>1990000_44000000</t>
-  </si>
-  <si>
-    <t>1990000_140000000</t>
-  </si>
-  <si>
-    <t>1990000_2000000</t>
-  </si>
-  <si>
-    <t>1990000_60000000</t>
-  </si>
-  <si>
-    <t>1990000_88000000</t>
-  </si>
-  <si>
-    <t>1990000_350000000</t>
-  </si>
-  <si>
-    <t>1990000_5000000</t>
-  </si>
-  <si>
-    <t>1990000_150000000</t>
-  </si>
-  <si>
-    <t>1990000_220000000</t>
+    <t>1990000_1050000000</t>
+  </si>
+  <si>
+    <t>1990000_1540000000</t>
   </si>
   <si>
     <t>3_3003|4_4003|5_5003|6_6003</t>
@@ -593,12 +590,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1097,6 +1094,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1113,9 +1113,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1">
@@ -1489,7 +1486,7 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1503,13 +1500,13 @@
       <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
@@ -1533,7 +1530,7 @@
       <c r="M2" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="7" t="s">
         <v>20</v>
       </c>
       <c r="O2" t="s">
@@ -1583,20 +1580,20 @@
       <c r="N3" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="5" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="4"/>
       <c r="D4" s="3"/>
       <c r="E4" s="4"/>
       <c r="M4" t="s">
         <v>35</v>
       </c>
-      <c r="O4" s="11"/>
+      <c r="O4" s="5"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5">
@@ -1608,7 +1605,7 @@
       <c r="C5">
         <v>1648000</v>
       </c>
-      <c r="D5" s="8"/>
+      <c r="D5" s="9"/>
       <c r="E5">
         <v>19001</v>
       </c>
@@ -1636,7 +1633,7 @@
       <c r="N5" t="s">
         <v>41</v>
       </c>
-      <c r="O5" s="11"/>
+      <c r="O5" s="5"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6">
@@ -1648,7 +1645,7 @@
       <c r="C6">
         <v>18570000</v>
       </c>
-      <c r="D6" s="8"/>
+      <c r="D6" s="9"/>
       <c r="E6">
         <v>19002</v>
       </c>
@@ -1673,7 +1670,7 @@
       <c r="L6" t="s">
         <v>46</v>
       </c>
-      <c r="O6" s="11"/>
+      <c r="O6" s="5"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7">
@@ -1685,7 +1682,7 @@
       <c r="C7">
         <v>156972500</v>
       </c>
-      <c r="D7" s="8"/>
+      <c r="D7" s="9"/>
       <c r="E7">
         <v>19003</v>
       </c>
@@ -1710,7 +1707,7 @@
       <c r="L7" t="s">
         <v>51</v>
       </c>
-      <c r="O7" s="11"/>
+      <c r="O7" s="5"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8">
@@ -1722,7 +1719,7 @@
       <c r="C8">
         <v>1604677500</v>
       </c>
-      <c r="D8" s="8"/>
+      <c r="D8" s="9"/>
       <c r="E8">
         <v>19004</v>
       </c>
@@ -1750,11 +1747,11 @@
       <c r="M8" t="s">
         <v>57</v>
       </c>
-      <c r="N8" t="s">
+      <c r="N8">
+        <v>3001</v>
+      </c>
+      <c r="O8" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="O8" s="11" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1767,14 +1764,14 @@
       <c r="C9">
         <v>700000</v>
       </c>
-      <c r="D9" s="8">
-        <v>700000</v>
+      <c r="D9" s="9">
+        <v>100000</v>
       </c>
       <c r="E9">
         <v>19005</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1783,18 +1780,18 @@
         <v>10000</v>
       </c>
       <c r="I9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J9" t="s">
         <v>61</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>62</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>63</v>
       </c>
-      <c r="L9" t="s">
-        <v>64</v>
-      </c>
-      <c r="O9" s="11"/>
+      <c r="O9" s="5"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10">
@@ -1806,14 +1803,14 @@
       <c r="C10">
         <v>1500000</v>
       </c>
-      <c r="D10" s="8">
-        <v>1500000</v>
+      <c r="D10" s="9">
+        <v>210000</v>
       </c>
       <c r="E10">
         <v>19006</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1822,18 +1819,18 @@
         <v>10000</v>
       </c>
       <c r="I10" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" t="s">
         <v>65</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>66</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>67</v>
       </c>
-      <c r="L10" t="s">
-        <v>68</v>
-      </c>
-      <c r="O10" s="11"/>
+      <c r="O10" s="5"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11">
@@ -1845,14 +1842,14 @@
       <c r="C11">
         <v>5000000</v>
       </c>
-      <c r="D11" s="8">
-        <v>5000000</v>
+      <c r="D11" s="9">
+        <v>720000</v>
       </c>
       <c r="E11">
         <v>19007</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1861,25 +1858,25 @@
         <v>10000</v>
       </c>
       <c r="I11" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" t="s">
         <v>69</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>70</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>71</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>72</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>73</v>
       </c>
-      <c r="N11" t="s">
+      <c r="O11" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="O11" s="11" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1892,14 +1889,14 @@
       <c r="C12">
         <v>10000000</v>
       </c>
-      <c r="D12" s="8">
-        <v>10000000</v>
+      <c r="D12" s="9">
+        <v>1430000</v>
       </c>
       <c r="E12">
         <v>19008</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1908,18 +1905,18 @@
         <v>10000</v>
       </c>
       <c r="I12" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" t="s">
         <v>76</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>77</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>78</v>
       </c>
-      <c r="L12" t="s">
-        <v>79</v>
-      </c>
-      <c r="O12" s="11"/>
+      <c r="O12" s="5"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13">
@@ -1931,14 +1928,14 @@
       <c r="C13">
         <v>30000000</v>
       </c>
-      <c r="D13" s="8">
-        <v>30000000</v>
+      <c r="D13" s="9">
+        <v>4280000</v>
       </c>
       <c r="E13">
         <v>19009</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1947,18 +1944,18 @@
         <v>10000</v>
       </c>
       <c r="I13" t="s">
+        <v>79</v>
+      </c>
+      <c r="J13" t="s">
         <v>80</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>81</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>82</v>
       </c>
-      <c r="L13" t="s">
-        <v>83</v>
-      </c>
-      <c r="O13" s="11"/>
+      <c r="O13" s="5"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14">
@@ -1967,12 +1964,12 @@
       <c r="B14">
         <v>9</v>
       </c>
-      <c r="D14" s="8"/>
+      <c r="D14" s="9"/>
       <c r="E14">
         <v>19010</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1981,36 +1978,49 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
+        <v>83</v>
+      </c>
+      <c r="J14" t="s">
         <v>84</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>85</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
         <v>86</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>87</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>88</v>
       </c>
-      <c r="N14" t="s">
-        <v>89</v>
-      </c>
-      <c r="O14" s="11"/>
-    </row>
-    <row r="23" spans="7:7">
-      <c r="G23" s="10"/>
-    </row>
-    <row r="24" spans="7:7">
-      <c r="G24" s="10"/>
-    </row>
-    <row r="25" spans="7:7">
-      <c r="G25" s="10"/>
-    </row>
-    <row r="26" spans="7:7">
-      <c r="G26" s="10"/>
+      <c r="O14" s="5"/>
+    </row>
+    <row r="19" spans="4:7">
+      <c r="D19" s="11"/>
+    </row>
+    <row r="20" spans="4:7">
+      <c r="D20" s="11"/>
+    </row>
+    <row r="21" spans="4:7">
+      <c r="D21" s="11"/>
+    </row>
+    <row r="22" spans="4:7">
+      <c r="D22" s="11"/>
+    </row>
+    <row r="23" spans="4:7">
+      <c r="D23" s="11"/>
+      <c r="G23" s="11"/>
+    </row>
+    <row r="24" spans="4:7">
+      <c r="G24" s="11"/>
+    </row>
+    <row r="25" spans="4:7">
+      <c r="G25" s="11"/>
+    </row>
+    <row r="26" spans="4:7">
+      <c r="G26" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="viplevel" sheetId="1" r:id="rId1"/>
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="94">
   <si>
     <t>id</t>
   </si>
@@ -333,7 +333,7 @@
     <t>3_3001</t>
   </si>
   <si>
-    <t>1_500</t>
+    <t>1_100</t>
   </si>
   <si>
     <t>-1_0</t>
@@ -351,6 +351,9 @@
     <t>1990000_92400000</t>
   </si>
   <si>
+    <t>1_200</t>
+  </si>
+  <si>
     <t>1990000_196000000</t>
   </si>
   <si>
@@ -363,6 +366,9 @@
     <t>1990000_123200000</t>
   </si>
   <si>
+    <t>1_300</t>
+  </si>
+  <si>
     <t>1990000_245000000</t>
   </si>
   <si>
@@ -381,7 +387,7 @@
     <t>3002|4002|5002|6002</t>
   </si>
   <si>
-    <t>1_500|2_30</t>
+    <t>1_400|2_250</t>
   </si>
   <si>
     <t>1990000_490000000</t>
@@ -396,6 +402,9 @@
     <t>1990000_308000000</t>
   </si>
   <si>
+    <t>1_500|2_500</t>
+  </si>
+  <si>
     <t>1990000_980000000</t>
   </si>
   <si>
@@ -408,6 +417,9 @@
     <t>1990000_616000000</t>
   </si>
   <si>
+    <t>1_500|2_750</t>
+  </si>
+  <si>
     <t>1990000_2450000000</t>
   </si>
   <si>
@@ -424,6 +436,9 @@
   </si>
   <si>
     <t>3003|4003|5003|6003</t>
+  </si>
+  <si>
+    <t>1_500|2_1000</t>
   </si>
 </sst>
 </file>
@@ -590,12 +605,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1613,7 +1628,7 @@
         <v>36</v>
       </c>
       <c r="G5">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="H5">
         <v>10000</v>
@@ -1653,7 +1668,7 @@
         <v>42</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="H6">
         <v>10000</v>
@@ -1690,7 +1705,7 @@
         <v>47</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="H7">
         <v>10000</v>
@@ -1762,10 +1777,10 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>700000</v>
+        <v>30000</v>
       </c>
       <c r="D9" s="9">
-        <v>100000</v>
+        <v>30000</v>
       </c>
       <c r="E9">
         <v>19005</v>
@@ -1791,7 +1806,9 @@
       <c r="L9" t="s">
         <v>63</v>
       </c>
-      <c r="O9" s="5"/>
+      <c r="O9" s="5" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10">
@@ -1801,10 +1818,10 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>1500000</v>
+        <v>200000</v>
       </c>
       <c r="D10" s="9">
-        <v>210000</v>
+        <v>200000</v>
       </c>
       <c r="E10">
         <v>19006</v>
@@ -1819,18 +1836,20 @@
         <v>10000</v>
       </c>
       <c r="I10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L10" t="s">
-        <v>67</v>
-      </c>
-      <c r="O10" s="5"/>
+        <v>68</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11">
@@ -1840,10 +1859,10 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="D11" s="9">
-        <v>720000</v>
+        <v>1000000</v>
       </c>
       <c r="E11">
         <v>19007</v>
@@ -1858,25 +1877,25 @@
         <v>10000</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1887,10 +1906,10 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>10000000</v>
+        <v>4200000</v>
       </c>
       <c r="D12" s="9">
-        <v>1430000</v>
+        <v>4200000</v>
       </c>
       <c r="E12">
         <v>19008</v>
@@ -1905,18 +1924,20 @@
         <v>10000</v>
       </c>
       <c r="I12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L12" t="s">
-        <v>78</v>
-      </c>
-      <c r="O12" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13">
@@ -1926,10 +1947,10 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>30000000</v>
+        <v>12800000</v>
       </c>
       <c r="D13" s="9">
-        <v>4280000</v>
+        <v>12800000</v>
       </c>
       <c r="E13">
         <v>19009</v>
@@ -1944,18 +1965,20 @@
         <v>10000</v>
       </c>
       <c r="I13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L13" t="s">
-        <v>82</v>
-      </c>
-      <c r="O13" s="5"/>
+        <v>85</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14">
@@ -1978,24 +2001,26 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="L14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="M14" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="N14" t="s">
-        <v>88</v>
-      </c>
-      <c r="O14" s="5"/>
+        <v>92</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="19" spans="4:7">
       <c r="D19" s="11"/>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="viplevel" sheetId="1" r:id="rId1"/>
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="91">
   <si>
     <t>id</t>
   </si>
@@ -282,9 +282,6 @@
     <t>1990000_6160000</t>
   </si>
   <si>
-    <t>1|2|3|4|5|6|7|8|9|10|11</t>
-  </si>
-  <si>
     <t>4320_928500</t>
   </si>
   <si>
@@ -384,9 +381,6 @@
     <t>3_3002|4_4002|5_5002|6_6002</t>
   </si>
   <si>
-    <t>3002|4002|5002|6002</t>
-  </si>
-  <si>
     <t>1_400|2_250</t>
   </si>
   <si>
@@ -433,9 +427,6 @@
   </si>
   <si>
     <t>3_3003|4_4003|5_5003|6_6003</t>
-  </si>
-  <si>
-    <t>3003|4003|5003|6003</t>
   </si>
   <si>
     <t>1_500|2_1000</t>
@@ -445,12 +436,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -605,12 +597,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1093,7 +1085,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1121,13 +1113,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1">
@@ -1449,7 +1444,8 @@
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="5" width="14.875" customWidth="1"/>
+    <col min="3" max="3" width="27.35" customWidth="1"/>
+    <col min="4" max="5" width="14.875" customWidth="1"/>
     <col min="6" max="6" width="17.375" customWidth="1"/>
     <col min="7" max="8" width="21.25" customWidth="1"/>
     <col min="9" max="12" width="20.375" customWidth="1"/>
@@ -1617,10 +1613,10 @@
       <c r="B5">
         <v>0</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="9">
         <v>1648000</v>
       </c>
-      <c r="D5" s="9"/>
+      <c r="D5" s="10"/>
       <c r="E5">
         <v>19001</v>
       </c>
@@ -1644,9 +1640,6 @@
       </c>
       <c r="L5" t="s">
         <v>40</v>
-      </c>
-      <c r="N5" t="s">
-        <v>41</v>
       </c>
       <c r="O5" s="5"/>
     </row>
@@ -1657,15 +1650,15 @@
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="9">
         <v>18570000</v>
       </c>
-      <c r="D6" s="9"/>
+      <c r="D6" s="10"/>
       <c r="E6">
         <v>19002</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6">
         <v>10000</v>
@@ -1674,16 +1667,16 @@
         <v>10000</v>
       </c>
       <c r="I6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" t="s">
         <v>43</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>44</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>45</v>
-      </c>
-      <c r="L6" t="s">
-        <v>46</v>
       </c>
       <c r="O6" s="5"/>
     </row>
@@ -1694,15 +1687,15 @@
       <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="9">
         <v>156972500</v>
       </c>
-      <c r="D7" s="9"/>
+      <c r="D7" s="10"/>
       <c r="E7">
         <v>19003</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G7">
         <v>10000</v>
@@ -1711,16 +1704,16 @@
         <v>10000</v>
       </c>
       <c r="I7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" t="s">
         <v>48</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>49</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>50</v>
-      </c>
-      <c r="L7" t="s">
-        <v>51</v>
       </c>
       <c r="O7" s="5"/>
     </row>
@@ -1731,42 +1724,39 @@
       <c r="B8">
         <v>3</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="9">
         <v>1604677500</v>
       </c>
-      <c r="D8" s="9"/>
+      <c r="D8" s="10"/>
       <c r="E8">
         <v>19004</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H8">
         <v>10000</v>
       </c>
       <c r="I8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" t="s">
         <v>53</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>54</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>55</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>56</v>
       </c>
-      <c r="M8" t="s">
+      <c r="O8" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="N8">
-        <v>3001</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1776,17 +1766,17 @@
       <c r="B9">
         <v>4</v>
       </c>
-      <c r="C9">
-        <v>30000</v>
-      </c>
-      <c r="D9" s="9">
+      <c r="C9" s="9">
+        <v>60000000000</v>
+      </c>
+      <c r="D9" s="10">
         <v>30000</v>
       </c>
       <c r="E9">
         <v>19005</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>59</v>
+      <c r="F9" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1795,19 +1785,19 @@
         <v>10000</v>
       </c>
       <c r="I9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" t="s">
         <v>60</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>61</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>62</v>
       </c>
-      <c r="L9" t="s">
+      <c r="O9" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1817,17 +1807,17 @@
       <c r="B10">
         <v>5</v>
       </c>
-      <c r="C10">
-        <v>200000</v>
-      </c>
-      <c r="D10" s="9">
+      <c r="C10" s="9">
+        <v>400000000000</v>
+      </c>
+      <c r="D10" s="10">
         <v>200000</v>
       </c>
       <c r="E10">
         <v>19006</v>
       </c>
-      <c r="F10" s="12" t="s">
-        <v>59</v>
+      <c r="F10" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1836,19 +1826,19 @@
         <v>10000</v>
       </c>
       <c r="I10" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" t="s">
         <v>65</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>66</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>67</v>
       </c>
-      <c r="L10" t="s">
+      <c r="O10" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1858,17 +1848,17 @@
       <c r="B11">
         <v>6</v>
       </c>
-      <c r="C11">
-        <v>1000000</v>
-      </c>
-      <c r="D11" s="9">
+      <c r="C11" s="9">
+        <v>2000000000000</v>
+      </c>
+      <c r="D11" s="10">
         <v>1000000</v>
       </c>
       <c r="E11">
         <v>19007</v>
       </c>
-      <c r="F11" s="12" t="s">
-        <v>59</v>
+      <c r="F11" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1877,25 +1867,22 @@
         <v>10000</v>
       </c>
       <c r="I11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J11" t="s">
         <v>70</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>71</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>72</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>73</v>
       </c>
-      <c r="M11" t="s">
+      <c r="O11" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="N11" t="s">
-        <v>75</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1905,17 +1892,17 @@
       <c r="B12">
         <v>7</v>
       </c>
-      <c r="C12">
-        <v>4200000</v>
-      </c>
-      <c r="D12" s="9">
+      <c r="C12" s="9">
+        <v>8400000000000</v>
+      </c>
+      <c r="D12" s="10">
         <v>4200000</v>
       </c>
       <c r="E12">
         <v>19008</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>59</v>
+      <c r="F12" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1924,19 +1911,19 @@
         <v>10000</v>
       </c>
       <c r="I12" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K12" t="s">
         <v>77</v>
       </c>
-      <c r="J12" t="s">
+      <c r="L12" t="s">
         <v>78</v>
       </c>
-      <c r="K12" t="s">
+      <c r="O12" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="L12" t="s">
-        <v>80</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1946,17 +1933,17 @@
       <c r="B13">
         <v>8</v>
       </c>
-      <c r="C13">
-        <v>12800000</v>
-      </c>
-      <c r="D13" s="9">
+      <c r="C13" s="9">
+        <v>25600000000000</v>
+      </c>
+      <c r="D13" s="10">
         <v>12800000</v>
       </c>
       <c r="E13">
         <v>19009</v>
       </c>
-      <c r="F13" s="12" t="s">
-        <v>59</v>
+      <c r="F13" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1965,19 +1952,19 @@
         <v>10000</v>
       </c>
       <c r="I13" t="s">
+        <v>80</v>
+      </c>
+      <c r="J13" t="s">
+        <v>81</v>
+      </c>
+      <c r="K13" t="s">
         <v>82</v>
       </c>
-      <c r="J13" t="s">
+      <c r="L13" t="s">
         <v>83</v>
       </c>
-      <c r="K13" t="s">
+      <c r="O13" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="L13" t="s">
-        <v>85</v>
-      </c>
-      <c r="O13" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -1987,12 +1974,12 @@
       <c r="B14">
         <v>9</v>
       </c>
-      <c r="D14" s="9"/>
+      <c r="D14" s="10"/>
       <c r="E14">
         <v>19010</v>
       </c>
-      <c r="F14" s="12" t="s">
-        <v>59</v>
+      <c r="F14" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2001,51 +1988,59 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
+        <v>85</v>
+      </c>
+      <c r="J14" t="s">
+        <v>86</v>
+      </c>
+      <c r="K14" t="s">
         <v>87</v>
       </c>
-      <c r="J14" t="s">
+      <c r="L14" t="s">
         <v>88</v>
       </c>
-      <c r="K14" t="s">
+      <c r="M14" t="s">
         <v>89</v>
       </c>
-      <c r="L14" t="s">
+      <c r="O14" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="M14" t="s">
-        <v>91</v>
-      </c>
-      <c r="N14" t="s">
-        <v>92</v>
-      </c>
-      <c r="O14" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="4:7">
-      <c r="D19" s="11"/>
-    </row>
-    <row r="20" spans="4:7">
-      <c r="D20" s="11"/>
-    </row>
-    <row r="21" spans="4:7">
-      <c r="D21" s="11"/>
-    </row>
-    <row r="22" spans="4:7">
-      <c r="D22" s="11"/>
-    </row>
-    <row r="23" spans="4:7">
-      <c r="D23" s="11"/>
-      <c r="G23" s="11"/>
-    </row>
-    <row r="24" spans="4:7">
-      <c r="G24" s="11"/>
-    </row>
-    <row r="25" spans="4:7">
-      <c r="G25" s="11"/>
-    </row>
-    <row r="26" spans="4:7">
-      <c r="G26" s="11"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="C16" s="12"/>
+    </row>
+    <row r="17" spans="3:7">
+      <c r="C17" s="12"/>
+    </row>
+    <row r="18" spans="3:7">
+      <c r="C18" s="12"/>
+    </row>
+    <row r="19" spans="3:7">
+      <c r="C19" s="12"/>
+      <c r="D19" s="9"/>
+    </row>
+    <row r="20" spans="3:7">
+      <c r="C20" s="12"/>
+      <c r="D20" s="9"/>
+    </row>
+    <row r="21" spans="3:7">
+      <c r="D21" s="9"/>
+    </row>
+    <row r="22" spans="3:7">
+      <c r="D22" s="9"/>
+    </row>
+    <row r="23" spans="3:7">
+      <c r="D23" s="9"/>
+      <c r="G23" s="9"/>
+    </row>
+    <row r="24" spans="3:7">
+      <c r="G24" s="9"/>
+    </row>
+    <row r="25" spans="3:7">
+      <c r="G25" s="9"/>
+    </row>
+    <row r="26" spans="3:7">
+      <c r="G26" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="91">
   <si>
     <t>id</t>
   </si>
@@ -282,9 +282,6 @@
     <t>1990000_6160000</t>
   </si>
   <si>
-    <t>1|2|3|4|5|6|7|8|9|10|11</t>
-  </si>
-  <si>
     <t>4320_928500</t>
   </si>
   <si>
@@ -384,9 +381,6 @@
     <t>3_3002|4_4002|5_5002|6_6002</t>
   </si>
   <si>
-    <t>3002|4002|5002|6002</t>
-  </si>
-  <si>
     <t>1_400|2_250</t>
   </si>
   <si>
@@ -433,9 +427,6 @@
   </si>
   <si>
     <t>3_3003|4_4003|5_5003|6_6003</t>
-  </si>
-  <si>
-    <t>3003|4003|5003|6003</t>
   </si>
   <si>
     <t>1_500|2_1000</t>
@@ -1645,9 +1636,6 @@
       <c r="L5" t="s">
         <v>40</v>
       </c>
-      <c r="N5" t="s">
-        <v>41</v>
-      </c>
       <c r="O5" s="5"/>
     </row>
     <row r="6" spans="1:15">
@@ -1665,7 +1653,7 @@
         <v>19002</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6">
         <v>10000</v>
@@ -1674,16 +1662,16 @@
         <v>10000</v>
       </c>
       <c r="I6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" t="s">
         <v>43</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>44</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>45</v>
-      </c>
-      <c r="L6" t="s">
-        <v>46</v>
       </c>
       <c r="O6" s="5"/>
     </row>
@@ -1702,7 +1690,7 @@
         <v>19003</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G7">
         <v>10000</v>
@@ -1711,16 +1699,16 @@
         <v>10000</v>
       </c>
       <c r="I7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" t="s">
         <v>48</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>49</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>50</v>
-      </c>
-      <c r="L7" t="s">
-        <v>51</v>
       </c>
       <c r="O7" s="5"/>
     </row>
@@ -1739,7 +1727,7 @@
         <v>19004</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1748,25 +1736,23 @@
         <v>10000</v>
       </c>
       <c r="I8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" t="s">
         <v>53</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>54</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>55</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>56</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8"/>
+      <c r="O8" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="N8">
-        <v>3001</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1786,7 +1772,7 @@
         <v>19005</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1795,19 +1781,19 @@
         <v>10000</v>
       </c>
       <c r="I9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" t="s">
         <v>60</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>61</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>62</v>
       </c>
-      <c r="L9" t="s">
+      <c r="O9" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1827,7 +1813,7 @@
         <v>19006</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1836,19 +1822,19 @@
         <v>10000</v>
       </c>
       <c r="I10" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" t="s">
         <v>65</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>66</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>67</v>
       </c>
-      <c r="L10" t="s">
+      <c r="O10" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1868,7 +1854,7 @@
         <v>19007</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1877,25 +1863,23 @@
         <v>10000</v>
       </c>
       <c r="I11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J11" t="s">
         <v>70</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>71</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>72</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>73</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11"/>
+      <c r="O11" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="N11" t="s">
-        <v>75</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1915,7 +1899,7 @@
         <v>19008</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1924,19 +1908,19 @@
         <v>10000</v>
       </c>
       <c r="I12" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K12" t="s">
         <v>77</v>
       </c>
-      <c r="J12" t="s">
+      <c r="L12" t="s">
         <v>78</v>
       </c>
-      <c r="K12" t="s">
+      <c r="O12" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="L12" t="s">
-        <v>80</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1956,7 +1940,7 @@
         <v>19009</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1965,19 +1949,19 @@
         <v>10000</v>
       </c>
       <c r="I13" t="s">
+        <v>80</v>
+      </c>
+      <c r="J13" t="s">
+        <v>81</v>
+      </c>
+      <c r="K13" t="s">
         <v>82</v>
       </c>
-      <c r="J13" t="s">
+      <c r="L13" t="s">
         <v>83</v>
       </c>
-      <c r="K13" t="s">
+      <c r="O13" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="L13" t="s">
-        <v>85</v>
-      </c>
-      <c r="O13" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -1992,7 +1976,7 @@
         <v>19010</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2001,25 +1985,23 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
+        <v>85</v>
+      </c>
+      <c r="J14" t="s">
+        <v>86</v>
+      </c>
+      <c r="K14" t="s">
         <v>87</v>
       </c>
-      <c r="J14" t="s">
+      <c r="L14" t="s">
         <v>88</v>
       </c>
-      <c r="K14" t="s">
+      <c r="M14" t="s">
         <v>89</v>
       </c>
-      <c r="L14" t="s">
+      <c r="N14"/>
+      <c r="O14" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="M14" t="s">
-        <v>91</v>
-      </c>
-      <c r="N14" t="s">
-        <v>92</v>
-      </c>
-      <c r="O14" s="5" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="19" spans="4:7">

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="viplevel" sheetId="1" r:id="rId1"/>
@@ -436,12 +436,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -596,12 +597,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1084,7 +1085,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1112,13 +1113,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1">
@@ -1440,7 +1444,8 @@
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="5" width="14.875" customWidth="1"/>
+    <col min="3" max="3" width="27.35" customWidth="1"/>
+    <col min="4" max="5" width="14.875" customWidth="1"/>
     <col min="6" max="6" width="17.375" customWidth="1"/>
     <col min="7" max="8" width="21.25" customWidth="1"/>
     <col min="9" max="12" width="20.375" customWidth="1"/>
@@ -1608,10 +1613,10 @@
       <c r="B5">
         <v>0</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="9">
         <v>1648000</v>
       </c>
-      <c r="D5" s="9"/>
+      <c r="D5" s="10"/>
       <c r="E5">
         <v>19001</v>
       </c>
@@ -1645,10 +1650,10 @@
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="9">
         <v>18570000</v>
       </c>
-      <c r="D6" s="9"/>
+      <c r="D6" s="10"/>
       <c r="E6">
         <v>19002</v>
       </c>
@@ -1682,10 +1687,10 @@
       <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="9">
         <v>156972500</v>
       </c>
-      <c r="D7" s="9"/>
+      <c r="D7" s="10"/>
       <c r="E7">
         <v>19003</v>
       </c>
@@ -1719,10 +1724,10 @@
       <c r="B8">
         <v>3</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="9">
         <v>1604677500</v>
       </c>
-      <c r="D8" s="9"/>
+      <c r="D8" s="10"/>
       <c r="E8">
         <v>19004</v>
       </c>
@@ -1730,7 +1735,7 @@
         <v>51</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H8">
         <v>10000</v>
@@ -1750,7 +1755,6 @@
       <c r="M8" t="s">
         <v>56</v>
       </c>
-      <c r="N8"/>
       <c r="O8" s="5" t="s">
         <v>57</v>
       </c>
@@ -1762,16 +1766,16 @@
       <c r="B9">
         <v>4</v>
       </c>
-      <c r="C9">
-        <v>30000</v>
-      </c>
-      <c r="D9" s="9">
+      <c r="C9" s="9">
+        <v>60000000000</v>
+      </c>
+      <c r="D9" s="10">
         <v>30000</v>
       </c>
       <c r="E9">
         <v>19005</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="13" t="s">
         <v>58</v>
       </c>
       <c r="G9">
@@ -1803,16 +1807,16 @@
       <c r="B10">
         <v>5</v>
       </c>
-      <c r="C10">
-        <v>200000</v>
-      </c>
-      <c r="D10" s="9">
+      <c r="C10" s="9">
+        <v>400000000000</v>
+      </c>
+      <c r="D10" s="10">
         <v>200000</v>
       </c>
       <c r="E10">
         <v>19006</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="13" t="s">
         <v>58</v>
       </c>
       <c r="G10">
@@ -1844,16 +1848,16 @@
       <c r="B11">
         <v>6</v>
       </c>
-      <c r="C11">
-        <v>1000000</v>
-      </c>
-      <c r="D11" s="9">
+      <c r="C11" s="9">
+        <v>2000000000000</v>
+      </c>
+      <c r="D11" s="10">
         <v>1000000</v>
       </c>
       <c r="E11">
         <v>19007</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="13" t="s">
         <v>58</v>
       </c>
       <c r="G11">
@@ -1877,7 +1881,6 @@
       <c r="M11" t="s">
         <v>73</v>
       </c>
-      <c r="N11"/>
       <c r="O11" s="5" t="s">
         <v>74</v>
       </c>
@@ -1889,16 +1892,16 @@
       <c r="B12">
         <v>7</v>
       </c>
-      <c r="C12">
-        <v>4200000</v>
-      </c>
-      <c r="D12" s="9">
+      <c r="C12" s="9">
+        <v>8400000000000</v>
+      </c>
+      <c r="D12" s="10">
         <v>4200000</v>
       </c>
       <c r="E12">
         <v>19008</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="13" t="s">
         <v>58</v>
       </c>
       <c r="G12">
@@ -1930,16 +1933,16 @@
       <c r="B13">
         <v>8</v>
       </c>
-      <c r="C13">
-        <v>12800000</v>
-      </c>
-      <c r="D13" s="9">
+      <c r="C13" s="9">
+        <v>25600000000000</v>
+      </c>
+      <c r="D13" s="10">
         <v>12800000</v>
       </c>
       <c r="E13">
         <v>19009</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="13" t="s">
         <v>58</v>
       </c>
       <c r="G13">
@@ -1971,11 +1974,11 @@
       <c r="B14">
         <v>9</v>
       </c>
-      <c r="D14" s="9"/>
+      <c r="D14" s="10"/>
       <c r="E14">
         <v>19010</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="13" t="s">
         <v>58</v>
       </c>
       <c r="G14">
@@ -1999,35 +2002,45 @@
       <c r="M14" t="s">
         <v>89</v>
       </c>
-      <c r="N14"/>
       <c r="O14" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="4:7">
-      <c r="D19" s="11"/>
-    </row>
-    <row r="20" spans="4:7">
-      <c r="D20" s="11"/>
-    </row>
-    <row r="21" spans="4:7">
-      <c r="D21" s="11"/>
-    </row>
-    <row r="22" spans="4:7">
-      <c r="D22" s="11"/>
-    </row>
-    <row r="23" spans="4:7">
-      <c r="D23" s="11"/>
-      <c r="G23" s="11"/>
-    </row>
-    <row r="24" spans="4:7">
-      <c r="G24" s="11"/>
-    </row>
-    <row r="25" spans="4:7">
-      <c r="G25" s="11"/>
-    </row>
-    <row r="26" spans="4:7">
-      <c r="G26" s="11"/>
+    <row r="16" spans="1:15">
+      <c r="C16" s="12"/>
+    </row>
+    <row r="17" spans="3:7">
+      <c r="C17" s="12"/>
+    </row>
+    <row r="18" spans="3:7">
+      <c r="C18" s="12"/>
+    </row>
+    <row r="19" spans="3:7">
+      <c r="C19" s="12"/>
+      <c r="D19" s="9"/>
+    </row>
+    <row r="20" spans="3:7">
+      <c r="C20" s="12"/>
+      <c r="D20" s="9"/>
+    </row>
+    <row r="21" spans="3:7">
+      <c r="D21" s="9"/>
+    </row>
+    <row r="22" spans="3:7">
+      <c r="D22" s="9"/>
+    </row>
+    <row r="23" spans="3:7">
+      <c r="D23" s="9"/>
+      <c r="G23" s="9"/>
+    </row>
+    <row r="24" spans="3:7">
+      <c r="G24" s="9"/>
+    </row>
+    <row r="25" spans="3:7">
+      <c r="G25" s="9"/>
+    </row>
+    <row r="26" spans="3:7">
+      <c r="G26" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="viplevel" sheetId="1" r:id="rId1"/>
@@ -78,7 +78,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-avatar表中类型_avatar表中ID</t>
+道具ID_道具数量</t>
         </r>
       </text>
     </comment>
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="93">
   <si>
     <t>id</t>
   </si>
@@ -282,6 +282,9 @@
     <t>1990000_6160000</t>
   </si>
   <si>
+    <t>1022502_1</t>
+  </si>
+  <si>
     <t>4320_928500</t>
   </si>
   <si>
@@ -327,7 +330,7 @@
     <t>1990000_30800000</t>
   </si>
   <si>
-    <t>3_3001</t>
+    <t>1031600_1</t>
   </si>
   <si>
     <t>1_100</t>
@@ -348,6 +351,9 @@
     <t>1990000_92400000</t>
   </si>
   <si>
+    <t>1022502_1|1022501_1</t>
+  </si>
+  <si>
     <t>1_200</t>
   </si>
   <si>
@@ -378,7 +384,7 @@
     <t>1990000_154000000</t>
   </si>
   <si>
-    <t>3_3002|4_4002|5_5002|6_6002</t>
+    <t>1031601_1|1031801_1|1032001_1|1032201_1</t>
   </si>
   <si>
     <t>1_400|2_250</t>
@@ -426,7 +432,7 @@
     <t>1990000_1540000000</t>
   </si>
   <si>
-    <t>3_3003|4_4003|5_5003|6_6003</t>
+    <t>1031602_1|1031802_1|1032002_1|1032202_1</t>
   </si>
   <si>
     <t>1_500|2_1000</t>
@@ -444,13 +450,19 @@
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -597,12 +609,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -955,177 +967,192 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1440,607 +1467,629 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="10.625" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="27.35" customWidth="1"/>
-    <col min="4" max="5" width="14.875" customWidth="1"/>
-    <col min="6" max="6" width="17.375" customWidth="1"/>
-    <col min="7" max="8" width="21.25" customWidth="1"/>
-    <col min="9" max="12" width="20.375" customWidth="1"/>
-    <col min="13" max="13" width="26.6166666666667" customWidth="1"/>
-    <col min="14" max="14" width="21.7666666666667" customWidth="1"/>
-    <col min="15" max="15" width="20.375" customWidth="1"/>
+    <col min="1" max="1" width="10.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.35" style="1" customWidth="1"/>
+    <col min="4" max="5" width="14.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.375" style="1" customWidth="1"/>
+    <col min="7" max="8" width="21.25" style="1" customWidth="1"/>
+    <col min="9" max="12" width="20.375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="26.6166666666667" style="1" customWidth="1"/>
+    <col min="14" max="14" width="21.7666666666667" style="1" customWidth="1"/>
+    <col min="15" max="15" width="20.375" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
-      <c r="M4" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="11"/>
+      <c r="M4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O4" s="5"/>
+      <c r="O4" s="13"/>
     </row>
     <row r="5" spans="1:15">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>0</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="14">
         <v>1648000</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5">
+      <c r="D5" s="15"/>
+      <c r="E5" s="1">
         <v>19001</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>10000</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>10000</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="5"/>
+      <c r="M5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="O5" s="13"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="14">
         <v>18570000</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6">
+      <c r="D6" s="15"/>
+      <c r="E6" s="1">
         <v>19002</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="1">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G6">
+      <c r="O6" s="13"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="1">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7" s="14">
+        <v>156972500</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="1">
+        <v>19003</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="1">
         <v>10000</v>
       </c>
-      <c r="H6">
+      <c r="H7" s="1">
         <v>10000</v>
       </c>
-      <c r="I6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K6" t="s">
-        <v>44</v>
-      </c>
-      <c r="L6" t="s">
-        <v>45</v>
-      </c>
-      <c r="O6" s="5"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7">
+      <c r="I7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="O7" s="13"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1">
         <v>3</v>
       </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7" s="9">
-        <v>156972500</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7">
-        <v>19003</v>
-      </c>
-      <c r="F7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7">
+      <c r="C8" s="14">
+        <v>1604677500</v>
+      </c>
+      <c r="D8" s="15"/>
+      <c r="E8" s="1">
+        <v>19004</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="1">
         <v>10000</v>
       </c>
-      <c r="H7">
+      <c r="H8" s="1">
         <v>10000</v>
       </c>
-      <c r="I7" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" t="s">
-        <v>48</v>
-      </c>
-      <c r="K7" t="s">
-        <v>49</v>
-      </c>
-      <c r="L7" t="s">
-        <v>50</v>
-      </c>
-      <c r="O7" s="5"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8">
+      <c r="I8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="1">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1">
         <v>4</v>
       </c>
-      <c r="B8">
-        <v>3</v>
-      </c>
-      <c r="C8" s="9">
-        <v>1604677500</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8">
-        <v>19004</v>
-      </c>
-      <c r="F8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8">
+      <c r="C9" s="14">
+        <v>60000000000</v>
+      </c>
+      <c r="D9" s="15">
+        <v>30000</v>
+      </c>
+      <c r="E9" s="1">
+        <v>19005</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
         <v>10000</v>
       </c>
-      <c r="H8">
+      <c r="I9" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="1">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1">
+        <v>5</v>
+      </c>
+      <c r="C10" s="14">
+        <v>400000000000</v>
+      </c>
+      <c r="D10" s="15">
+        <v>200000</v>
+      </c>
+      <c r="E10" s="1">
+        <v>19006</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
         <v>10000</v>
       </c>
-      <c r="I8" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" t="s">
-        <v>53</v>
-      </c>
-      <c r="K8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L8" t="s">
-        <v>55</v>
-      </c>
-      <c r="M8" t="s">
-        <v>56</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9">
-        <v>5</v>
-      </c>
-      <c r="B9">
-        <v>4</v>
-      </c>
-      <c r="C9" s="9">
-        <v>60000000000</v>
-      </c>
-      <c r="D9" s="10">
-        <v>30000</v>
-      </c>
-      <c r="E9">
-        <v>19005</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9">
+      <c r="I10" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="1">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1">
+        <v>6</v>
+      </c>
+      <c r="C11" s="14">
+        <v>2000000000000</v>
+      </c>
+      <c r="D11" s="15">
+        <v>1000000</v>
+      </c>
+      <c r="E11" s="1">
+        <v>19007</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="1">
         <v>0</v>
       </c>
-      <c r="H9">
+      <c r="H11" s="1">
         <v>10000</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I11" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="1">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1">
+        <v>7</v>
+      </c>
+      <c r="C12" s="14">
+        <v>8400000000000</v>
+      </c>
+      <c r="D12" s="15">
+        <v>4200000</v>
+      </c>
+      <c r="E12" s="1">
+        <v>19008</v>
+      </c>
+      <c r="F12" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="J9" t="s">
-        <v>60</v>
-      </c>
-      <c r="K9" t="s">
-        <v>61</v>
-      </c>
-      <c r="L9" t="s">
-        <v>62</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10">
-        <v>6</v>
-      </c>
-      <c r="B10">
-        <v>5</v>
-      </c>
-      <c r="C10" s="9">
-        <v>400000000000</v>
-      </c>
-      <c r="D10" s="10">
-        <v>200000</v>
-      </c>
-      <c r="E10">
-        <v>19006</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10">
+      <c r="G12" s="1">
         <v>0</v>
       </c>
-      <c r="H10">
+      <c r="H12" s="1">
         <v>10000</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I12" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="M12" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J10" t="s">
-        <v>65</v>
-      </c>
-      <c r="K10" t="s">
-        <v>66</v>
-      </c>
-      <c r="L10" t="s">
-        <v>67</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11">
-        <v>7</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11" s="9">
-        <v>2000000000000</v>
-      </c>
-      <c r="D11" s="10">
-        <v>1000000</v>
-      </c>
-      <c r="E11">
-        <v>19007</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11">
+      <c r="O12" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="1">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1">
+        <v>8</v>
+      </c>
+      <c r="C13" s="14">
+        <v>25600000000000</v>
+      </c>
+      <c r="D13" s="15">
+        <v>12800000</v>
+      </c>
+      <c r="E13" s="1">
+        <v>19009</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="1">
         <v>0</v>
       </c>
-      <c r="H11">
+      <c r="H13" s="1">
         <v>10000</v>
       </c>
-      <c r="I11" t="s">
-        <v>69</v>
-      </c>
-      <c r="J11" t="s">
-        <v>70</v>
-      </c>
-      <c r="K11" t="s">
-        <v>71</v>
-      </c>
-      <c r="L11" t="s">
-        <v>72</v>
-      </c>
-      <c r="M11" t="s">
-        <v>73</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12">
-        <v>8</v>
-      </c>
-      <c r="B12">
-        <v>7</v>
-      </c>
-      <c r="C12" s="9">
-        <v>8400000000000</v>
-      </c>
-      <c r="D12" s="10">
-        <v>4200000</v>
-      </c>
-      <c r="E12">
-        <v>19008</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12">
+      <c r="I13" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="1">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1">
+        <v>9</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="1">
+        <v>19010</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="1">
         <v>0</v>
       </c>
-      <c r="H12">
-        <v>10000</v>
-      </c>
-      <c r="I12" t="s">
-        <v>75</v>
-      </c>
-      <c r="J12" t="s">
-        <v>76</v>
-      </c>
-      <c r="K12" t="s">
-        <v>77</v>
-      </c>
-      <c r="L12" t="s">
-        <v>78</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13">
-        <v>9</v>
-      </c>
-      <c r="B13">
-        <v>8</v>
-      </c>
-      <c r="C13" s="9">
-        <v>25600000000000</v>
-      </c>
-      <c r="D13" s="10">
-        <v>12800000</v>
-      </c>
-      <c r="E13">
-        <v>19009</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13">
+      <c r="H14" s="1">
         <v>0</v>
       </c>
-      <c r="H13">
-        <v>10000</v>
-      </c>
-      <c r="I13" t="s">
-        <v>80</v>
-      </c>
-      <c r="J13" t="s">
-        <v>81</v>
-      </c>
-      <c r="K13" t="s">
-        <v>82</v>
-      </c>
-      <c r="L13" t="s">
-        <v>83</v>
-      </c>
-      <c r="O13" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14">
-        <v>10</v>
-      </c>
-      <c r="B14">
-        <v>9</v>
-      </c>
-      <c r="D14" s="10"/>
-      <c r="E14">
-        <v>19010</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14" t="s">
-        <v>85</v>
-      </c>
-      <c r="J14" t="s">
-        <v>86</v>
-      </c>
-      <c r="K14" t="s">
+      <c r="I14" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="L14" t="s">
+      <c r="J14" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="M14" t="s">
+      <c r="K14" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="O14" s="5" t="s">
+      <c r="L14" s="6" t="s">
         <v>90</v>
       </c>
+      <c r="M14" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="C16" s="12"/>
+      <c r="C16" s="17"/>
     </row>
     <row r="17" spans="3:7">
-      <c r="C17" s="12"/>
+      <c r="C17" s="17"/>
     </row>
     <row r="18" spans="3:7">
-      <c r="C18" s="12"/>
+      <c r="C18" s="17"/>
     </row>
     <row r="19" spans="3:7">
-      <c r="C19" s="12"/>
-      <c r="D19" s="9"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="14"/>
     </row>
     <row r="20" spans="3:7">
-      <c r="C20" s="12"/>
-      <c r="D20" s="9"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="14"/>
     </row>
     <row r="21" spans="3:7">
-      <c r="D21" s="9"/>
+      <c r="D21" s="14"/>
     </row>
     <row r="22" spans="3:7">
-      <c r="D22" s="9"/>
+      <c r="D22" s="14"/>
     </row>
     <row r="23" spans="3:7">
-      <c r="D23" s="9"/>
-      <c r="G23" s="9"/>
+      <c r="D23" s="14"/>
+      <c r="G23" s="14"/>
     </row>
     <row r="24" spans="3:7">
-      <c r="G24" s="9"/>
+      <c r="G24" s="14"/>
     </row>
     <row r="25" spans="3:7">
-      <c r="G25" s="9"/>
+      <c r="G25" s="14"/>
     </row>
     <row r="26" spans="3:7">
-      <c r="G26" s="9"/>
+      <c r="G26" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -57,28 +57,6 @@
 x:距离上次登录时间间隔大于X分钟,-1表示不需要判断
 Y:经验减少Y
 </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-道具ID_道具数量</t>
         </r>
       </text>
     </comment>
@@ -189,13 +167,13 @@
     <t>每周奖励</t>
   </si>
   <si>
-    <t>等级奖励</t>
+    <t>等级金币奖励</t>
   </si>
   <si>
     <t>年奖励</t>
   </si>
   <si>
-    <t>新解锁装扮</t>
+    <t>等级道具奖励</t>
   </si>
   <si>
     <t>服务器解锁装扮</t>
@@ -609,12 +587,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1097,7 +1075,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1116,9 +1094,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1127,18 +1102,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
@@ -1498,34 +1461,34 @@
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1539,13 +1502,13 @@
       <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="8" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -1554,25 +1517,25 @@
       <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1592,47 +1555,47 @@
       <c r="E3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="6" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="11"/>
-      <c r="M4" s="6" t="s">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="5"/>
+      <c r="M4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="O4" s="13"/>
+      <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
@@ -1641,14 +1604,14 @@
       <c r="B5" s="1">
         <v>0</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="9">
         <v>1648000</v>
       </c>
-      <c r="D5" s="15"/>
+      <c r="D5" s="10"/>
       <c r="E5" s="1">
         <v>19001</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G5" s="1">
@@ -1657,22 +1620,22 @@
       <c r="H5" s="1">
         <v>10000</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="O5" s="13"/>
+      <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
@@ -1681,14 +1644,14 @@
       <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="9">
         <v>18570000</v>
       </c>
-      <c r="D6" s="15"/>
+      <c r="D6" s="10"/>
       <c r="E6" s="1">
         <v>19002</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="1" t="s">
         <v>42</v>
       </c>
       <c r="G6" s="1">
@@ -1697,22 +1660,22 @@
       <c r="H6" s="1">
         <v>10000</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="O6" s="13"/>
+      <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
@@ -1721,14 +1684,14 @@
       <c r="B7" s="1">
         <v>2</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="9">
         <v>156972500</v>
       </c>
-      <c r="D7" s="15"/>
+      <c r="D7" s="10"/>
       <c r="E7" s="1">
         <v>19003</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G7" s="1">
@@ -1737,22 +1700,22 @@
       <c r="H7" s="1">
         <v>10000</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="O7" s="13"/>
+      <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
@@ -1761,14 +1724,14 @@
       <c r="B8" s="1">
         <v>3</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="9">
         <v>1604677500</v>
       </c>
-      <c r="D8" s="15"/>
+      <c r="D8" s="10"/>
       <c r="E8" s="1">
         <v>19004</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="1" t="s">
         <v>52</v>
       </c>
       <c r="G8" s="1">
@@ -1777,22 +1740,22 @@
       <c r="H8" s="1">
         <v>10000</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="O8" s="7" t="s">
+      <c r="O8" s="6" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1803,16 +1766,16 @@
       <c r="B9" s="1">
         <v>4</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="9">
         <v>60000000000</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="10">
         <v>30000</v>
       </c>
       <c r="E9" s="1">
         <v>19005</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="13" t="s">
         <v>59</v>
       </c>
       <c r="G9" s="1">
@@ -1821,22 +1784,22 @@
       <c r="H9" s="1">
         <v>10000</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="O9" s="7" t="s">
+      <c r="O9" s="6" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1847,16 +1810,16 @@
       <c r="B10" s="1">
         <v>5</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="9">
         <v>400000000000</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="10">
         <v>200000</v>
       </c>
       <c r="E10" s="1">
         <v>19006</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="13" t="s">
         <v>59</v>
       </c>
       <c r="G10" s="1">
@@ -1865,22 +1828,22 @@
       <c r="H10" s="1">
         <v>10000</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="O10" s="7" t="s">
+      <c r="O10" s="6" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1891,16 +1854,16 @@
       <c r="B11" s="1">
         <v>6</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="9">
         <v>2000000000000</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="10">
         <v>1000000</v>
       </c>
       <c r="E11" s="1">
         <v>19007</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="13" t="s">
         <v>59</v>
       </c>
       <c r="G11" s="1">
@@ -1909,22 +1872,22 @@
       <c r="H11" s="1">
         <v>10000</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="M11" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="O11" s="7" t="s">
+      <c r="O11" s="6" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1935,16 +1898,16 @@
       <c r="B12" s="1">
         <v>7</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="9">
         <v>8400000000000</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="10">
         <v>4200000</v>
       </c>
       <c r="E12" s="1">
         <v>19008</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="13" t="s">
         <v>59</v>
       </c>
       <c r="G12" s="1">
@@ -1953,22 +1916,22 @@
       <c r="H12" s="1">
         <v>10000</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="M12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="O12" s="7" t="s">
+      <c r="O12" s="6" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1979,16 +1942,16 @@
       <c r="B13" s="1">
         <v>8</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="9">
         <v>25600000000000</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="10">
         <v>12800000</v>
       </c>
       <c r="E13" s="1">
         <v>19009</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="13" t="s">
         <v>59</v>
       </c>
       <c r="G13" s="1">
@@ -1997,22 +1960,22 @@
       <c r="H13" s="1">
         <v>10000</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="M13" s="6" t="s">
+      <c r="M13" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="O13" s="7" t="s">
+      <c r="O13" s="6" t="s">
         <v>86</v>
       </c>
     </row>
@@ -2023,11 +1986,11 @@
       <c r="B14" s="1">
         <v>9</v>
       </c>
-      <c r="D14" s="15"/>
+      <c r="D14" s="10"/>
       <c r="E14" s="1">
         <v>19010</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="13" t="s">
         <v>59</v>
       </c>
       <c r="G14" s="1">
@@ -2036,60 +1999,60 @@
       <c r="H14" s="1">
         <v>0</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="J14" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="K14" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="L14" s="6" t="s">
+      <c r="L14" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="M14" s="6" t="s">
+      <c r="M14" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="O14" s="7" t="s">
+      <c r="O14" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="C16" s="17"/>
+      <c r="C16" s="12"/>
     </row>
     <row r="17" spans="3:7">
-      <c r="C17" s="17"/>
+      <c r="C17" s="12"/>
     </row>
     <row r="18" spans="3:7">
-      <c r="C18" s="17"/>
+      <c r="C18" s="12"/>
     </row>
     <row r="19" spans="3:7">
-      <c r="C19" s="17"/>
-      <c r="D19" s="14"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="9"/>
     </row>
     <row r="20" spans="3:7">
-      <c r="C20" s="17"/>
-      <c r="D20" s="14"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="9"/>
     </row>
     <row r="21" spans="3:7">
-      <c r="D21" s="14"/>
+      <c r="D21" s="9"/>
     </row>
     <row r="22" spans="3:7">
-      <c r="D22" s="14"/>
+      <c r="D22" s="9"/>
     </row>
     <row r="23" spans="3:7">
-      <c r="D23" s="14"/>
-      <c r="G23" s="14"/>
+      <c r="D23" s="9"/>
+      <c r="G23" s="9"/>
     </row>
     <row r="24" spans="3:7">
-      <c r="G24" s="14"/>
+      <c r="G24" s="9"/>
     </row>
     <row r="25" spans="3:7">
-      <c r="G25" s="14"/>
+      <c r="G25" s="9"/>
     </row>
     <row r="26" spans="3:7">
-      <c r="G26" s="14"/>
+      <c r="G26" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -4,13 +4,16 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="viplevel" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -57,6 +60,28 @@
 x:距离上次登录时间间隔大于X分钟,-1表示不需要判断
 Y:经验减少Y
 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+触发和刷新时间走globalConfig表中ID56值</t>
         </r>
       </text>
     </comment>
@@ -135,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="109">
   <si>
     <t>id</t>
   </si>
@@ -170,7 +195,7 @@
     <t>等级金币奖励</t>
   </si>
   <si>
-    <t>年奖励</t>
+    <t>季度奖励</t>
   </si>
   <si>
     <t>等级道具奖励</t>
@@ -194,12 +219,12 @@
     <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
+    <t>list&lt;int&gt;{|}</t>
+  </si>
+  <si>
     <t>map&lt;int{_}int&gt;{|}</t>
   </si>
   <si>
-    <t>list&lt;int&gt;{|}</t>
-  </si>
-  <si>
     <t>viplevel</t>
   </si>
   <si>
@@ -242,9 +267,6 @@
     <t>privilegedFunctions</t>
   </si>
   <si>
-    <t>client</t>
-  </si>
-  <si>
     <t>4320_164800</t>
   </si>
   <si>
@@ -257,10 +279,10 @@
     <t>1990000_4200000</t>
   </si>
   <si>
-    <t>1990000_6160000</t>
-  </si>
-  <si>
-    <t>1022502_1</t>
+    <t>1990000_1540000</t>
+  </si>
+  <si>
+    <t>1022502_1|1980000_10</t>
   </si>
   <si>
     <t>4320_928500</t>
@@ -275,7 +297,10 @@
     <t>1990000_8400000</t>
   </si>
   <si>
-    <t>1990000_12320000</t>
+    <t>1990000_3080000</t>
+  </si>
+  <si>
+    <t>1022501_5|1980000_20</t>
   </si>
   <si>
     <t>4320_5200000</t>
@@ -290,7 +315,10 @@
     <t>1990000_12600000</t>
   </si>
   <si>
-    <t>1990000_18480000</t>
+    <t>1990000_4620000</t>
+  </si>
+  <si>
+    <t>1010301_5|1980000_30</t>
   </si>
   <si>
     <t>4320_40000000</t>
@@ -305,46 +333,49 @@
     <t>1990000_21000000</t>
   </si>
   <si>
+    <t>1990000_7700000</t>
+  </si>
+  <si>
+    <t>1031600_1|1022503_5|1980000_50</t>
+  </si>
+  <si>
+    <t>1_100</t>
+  </si>
+  <si>
+    <t>-1_0</t>
+  </si>
+  <si>
+    <t>1990000_147000000</t>
+  </si>
+  <si>
+    <t>1990000_2100000</t>
+  </si>
+  <si>
+    <t>1990000_63000000</t>
+  </si>
+  <si>
+    <t>1990000_23100000</t>
+  </si>
+  <si>
+    <t>1031801_1|1022502_5|1980000_100</t>
+  </si>
+  <si>
+    <t>1_200</t>
+  </si>
+  <si>
+    <t>1990000_196000000</t>
+  </si>
+  <si>
+    <t>1990000_2800000</t>
+  </si>
+  <si>
+    <t>1990000_84000000</t>
+  </si>
+  <si>
     <t>1990000_30800000</t>
   </si>
   <si>
-    <t>1031600_1</t>
-  </si>
-  <si>
-    <t>1_100</t>
-  </si>
-  <si>
-    <t>-1_0</t>
-  </si>
-  <si>
-    <t>1990000_147000000</t>
-  </si>
-  <si>
-    <t>1990000_2100000</t>
-  </si>
-  <si>
-    <t>1990000_63000000</t>
-  </si>
-  <si>
-    <t>1990000_92400000</t>
-  </si>
-  <si>
-    <t>1022502_1|1022501_1</t>
-  </si>
-  <si>
-    <t>1_200</t>
-  </si>
-  <si>
-    <t>1990000_196000000</t>
-  </si>
-  <si>
-    <t>1990000_2800000</t>
-  </si>
-  <si>
-    <t>1990000_84000000</t>
-  </si>
-  <si>
-    <t>1990000_123200000</t>
+    <t>1032001_1|1022503_10|1980000_1000</t>
   </si>
   <si>
     <t>1_300</t>
@@ -359,40 +390,46 @@
     <t>1990000_105000000</t>
   </si>
   <si>
+    <t>1990000_38500000</t>
+  </si>
+  <si>
+    <t>1032201_1|1022502_10|1980000_2000</t>
+  </si>
+  <si>
+    <t>1_400|2_250</t>
+  </si>
+  <si>
+    <t>1990000_490000000</t>
+  </si>
+  <si>
+    <t>1990000_7000000</t>
+  </si>
+  <si>
+    <t>1990000_210000000</t>
+  </si>
+  <si>
+    <t>1990000_77000000</t>
+  </si>
+  <si>
+    <t>1031802_1|1022503_20|1980000_3000</t>
+  </si>
+  <si>
+    <t>1_500|2_500</t>
+  </si>
+  <si>
+    <t>1990000_980000000</t>
+  </si>
+  <si>
+    <t>1990000_14000000</t>
+  </si>
+  <si>
+    <t>1990000_420000000</t>
+  </si>
+  <si>
     <t>1990000_154000000</t>
   </si>
   <si>
-    <t>1031601_1|1031801_1|1032001_1|1032201_1</t>
-  </si>
-  <si>
-    <t>1_400|2_250</t>
-  </si>
-  <si>
-    <t>1990000_490000000</t>
-  </si>
-  <si>
-    <t>1990000_7000000</t>
-  </si>
-  <si>
-    <t>1990000_210000000</t>
-  </si>
-  <si>
-    <t>1990000_308000000</t>
-  </si>
-  <si>
-    <t>1_500|2_500</t>
-  </si>
-  <si>
-    <t>1990000_980000000</t>
-  </si>
-  <si>
-    <t>1990000_14000000</t>
-  </si>
-  <si>
-    <t>1990000_420000000</t>
-  </si>
-  <si>
-    <t>1990000_616000000</t>
+    <t>1032002_1|1022502_20|1980000_5000</t>
   </si>
   <si>
     <t>1_500|2_750</t>
@@ -407,13 +444,49 @@
     <t>1990000_1050000000</t>
   </si>
   <si>
-    <t>1990000_1540000000</t>
-  </si>
-  <si>
-    <t>1031602_1|1031802_1|1032002_1|1032202_1</t>
+    <t>1990000_385000000</t>
+  </si>
+  <si>
+    <t>1032202_1|1022503_20|1980000_10000</t>
   </si>
   <si>
     <t>1_500|2_1000</t>
+  </si>
+  <si>
+    <t>刮刮卡</t>
+  </si>
+  <si>
+    <t>钻石</t>
+  </si>
+  <si>
+    <t>祈福卡</t>
+  </si>
+  <si>
+    <t>赌场工具（普通）</t>
+  </si>
+  <si>
+    <t>头衔1</t>
+  </si>
+  <si>
+    <t>夺宝优惠券</t>
+  </si>
+  <si>
+    <t>筹码2</t>
+  </si>
+  <si>
+    <t>牌背2</t>
+  </si>
+  <si>
+    <t>大厅背景2</t>
+  </si>
+  <si>
+    <t>筹码3</t>
+  </si>
+  <si>
+    <t>牌背3</t>
+  </si>
+  <si>
+    <t>大厅背景3</t>
   </si>
 </sst>
 </file>
@@ -428,7 +501,7 @@
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -441,6 +514,12 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -587,12 +666,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -604,6 +683,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -758,12 +843,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -945,55 +1024,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1008,78 +1084,84 @@
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1088,16 +1170,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1106,7 +1188,7 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -1177,6 +1259,1740 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Item"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>道具ID</v>
+          </cell>
+        </row>
+        <row r="1">
+          <cell r="D1" t="str">
+            <v>备注</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>int</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>id</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>1010101</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5" t="str">
+            <v>金币礼包</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>1010201</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="D6" t="str">
+            <v>钻石礼包</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>1010301</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="D7" t="str">
+            <v>赌场工具（普通）</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>1010302</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8" t="str">
+            <v>赌场工具（精良）</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>1010303</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9" t="str">
+            <v>赌场工具（优秀）</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>1010304</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="D10" t="str">
+            <v>赌场工具（绝佳）</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>1010305</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="D11" t="str">
+            <v>赌场工具（传奇）</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>1010311</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="D12" t="str">
+            <v>拼图随机礼包(一星)</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>1010312</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="D13" t="str">
+            <v>拼图随机礼包(二星)</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>1010313</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="D14" t="str">
+            <v>拼图随机礼包(三星)</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>1010314</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="D15" t="str">
+            <v>拼图随机礼包(四星)</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>1010315</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="D16" t="str">
+            <v>拼图随机礼包(五星)</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>1020001</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="D17" t="str">
+            <v>白金卡</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>1020002</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="D18" t="str">
+            <v>测试道具2</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>1020003</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="D19" t="str">
+            <v>测试道具3</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>1020004</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="D20" t="str">
+            <v>测试道具4</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>1020005</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="D21" t="str">
+            <v>测试道具5</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>1020006</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="D22" t="str">
+            <v>测试道具6</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>1030011</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="D23" t="str">
+            <v>图鉴1-图片</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>1030012</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="D24" t="str">
+            <v>图鉴2-图片</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>1030013</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="D25" t="str">
+            <v>图鉴3-图片</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>1030014</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="D26" t="str">
+            <v>图鉴4-图片</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>1030015</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="D27" t="str">
+            <v>图鉴5-图片</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>1030016</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="D28" t="str">
+            <v>图鉴6-图片</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>1030017</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="D29" t="str">
+            <v>图鉴7-图片</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>1030018</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="D30" t="str">
+            <v>图鉴8-图片</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>1030101</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="D31" t="str">
+            <v>图鉴1-碎片1</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>1030102</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="D32" t="str">
+            <v>图鉴1-碎片2</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>1030103</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="D33" t="str">
+            <v>图鉴1-碎片3</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>1030104</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="D34" t="str">
+            <v>图鉴1-碎片4</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>1030105</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="D35" t="str">
+            <v>图鉴1-碎片5</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36">
+            <v>1030106</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="D36" t="str">
+            <v>图鉴1-碎片6</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>1030107</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="D37" t="str">
+            <v>图鉴1-碎片7</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>1030108</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="D38" t="str">
+            <v>图鉴1-碎片8</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>1030109</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="D39" t="str">
+            <v>图鉴1-碎片9</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>1030110</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="D40" t="str">
+            <v>图鉴1-碎片10</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>1030111</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="D41" t="str">
+            <v>图鉴1-碎片11</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>1030112</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="D42" t="str">
+            <v>图鉴1-碎片12</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>1030121</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="D43" t="str">
+            <v>图鉴2-碎片1</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>1030122</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="D44" t="str">
+            <v>图鉴2-碎片2</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>1030123</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="D45" t="str">
+            <v>图鉴2-碎片3</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46">
+            <v>1030124</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="D46" t="str">
+            <v>图鉴2-碎片4</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47">
+            <v>1030125</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="D47" t="str">
+            <v>图鉴2-碎片5</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48">
+            <v>1030126</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="D48" t="str">
+            <v>图鉴2-碎片6</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49">
+            <v>1030127</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="D49" t="str">
+            <v>图鉴2-碎片7</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50">
+            <v>1030128</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="D50" t="str">
+            <v>图鉴2-碎片8</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51">
+            <v>1030129</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="D51" t="str">
+            <v>图鉴2-碎片9</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52">
+            <v>1030130</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="D52" t="str">
+            <v>图鉴2-碎片10</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53">
+            <v>1030131</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="D53" t="str">
+            <v>图鉴2-碎片11</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54">
+            <v>1030132</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="D54" t="str">
+            <v>图鉴2-碎片12</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55">
+            <v>1030141</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="D55" t="str">
+            <v>图鉴3-碎片1</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56">
+            <v>1030142</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="D56" t="str">
+            <v>图鉴3-碎片2</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57">
+            <v>1030143</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="D57" t="str">
+            <v>图鉴3-碎片3</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58">
+            <v>1030144</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="D58" t="str">
+            <v>图鉴3-碎片4</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59">
+            <v>1030145</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="D59" t="str">
+            <v>图鉴3-碎片5</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60">
+            <v>1030146</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="D60" t="str">
+            <v>图鉴3-碎片6</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61">
+            <v>1030147</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="D61" t="str">
+            <v>图鉴3-碎片7</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62">
+            <v>1030148</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="D62" t="str">
+            <v>图鉴3-碎片8</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63">
+            <v>1030149</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="D63" t="str">
+            <v>图鉴3-碎片9</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64">
+            <v>1030150</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="D64" t="str">
+            <v>图鉴3-碎片10</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65">
+            <v>1030151</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="D65" t="str">
+            <v>图鉴3-碎片11</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66">
+            <v>1030152</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="D66" t="str">
+            <v>图鉴3-碎片12</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67">
+            <v>1030161</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="D67" t="str">
+            <v>图鉴4-碎片1</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68">
+            <v>1030162</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="D68" t="str">
+            <v>图鉴4-碎片2</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69">
+            <v>1030163</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="D69" t="str">
+            <v>图鉴4-碎片3</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70">
+            <v>1030164</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="D70" t="str">
+            <v>图鉴4-碎片4</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71">
+            <v>1030165</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="D71" t="str">
+            <v>图鉴4-碎片5</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72">
+            <v>1030166</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="D72" t="str">
+            <v>图鉴4-碎片6</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="A73">
+            <v>1030167</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="D73" t="str">
+            <v>图鉴4-碎片7</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="A74">
+            <v>1030168</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="D74" t="str">
+            <v>图鉴4-碎片8</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="A75">
+            <v>1030169</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="D75" t="str">
+            <v>图鉴4-碎片9</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="A76">
+            <v>1030170</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="D76" t="str">
+            <v>图鉴4-碎片10</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="A77">
+            <v>1030171</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="D77" t="str">
+            <v>图鉴4-碎片11</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="A78">
+            <v>1030172</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="D78" t="str">
+            <v>图鉴4-碎片12</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="A79">
+            <v>1030181</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="D79" t="str">
+            <v>图鉴5-碎片1</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="A80">
+            <v>1030182</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="D80" t="str">
+            <v>图鉴5-碎片2</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="A81">
+            <v>1030183</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="D81" t="str">
+            <v>图鉴5-碎片3</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="A82">
+            <v>1030184</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="D82" t="str">
+            <v>图鉴5-碎片4</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="A83">
+            <v>1030185</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="D83" t="str">
+            <v>图鉴5-碎片5</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="A84">
+            <v>1030186</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="D84" t="str">
+            <v>图鉴5-碎片6</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="A85">
+            <v>1030187</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="D85" t="str">
+            <v>图鉴5-碎片7</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="A86">
+            <v>1030188</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="D86" t="str">
+            <v>图鉴5-碎片8</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="A87">
+            <v>1030189</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="D87" t="str">
+            <v>图鉴5-碎片9</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="A88">
+            <v>1030190</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="D88" t="str">
+            <v>图鉴5-碎片10</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="A89">
+            <v>1030191</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="D89" t="str">
+            <v>图鉴5-碎片11</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="A90">
+            <v>1030192</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="D90" t="str">
+            <v>图鉴5-碎片12</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="A91">
+            <v>1030201</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="D91" t="str">
+            <v>图鉴6-碎片1</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="A92">
+            <v>1030202</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="D92" t="str">
+            <v>图鉴6-碎片2</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="A93">
+            <v>1030203</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="D93" t="str">
+            <v>图鉴6-碎片3</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="A94">
+            <v>1030204</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="D94" t="str">
+            <v>图鉴6-碎片4</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="A95">
+            <v>1030205</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="D95" t="str">
+            <v>图鉴6-碎片5</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="A96">
+            <v>1030206</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="D96" t="str">
+            <v>图鉴6-碎片6</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="A97">
+            <v>1030207</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="D97" t="str">
+            <v>图鉴6-碎片7</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="A98">
+            <v>1030208</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="D98" t="str">
+            <v>图鉴6-碎片8</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="A99">
+            <v>1030209</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="D99" t="str">
+            <v>图鉴6-碎片9</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="A100">
+            <v>1030210</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="D100" t="str">
+            <v>图鉴6-碎片10</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="A101">
+            <v>1030211</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="D101" t="str">
+            <v>图鉴6-碎片11</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="A102">
+            <v>1030212</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="D102" t="str">
+            <v>图鉴6-碎片12</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="A103">
+            <v>1030221</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="D103" t="str">
+            <v>图鉴7-碎片1</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="A104">
+            <v>1030222</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="D104" t="str">
+            <v>图鉴7-碎片2</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="A105">
+            <v>1030223</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="D105" t="str">
+            <v>图鉴7-碎片3</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="A106">
+            <v>1030224</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="D106" t="str">
+            <v>图鉴7-碎片4</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="A107">
+            <v>1030225</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="D107" t="str">
+            <v>图鉴7-碎片5</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="A108">
+            <v>1030226</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="D108" t="str">
+            <v>图鉴7-碎片6</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="A109">
+            <v>1030227</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="D109" t="str">
+            <v>图鉴7-碎片7</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="A110">
+            <v>1030228</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="D110" t="str">
+            <v>图鉴7-碎片8</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="A111">
+            <v>1030229</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="D111" t="str">
+            <v>图鉴7-碎片9</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="A112">
+            <v>1030230</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="D112" t="str">
+            <v>图鉴7-碎片10</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="A113">
+            <v>1030231</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="D113" t="str">
+            <v>图鉴7-碎片11</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="A114">
+            <v>1030232</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="D114" t="str">
+            <v>图鉴7-碎片12</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="A115">
+            <v>1030241</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="D115" t="str">
+            <v>图鉴8-碎片1</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="A116">
+            <v>1030242</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="D116" t="str">
+            <v>图鉴8-碎片2</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="A117">
+            <v>1030243</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="D117" t="str">
+            <v>图鉴8-碎片3</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="A118">
+            <v>1030244</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="D118" t="str">
+            <v>图鉴8-碎片4</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="A119">
+            <v>1030245</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="D119" t="str">
+            <v>图鉴8-碎片5</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="A120">
+            <v>1030246</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="D120" t="str">
+            <v>图鉴8-碎片6</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="A121">
+            <v>1030247</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="D121" t="str">
+            <v>图鉴8-碎片7</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="A122">
+            <v>1030248</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="D122" t="str">
+            <v>图鉴8-碎片8</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="A123">
+            <v>1030249</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="D123" t="str">
+            <v>图鉴8-碎片9</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="A124">
+            <v>1030250</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="D124" t="str">
+            <v>图鉴8-碎片10</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="A125">
+            <v>1030251</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="D125" t="str">
+            <v>图鉴8-碎片11</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="A126">
+            <v>1030252</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="D126" t="str">
+            <v>图鉴8-碎片12</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="A127">
+            <v>1031001</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="D127" t="str">
+            <v>头像2</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="A128">
+            <v>1031002</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="D128" t="str">
+            <v>头像3</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="A129">
+            <v>1031201</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="D129" t="str">
+            <v>头像框2</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="A130">
+            <v>1031202</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="D130" t="str">
+            <v>头像框3</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="A131">
+            <v>1031350</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="D131" t="str">
+            <v>头像框-每日奖金</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="A132">
+            <v>1031351</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="D132" t="str">
+            <v>头像框-首充专属</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="A133">
+            <v>1021401</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="D133" t="str">
+            <v>国旗2</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="A134">
+            <v>1021402</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="D134" t="str">
+            <v>国旗3</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="A135">
+            <v>1031600</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="D135" t="str">
+            <v>头衔1</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="A136">
+            <v>1031601</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="D136" t="str">
+            <v>头衔2</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="A137">
+            <v>1031602</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="D137" t="str">
+            <v>头衔3</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="A138">
+            <v>1031801</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="D138" t="str">
+            <v>筹码2</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="A139">
+            <v>1031802</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="D139" t="str">
+            <v>筹码3</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="A140">
+            <v>1032001</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="D140" t="str">
+            <v>牌背2</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="A141">
+            <v>1032002</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="D141" t="str">
+            <v>牌背3</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="A142">
+            <v>1032201</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="D142" t="str">
+            <v>大厅背景2</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="A143">
+            <v>1032202</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="D143" t="str">
+            <v>大厅背景3</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="A144">
+            <v>1022501</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="D144" t="str">
+            <v>祈福卡</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="A145">
+            <v>1022502</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="D145" t="str">
+            <v>刮刮卡</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="A146">
+            <v>1022503</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="D146" t="str">
+            <v>夺宝优惠券</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="A147">
+            <v>1022504</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="D147" t="str">
+            <v>积分</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="A148">
+            <v>1023001</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="D148" t="str">
+            <v>1星扳手</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="A149">
+            <v>1023002</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="D149" t="str">
+            <v>2星扳手</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="A150">
+            <v>1023003</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="D150" t="str">
+            <v>3星扳手</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="A151">
+            <v>1023004</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="D151" t="str">
+            <v>4星扳手</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="A152">
+            <v>1023005</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="D152" t="str">
+            <v>5星扳手</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="A153">
+            <v>1023101</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="D153" t="str">
+            <v>1星筹码</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="A154">
+            <v>1023102</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="D154" t="str">
+            <v>2星筹码</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="A155">
+            <v>1023103</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="D155" t="str">
+            <v>3星筹码</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="A156">
+            <v>1023104</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="D156" t="str">
+            <v>4星筹码</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="A157">
+            <v>1023105</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="D157" t="str">
+            <v>5星筹码</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="A158">
+            <v>1023201</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="D158" t="str">
+            <v>1星螺母</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="A159">
+            <v>1023202</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="D159" t="str">
+            <v>2星螺母</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="A160">
+            <v>1023203</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="D160" t="str">
+            <v>3星螺母</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="A161">
+            <v>1023204</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="D161" t="str">
+            <v>4星螺母</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="A162">
+            <v>1023205</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="D162" t="str">
+            <v>5星螺母</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="A163">
+            <v>1023301</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="D163" t="str">
+            <v>1星木材</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="A164">
+            <v>1023302</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="D164" t="str">
+            <v>2星木材</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="A165">
+            <v>1023303</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="D165" t="str">
+            <v>3星木材</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="A166">
+            <v>1023304</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="D166" t="str">
+            <v>4星木材</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="A167">
+            <v>1023305</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="D167" t="str">
+            <v>5星木材</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="A168">
+            <v>1023401</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="D168" t="str">
+            <v>1星酒瓶</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="A169">
+            <v>1023402</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="D169" t="str">
+            <v>2星酒瓶</v>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="A170">
+            <v>1023403</v>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="D170" t="str">
+            <v>3星酒瓶</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="A171">
+            <v>1023404</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="D171" t="str">
+            <v>4星酒瓶</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="A172">
+            <v>1023405</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="D172" t="str">
+            <v>5星酒瓶</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="A173">
+            <v>1990000</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="D173" t="str">
+            <v>金币</v>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="A174">
+            <v>1980000</v>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="D174" t="str">
+            <v>钻石</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1429,7 +3245,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.625" style="1" customWidth="1"/>
@@ -1439,26 +3255,28 @@
     <col min="6" max="6" width="17.375" style="1" customWidth="1"/>
     <col min="7" max="8" width="21.25" style="1" customWidth="1"/>
     <col min="9" max="12" width="20.375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="26.6166666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="37.375" style="1" customWidth="1"/>
     <col min="14" max="14" width="21.7666666666667" style="1" customWidth="1"/>
     <col min="15" max="15" width="20.375" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="16" max="17" width="9" style="1"/>
+    <col min="18" max="18" width="9.25" style="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1488,33 +3306,33 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:25">
+      <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -1530,29 +3348,29 @@
         <v>18</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="O2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:25">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>24</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -1582,37 +3400,34 @@
       <c r="N3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5"/>
-      <c r="M4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="O4" s="6"/>
+    <row r="4" spans="1:25">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="6"/>
+      <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="1">
         <v>0</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="10">
         <v>1648000</v>
       </c>
-      <c r="D5" s="10"/>
+      <c r="D5" s="11"/>
       <c r="E5" s="1">
         <v>19001</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G5" s="1">
         <v>10000</v>
@@ -1621,38 +3436,48 @@
         <v>10000</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O5" s="6"/>
+      <c r="O5" s="7"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5"/>
+      <c r="T5"/>
+      <c r="U5"/>
+      <c r="V5"/>
+      <c r="W5"/>
+      <c r="X5"/>
+      <c r="Y5"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:25">
       <c r="A6" s="1">
         <v>2</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="10">
         <v>18570000</v>
       </c>
-      <c r="D6" s="10"/>
+      <c r="D6" s="11"/>
       <c r="E6" s="1">
         <v>19002</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6" s="1">
         <v>10000</v>
@@ -1661,33 +3486,43 @@
         <v>10000</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="M6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O6" s="6"/>
+      <c r="O6" s="7"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+      <c r="R6"/>
+      <c r="S6"/>
+      <c r="T6"/>
+      <c r="U6"/>
+      <c r="V6"/>
+      <c r="W6"/>
+      <c r="X6"/>
+      <c r="Y6"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:25">
       <c r="A7" s="1">
         <v>3</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="10">
         <v>156972500</v>
       </c>
-      <c r="D7" s="10"/>
+      <c r="D7" s="11"/>
       <c r="E7" s="1">
         <v>19003</v>
       </c>
@@ -1713,26 +3548,36 @@
         <v>51</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O7" s="6"/>
+        <v>52</v>
+      </c>
+      <c r="O7" s="7"/>
+      <c r="P7"/>
+      <c r="Q7"/>
+      <c r="R7"/>
+      <c r="S7"/>
+      <c r="T7"/>
+      <c r="U7"/>
+      <c r="V7"/>
+      <c r="W7"/>
+      <c r="X7"/>
+      <c r="Y7"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:25">
       <c r="A8" s="1">
         <v>4</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="10">
         <v>1604677500</v>
       </c>
-      <c r="D8" s="10"/>
+      <c r="D8" s="11"/>
       <c r="E8" s="1">
         <v>19004</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8" s="1">
         <v>10000</v>
@@ -1741,42 +3586,52 @@
         <v>10000</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="O8" s="6" t="s">
         <v>58</v>
       </c>
+      <c r="O8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8"/>
+      <c r="T8"/>
+      <c r="U8"/>
+      <c r="V8"/>
+      <c r="W8"/>
+      <c r="X8"/>
+      <c r="Y8"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:25">
       <c r="A9" s="1">
         <v>5</v>
       </c>
       <c r="B9" s="1">
         <v>4</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="10">
         <v>60000000000</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="11">
         <v>30000</v>
       </c>
       <c r="E9" s="1">
         <v>19005</v>
       </c>
-      <c r="F9" s="13" t="s">
-        <v>59</v>
+      <c r="F9" s="14" t="s">
+        <v>60</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -1785,42 +3640,52 @@
         <v>10000</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O9" s="6" t="s">
         <v>65</v>
       </c>
+      <c r="O9" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="P9"/>
+      <c r="Q9"/>
+      <c r="R9"/>
+      <c r="S9"/>
+      <c r="T9"/>
+      <c r="U9"/>
+      <c r="V9"/>
+      <c r="W9"/>
+      <c r="X9"/>
+      <c r="Y9"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:25">
       <c r="A10" s="1">
         <v>6</v>
       </c>
       <c r="B10" s="1">
         <v>5</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="10">
         <v>400000000000</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="11">
         <v>200000</v>
       </c>
       <c r="E10" s="1">
         <v>19006</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>59</v>
+      <c r="F10" s="14" t="s">
+        <v>60</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1829,42 +3694,52 @@
         <v>10000</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P10"/>
+      <c r="Q10"/>
+      <c r="R10"/>
+      <c r="S10"/>
+      <c r="T10"/>
+      <c r="U10"/>
+      <c r="V10"/>
+      <c r="W10"/>
+      <c r="X10"/>
+      <c r="Y10"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:25">
       <c r="A11" s="1">
         <v>7</v>
       </c>
       <c r="B11" s="1">
         <v>6</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="10">
         <v>2000000000000</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="11">
         <v>1000000</v>
       </c>
       <c r="E11" s="1">
         <v>19007</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>59</v>
+      <c r="F11" s="14" t="s">
+        <v>60</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -1873,42 +3748,52 @@
         <v>10000</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="P11"/>
+      <c r="Q11"/>
+      <c r="R11"/>
+      <c r="S11"/>
+      <c r="T11"/>
+      <c r="U11"/>
+      <c r="V11"/>
+      <c r="W11"/>
+      <c r="X11"/>
+      <c r="Y11"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:25">
       <c r="A12" s="1">
         <v>8</v>
       </c>
       <c r="B12" s="1">
         <v>7</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="10">
         <v>8400000000000</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="11">
         <v>4200000</v>
       </c>
       <c r="E12" s="1">
         <v>19008</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>59</v>
+      <c r="F12" s="14" t="s">
+        <v>60</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1917,42 +3802,52 @@
         <v>10000</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>81</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="P12"/>
+      <c r="Q12"/>
+      <c r="R12"/>
+      <c r="S12"/>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
+      <c r="W12"/>
+      <c r="X12"/>
+      <c r="Y12"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:25">
       <c r="A13" s="1">
         <v>9</v>
       </c>
       <c r="B13" s="1">
         <v>8</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="10">
         <v>25600000000000</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="11">
         <v>12800000</v>
       </c>
       <c r="E13" s="1">
         <v>19009</v>
       </c>
-      <c r="F13" s="13" t="s">
-        <v>59</v>
+      <c r="F13" s="14" t="s">
+        <v>60</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -1961,37 +3856,47 @@
         <v>10000</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>86</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="P13"/>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
+      <c r="W13"/>
+      <c r="X13"/>
+      <c r="Y13"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:25">
       <c r="A14" s="1">
         <v>10</v>
       </c>
       <c r="B14" s="1">
         <v>9</v>
       </c>
-      <c r="D14" s="10"/>
+      <c r="D14" s="11"/>
       <c r="E14" s="1">
         <v>19010</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>59</v>
+      <c r="F14" s="14" t="s">
+        <v>60</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -2000,59 +3905,69 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>92</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="P14"/>
+      <c r="Q14"/>
+      <c r="R14"/>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14"/>
+      <c r="W14"/>
+      <c r="X14"/>
+      <c r="Y14"/>
     </row>
-    <row r="16" spans="1:15">
-      <c r="C16" s="12"/>
+    <row r="16" spans="1:25">
+      <c r="C16" s="13"/>
     </row>
     <row r="17" spans="3:7">
-      <c r="C17" s="12"/>
+      <c r="C17" s="13"/>
     </row>
     <row r="18" spans="3:7">
-      <c r="C18" s="12"/>
+      <c r="C18" s="13"/>
     </row>
     <row r="19" spans="3:7">
-      <c r="C19" s="12"/>
-      <c r="D19" s="9"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="10"/>
     </row>
     <row r="20" spans="3:7">
-      <c r="C20" s="12"/>
-      <c r="D20" s="9"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="10"/>
     </row>
     <row r="21" spans="3:7">
-      <c r="D21" s="9"/>
+      <c r="D21" s="10"/>
     </row>
     <row r="22" spans="3:7">
-      <c r="D22" s="9"/>
+      <c r="D22" s="10"/>
     </row>
     <row r="23" spans="3:7">
-      <c r="D23" s="9"/>
-      <c r="G23" s="9"/>
+      <c r="D23" s="10"/>
+      <c r="G23" s="10"/>
     </row>
     <row r="24" spans="3:7">
-      <c r="G24" s="9"/>
+      <c r="G24" s="10"/>
     </row>
     <row r="25" spans="3:7">
-      <c r="G25" s="9"/>
+      <c r="G25" s="10"/>
     </row>
     <row r="26" spans="3:7">
-      <c r="G26" s="9"/>
+      <c r="G26" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2065,9 +3980,339 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
+  <dimension ref="A4:J13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <sheetData>
+    <row r="4" ht="16.5" spans="1:10">
+      <c r="A4" s="1">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="1">
+        <f>_xlfn.XLOOKUP(B4,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1022502</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" s="1">
+        <f>_xlfn.XLOOKUP(E4,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1980000</v>
+      </c>
+      <c r="G4" s="1">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:10">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="1">
+        <f>_xlfn.XLOOKUP(B5,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1022501</v>
+      </c>
+      <c r="D5" s="1">
+        <v>5</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" s="1">
+        <f>_xlfn.XLOOKUP(E5,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1980000</v>
+      </c>
+      <c r="G5" s="1">
+        <v>20</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" ht="16.5" spans="1:10">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="1">
+        <f>_xlfn.XLOOKUP(B6,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1010301</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="1">
+        <f>_xlfn.XLOOKUP(E6,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1980000</v>
+      </c>
+      <c r="G6" s="1">
+        <v>30</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:10">
+      <c r="A7" s="1">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="1">
+        <f>_xlfn.XLOOKUP(B7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1031600</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7" s="1">
+        <f>_xlfn.XLOOKUP(E7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1022503</v>
+      </c>
+      <c r="G7" s="1">
+        <v>5</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I7" s="1">
+        <f>_xlfn.XLOOKUP(H7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1980000</v>
+      </c>
+      <c r="J7" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:10">
+      <c r="A8" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="1">
+        <f>_xlfn.XLOOKUP(B8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1031801</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="1">
+        <f>_xlfn.XLOOKUP(E8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1022502</v>
+      </c>
+      <c r="G8" s="1">
+        <v>5</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I8" s="1">
+        <f>_xlfn.XLOOKUP(H8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1980000</v>
+      </c>
+      <c r="J8" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:10">
+      <c r="A9" s="1">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="1">
+        <f>_xlfn.XLOOKUP(B9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1032001</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F9" s="1">
+        <f>_xlfn.XLOOKUP(E9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1022503</v>
+      </c>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I9" s="1">
+        <f>_xlfn.XLOOKUP(H9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1980000</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:10">
+      <c r="A10" s="1">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="1">
+        <f>_xlfn.XLOOKUP(B10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1032201</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" s="1">
+        <f>_xlfn.XLOOKUP(E10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1022502</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" s="1">
+        <f>_xlfn.XLOOKUP(H10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1980000</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:10">
+      <c r="A11" s="1">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="1">
+        <f>_xlfn.XLOOKUP(B11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1031802</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="1">
+        <f>_xlfn.XLOOKUP(E11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1022503</v>
+      </c>
+      <c r="G11" s="1">
+        <v>20</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I11" s="1">
+        <f>_xlfn.XLOOKUP(H11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1980000</v>
+      </c>
+      <c r="J11" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:10">
+      <c r="A12" s="1">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="1">
+        <f>_xlfn.XLOOKUP(B12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1032002</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="1">
+        <f>_xlfn.XLOOKUP(E12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1022502</v>
+      </c>
+      <c r="G12" s="1">
+        <v>20</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I12" s="1">
+        <f>_xlfn.XLOOKUP(H12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1980000</v>
+      </c>
+      <c r="J12" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:10">
+      <c r="A13" s="1">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="1">
+        <f>_xlfn.XLOOKUP(B13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1032202</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F13" s="1">
+        <f>_xlfn.XLOOKUP(E13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1022503</v>
+      </c>
+      <c r="G13" s="1">
+        <v>20</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I13" s="1">
+        <f>_xlfn.XLOOKUP(H13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
+        <v>1980000</v>
+      </c>
+      <c r="J13" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="viplevel" sheetId="1" r:id="rId1"/>
@@ -393,7 +393,7 @@
     <t>1990000_38500000</t>
   </si>
   <si>
-    <t>1032201_1|1022502_10|1980000_2000</t>
+    <t>1030601_1|1032201_1|1022502_10|1980000_2000</t>
   </si>
   <si>
     <t>1_400|2_250</t>
@@ -447,7 +447,7 @@
     <t>1990000_385000000</t>
   </si>
   <si>
-    <t>1032202_1|1022503_20|1980000_10000</t>
+    <t>1030602_1|1032202_1|1022503_20|1980000_10000</t>
   </si>
   <si>
     <t>1_500|2_1000</t>
@@ -2596,7 +2596,7 @@
         </row>
         <row r="135">
           <cell r="D135" t="str">
-            <v>头衔1</v>
+            <v>头衔1-财富贵族</v>
           </cell>
         </row>
         <row r="136">
@@ -2606,7 +2606,7 @@
         </row>
         <row r="136">
           <cell r="D136" t="str">
-            <v>头衔2</v>
+            <v>头衔2-一夜暴富</v>
           </cell>
         </row>
         <row r="137">
@@ -2616,7 +2616,7 @@
         </row>
         <row r="137">
           <cell r="D137" t="str">
-            <v>头衔3</v>
+            <v>头衔3-四方来财</v>
           </cell>
         </row>
         <row r="138">
@@ -2626,7 +2626,7 @@
         </row>
         <row r="138">
           <cell r="D138" t="str">
-            <v>筹码2</v>
+            <v>筹码2-翡翠贵族</v>
           </cell>
         </row>
         <row r="139">
@@ -2636,7 +2636,7 @@
         </row>
         <row r="139">
           <cell r="D139" t="str">
-            <v>筹码3</v>
+            <v>筹码3-水晶皇室</v>
           </cell>
         </row>
         <row r="140">
@@ -2646,7 +2646,7 @@
         </row>
         <row r="140">
           <cell r="D140" t="str">
-            <v>牌背2</v>
+            <v>牌背2-神秘塔罗</v>
           </cell>
         </row>
         <row r="141">
@@ -2656,7 +2656,7 @@
         </row>
         <row r="141">
           <cell r="D141" t="str">
-            <v>牌背3</v>
+            <v>牌背3-命运之手</v>
           </cell>
         </row>
         <row r="142">
@@ -2666,7 +2666,7 @@
         </row>
         <row r="142">
           <cell r="D142" t="str">
-            <v>大厅背景2</v>
+            <v>大厅背景2-决赛之夜</v>
           </cell>
         </row>
         <row r="143">
@@ -2676,7 +2676,7 @@
         </row>
         <row r="143">
           <cell r="D143" t="str">
-            <v>大厅背景3</v>
+            <v>大厅背景3-度假海滩</v>
           </cell>
         </row>
         <row r="144">
@@ -4074,9 +4074,9 @@
       <c r="B7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="1" t="e">
         <f>_xlfn.XLOOKUP(B7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
-        <v>1031600</v>
+        <v>#N/A</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -4109,9 +4109,9 @@
       <c r="B8" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="1" t="e">
         <f>_xlfn.XLOOKUP(B8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
-        <v>1031801</v>
+        <v>#N/A</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -4144,9 +4144,9 @@
       <c r="B9" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="1" t="e">
         <f>_xlfn.XLOOKUP(B9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
-        <v>1032001</v>
+        <v>#N/A</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -4179,9 +4179,9 @@
       <c r="B10" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="1" t="e">
         <f>_xlfn.XLOOKUP(B10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
-        <v>1032201</v>
+        <v>#N/A</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -4214,9 +4214,9 @@
       <c r="B11" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="1" t="e">
         <f>_xlfn.XLOOKUP(B11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
-        <v>1031802</v>
+        <v>#N/A</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -4249,9 +4249,9 @@
       <c r="B12" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="1" t="e">
         <f>_xlfn.XLOOKUP(B12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
-        <v>1032002</v>
+        <v>#N/A</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
@@ -4284,9 +4284,9 @@
       <c r="B13" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="1" t="e">
         <f>_xlfn.XLOOKUP(B13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
-        <v>1032202</v>
+        <v>#N/A</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -393,7 +393,7 @@
     <t>1990000_38500000</t>
   </si>
   <si>
-    <t>1030601_1|1032201_1|1022502_10|1980000_2000</t>
+    <t>1031601_1|1032201_1|1022502_10|1980000_2000</t>
   </si>
   <si>
     <t>1_400|2_250</t>
@@ -447,7 +447,7 @@
     <t>1990000_385000000</t>
   </si>
   <si>
-    <t>1030602_1|1032202_1|1022503_20|1980000_10000</t>
+    <t>1031602_1|1032202_1|1022503_20|1980000_10000</t>
   </si>
   <si>
     <t>1_500|2_1000</t>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="viplevel" sheetId="1" r:id="rId1"/>
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="107">
   <si>
     <t>id</t>
   </si>
@@ -267,190 +267,184 @@
     <t>privilegedFunctions</t>
   </si>
   <si>
-    <t>4320_164800</t>
-  </si>
-  <si>
-    <t>1990000_9800000</t>
-  </si>
-  <si>
-    <t>1990000_140000</t>
-  </si>
-  <si>
-    <t>1990000_4200000</t>
-  </si>
-  <si>
-    <t>1990000_1540000</t>
-  </si>
-  <si>
-    <t>1022502_1|1980000_10</t>
-  </si>
-  <si>
-    <t>4320_928500</t>
-  </si>
-  <si>
-    <t>1990000_19600000</t>
-  </si>
-  <si>
-    <t>1990000_280000</t>
-  </si>
-  <si>
-    <t>1990000_8400000</t>
-  </si>
-  <si>
-    <t>1990000_3080000</t>
-  </si>
-  <si>
-    <t>1022501_5|1980000_20</t>
-  </si>
-  <si>
-    <t>4320_5200000</t>
-  </si>
-  <si>
-    <t>1990000_29400000</t>
-  </si>
-  <si>
-    <t>1990000_420000</t>
-  </si>
-  <si>
-    <t>1990000_12600000</t>
-  </si>
-  <si>
-    <t>1990000_4620000</t>
-  </si>
-  <si>
-    <t>1010301_5|1980000_30</t>
-  </si>
-  <si>
-    <t>4320_40000000</t>
-  </si>
-  <si>
-    <t>1990000_49000000</t>
-  </si>
-  <si>
-    <t>1990000_700000</t>
-  </si>
-  <si>
-    <t>1990000_21000000</t>
-  </si>
-  <si>
-    <t>1990000_7700000</t>
-  </si>
-  <si>
-    <t>1031600_1|1022503_5|1980000_50</t>
-  </si>
-  <si>
-    <t>1_100</t>
+    <t>4320_1098680</t>
+  </si>
+  <si>
+    <t>1990000_300</t>
+  </si>
+  <si>
+    <t>1990000_10</t>
+  </si>
+  <si>
+    <t>1990000_200</t>
+  </si>
+  <si>
+    <t>1990000_50</t>
+  </si>
+  <si>
+    <t>4320_12380000</t>
+  </si>
+  <si>
+    <t>1990000_2900</t>
+  </si>
+  <si>
+    <t>1990000_0</t>
+  </si>
+  <si>
+    <t>1990000_1900</t>
+  </si>
+  <si>
+    <t>1990000_400</t>
+  </si>
+  <si>
+    <t>1020001_1</t>
+  </si>
+  <si>
+    <t>4320_104648340</t>
+  </si>
+  <si>
+    <t>1990000_28200</t>
+  </si>
+  <si>
+    <t>1990000_900</t>
+  </si>
+  <si>
+    <t>1990000_18800</t>
+  </si>
+  <si>
+    <t>1990000_4700</t>
+  </si>
+  <si>
+    <t>4320_1069785000</t>
+  </si>
+  <si>
+    <t>1990000_200900</t>
+  </si>
+  <si>
+    <t>1990000_6600</t>
+  </si>
+  <si>
+    <t>1990000_133900</t>
+  </si>
+  <si>
+    <t>1990000_33400</t>
+  </si>
+  <si>
+    <t>1031600_1|1020001_1</t>
+  </si>
+  <si>
+    <t>1_50</t>
   </si>
   <si>
     <t>-1_0</t>
   </si>
   <si>
-    <t>1990000_147000000</t>
-  </si>
-  <si>
-    <t>1990000_2100000</t>
-  </si>
-  <si>
-    <t>1990000_63000000</t>
-  </si>
-  <si>
-    <t>1990000_23100000</t>
-  </si>
-  <si>
-    <t>1031801_1|1022502_5|1980000_100</t>
+    <t>1990000_1668800</t>
+  </si>
+  <si>
+    <t>1990000_55600</t>
+  </si>
+  <si>
+    <t>1990000_1112500</t>
+  </si>
+  <si>
+    <t>1990000_278100</t>
+  </si>
+  <si>
+    <t>1031801_1|1020001_5</t>
+  </si>
+  <si>
+    <t>1_150</t>
+  </si>
+  <si>
+    <t>1990000_3030200</t>
+  </si>
+  <si>
+    <t>1990000_101000</t>
+  </si>
+  <si>
+    <t>1990000_2020100</t>
+  </si>
+  <si>
+    <t>1990000_505000</t>
+  </si>
+  <si>
+    <t>1032001_1|1020001_10</t>
   </si>
   <si>
     <t>1_200</t>
   </si>
   <si>
-    <t>1990000_196000000</t>
-  </si>
-  <si>
-    <t>1990000_2800000</t>
-  </si>
-  <si>
-    <t>1990000_84000000</t>
-  </si>
-  <si>
-    <t>1990000_30800000</t>
-  </si>
-  <si>
-    <t>1032001_1|1022503_10|1980000_1000</t>
-  </si>
-  <si>
-    <t>1_300</t>
-  </si>
-  <si>
-    <t>1990000_245000000</t>
-  </si>
-  <si>
-    <t>1990000_3500000</t>
-  </si>
-  <si>
-    <t>1990000_105000000</t>
-  </si>
-  <si>
-    <t>1990000_38500000</t>
-  </si>
-  <si>
-    <t>1031601_1|1032201_1|1022502_10|1980000_2000</t>
-  </si>
-  <si>
-    <t>1_400|2_250</t>
-  </si>
-  <si>
-    <t>1990000_490000000</t>
-  </si>
-  <si>
-    <t>1990000_7000000</t>
-  </si>
-  <si>
-    <t>1990000_210000000</t>
-  </si>
-  <si>
-    <t>1990000_77000000</t>
-  </si>
-  <si>
-    <t>1031802_1|1022503_20|1980000_3000</t>
-  </si>
-  <si>
-    <t>1_500|2_500</t>
-  </si>
-  <si>
-    <t>1990000_980000000</t>
-  </si>
-  <si>
-    <t>1990000_14000000</t>
-  </si>
-  <si>
-    <t>1990000_420000000</t>
-  </si>
-  <si>
-    <t>1990000_154000000</t>
-  </si>
-  <si>
-    <t>1032002_1|1022502_20|1980000_5000</t>
-  </si>
-  <si>
-    <t>1_500|2_750</t>
-  </si>
-  <si>
-    <t>1990000_2450000000</t>
-  </si>
-  <si>
-    <t>1990000_35000000</t>
-  </si>
-  <si>
-    <t>1990000_1050000000</t>
-  </si>
-  <si>
-    <t>1990000_385000000</t>
-  </si>
-  <si>
-    <t>1031602_1|1032202_1|1022503_20|1980000_10000</t>
-  </si>
-  <si>
-    <t>1_500|2_1000</t>
+    <t>1990000_8574300</t>
+  </si>
+  <si>
+    <t>1990000_285800</t>
+  </si>
+  <si>
+    <t>1990000_5716200</t>
+  </si>
+  <si>
+    <t>1990000_1429000</t>
+  </si>
+  <si>
+    <t>1031601_1|1020001_10</t>
+  </si>
+  <si>
+    <t>1_250|2_50</t>
+  </si>
+  <si>
+    <t>1990000_39354800</t>
+  </si>
+  <si>
+    <t>1990000_1311800</t>
+  </si>
+  <si>
+    <t>1990000_26236500</t>
+  </si>
+  <si>
+    <t>1990000_6559100</t>
+  </si>
+  <si>
+    <t>1031802_1|1020001_20</t>
+  </si>
+  <si>
+    <t>1_300|2_100</t>
+  </si>
+  <si>
+    <t>1990000_126373000</t>
+  </si>
+  <si>
+    <t>1990000_4212400</t>
+  </si>
+  <si>
+    <t>1990000_84248600</t>
+  </si>
+  <si>
+    <t>1990000_21062100</t>
+  </si>
+  <si>
+    <t>1032002_1|1020001_20</t>
+  </si>
+  <si>
+    <t>1_400|2_200</t>
+  </si>
+  <si>
+    <t>1990000_630179700</t>
+  </si>
+  <si>
+    <t>1990000_21005900</t>
+  </si>
+  <si>
+    <t>1990000_420119800</t>
+  </si>
+  <si>
+    <t>1990000_105029900</t>
+  </si>
+  <si>
+    <t>1031602_1|1020001_20</t>
+  </si>
+  <si>
+    <t>1_500|2_300</t>
   </si>
   <si>
     <t>刮刮卡</t>
@@ -1154,7 +1148,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1189,6 +1183,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -3251,7 +3248,8 @@
     <col min="1" max="1" width="10.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
     <col min="3" max="3" width="27.35" style="1" customWidth="1"/>
-    <col min="4" max="5" width="14.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.375" style="1" customWidth="1"/>
     <col min="7" max="8" width="21.25" style="1" customWidth="1"/>
     <col min="9" max="12" width="20.375" style="1" customWidth="1"/>
@@ -3420,7 +3418,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="10">
-        <v>1648000</v>
+        <v>5493400</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="1">
@@ -3446,9 +3444,6 @@
       </c>
       <c r="L5" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="O5" s="7"/>
       <c r="P5"/>
@@ -3470,14 +3465,14 @@
         <v>1</v>
       </c>
       <c r="C6" s="10">
-        <v>18570000</v>
+        <v>61900000</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="1">
         <v>19002</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" s="1">
         <v>10000</v>
@@ -3486,19 +3481,19 @@
         <v>10000</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6"/>
@@ -3520,14 +3515,14 @@
         <v>2</v>
       </c>
       <c r="C7" s="10">
-        <v>156972500</v>
+        <v>523241700</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="1">
         <v>19003</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G7" s="1">
         <v>10000</v>
@@ -3536,19 +3531,19 @@
         <v>10000</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="M7" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="O7" s="7"/>
       <c r="P7"/>
@@ -3570,14 +3565,14 @@
         <v>3</v>
       </c>
       <c r="C8" s="10">
-        <v>1604677500</v>
+        <v>5348925000</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="1">
         <v>19004</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G8" s="1">
         <v>10000</v>
@@ -3586,22 +3581,22 @@
         <v>10000</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="O8" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>59</v>
       </c>
       <c r="P8"/>
       <c r="Q8"/>
@@ -3622,16 +3617,16 @@
         <v>4</v>
       </c>
       <c r="C9" s="10">
-        <v>60000000000</v>
-      </c>
-      <c r="D9" s="11">
-        <v>30000</v>
+        <v>12626100000</v>
+      </c>
+      <c r="D9" s="12">
+        <v>928290000</v>
       </c>
       <c r="E9" s="1">
         <v>19005</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>60</v>
+      <c r="F9" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -3640,22 +3635,22 @@
         <v>10000</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="O9" s="7" t="s">
         <v>64</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>66</v>
       </c>
       <c r="P9"/>
       <c r="Q9"/>
@@ -3676,16 +3671,16 @@
         <v>5</v>
       </c>
       <c r="C10" s="10">
-        <v>400000000000</v>
-      </c>
-      <c r="D10" s="11">
-        <v>200000</v>
+        <v>71453233400</v>
+      </c>
+      <c r="D10" s="12">
+        <v>4500950000</v>
       </c>
       <c r="E10" s="1">
         <v>19006</v>
       </c>
-      <c r="F10" s="14" t="s">
-        <v>60</v>
+      <c r="F10" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -3694,22 +3689,22 @@
         <v>10000</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="O10" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="P10"/>
       <c r="Q10"/>
@@ -3730,16 +3725,16 @@
         <v>6</v>
       </c>
       <c r="C11" s="10">
-        <v>2000000000000</v>
-      </c>
-      <c r="D11" s="11">
-        <v>1000000</v>
+        <v>364396583400</v>
+      </c>
+      <c r="D11" s="12">
+        <v>22607170000</v>
       </c>
       <c r="E11" s="1">
         <v>19007</v>
       </c>
-      <c r="F11" s="14" t="s">
-        <v>60</v>
+      <c r="F11" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -3748,22 +3743,22 @@
         <v>10000</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="O11" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>78</v>
       </c>
       <c r="P11"/>
       <c r="Q11"/>
@@ -3784,16 +3779,16 @@
         <v>7</v>
       </c>
       <c r="C12" s="10">
-        <v>8400000000000</v>
-      </c>
-      <c r="D12" s="11">
-        <v>4200000</v>
+        <v>1316385583400</v>
+      </c>
+      <c r="D12" s="12">
+        <v>87654660000</v>
       </c>
       <c r="E12" s="1">
         <v>19008</v>
       </c>
-      <c r="F12" s="14" t="s">
-        <v>60</v>
+      <c r="F12" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -3802,22 +3797,22 @@
         <v>10000</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="O12" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>84</v>
       </c>
       <c r="P12"/>
       <c r="Q12"/>
@@ -3838,16 +3833,16 @@
         <v>8</v>
       </c>
       <c r="C13" s="10">
-        <v>25600000000000</v>
-      </c>
-      <c r="D13" s="11">
-        <v>12800000</v>
+        <v>7001997166700</v>
+      </c>
+      <c r="D13" s="12">
+        <v>429867120000</v>
       </c>
       <c r="E13" s="1">
         <v>19009</v>
       </c>
-      <c r="F13" s="14" t="s">
-        <v>60</v>
+      <c r="F13" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -3856,22 +3851,22 @@
         <v>10000</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="O13" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>90</v>
       </c>
       <c r="P13"/>
       <c r="Q13"/>
@@ -3895,8 +3890,8 @@
       <c r="E14" s="1">
         <v>19010</v>
       </c>
-      <c r="F14" s="14" t="s">
-        <v>60</v>
+      <c r="F14" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -3905,22 +3900,22 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="O14" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>96</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
@@ -3934,20 +3929,20 @@
       <c r="Y14"/>
     </row>
     <row r="16" spans="1:25">
-      <c r="C16" s="13"/>
+      <c r="C16" s="14"/>
     </row>
     <row r="17" spans="3:7">
-      <c r="C17" s="13"/>
+      <c r="C17" s="14"/>
     </row>
     <row r="18" spans="3:7">
-      <c r="C18" s="13"/>
+      <c r="C18" s="14"/>
     </row>
     <row r="19" spans="3:7">
-      <c r="C19" s="13"/>
+      <c r="C19" s="14"/>
       <c r="D19" s="10"/>
     </row>
     <row r="20" spans="3:7">
-      <c r="C20" s="13"/>
+      <c r="C20" s="14"/>
       <c r="D20" s="10"/>
     </row>
     <row r="21" spans="3:7">
@@ -3988,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C4" s="1">
         <f>_xlfn.XLOOKUP(B4,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3998,7 +3993,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F4" s="1">
         <f>_xlfn.XLOOKUP(E4,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4016,7 +4011,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C5" s="1">
         <f>_xlfn.XLOOKUP(B5,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4026,7 +4021,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F5" s="1">
         <f>_xlfn.XLOOKUP(E5,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4044,7 +4039,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C6" s="1">
         <f>_xlfn.XLOOKUP(B6,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4054,7 +4049,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F6" s="1">
         <f>_xlfn.XLOOKUP(E6,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4072,7 +4067,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C7" s="1" t="e">
         <f>_xlfn.XLOOKUP(B7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4082,7 +4077,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F7" s="1">
         <f>_xlfn.XLOOKUP(E7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4092,7 +4087,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I7" s="1">
         <f>_xlfn.XLOOKUP(H7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4107,7 +4102,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C8" s="1" t="e">
         <f>_xlfn.XLOOKUP(B8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4117,7 +4112,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F8" s="1">
         <f>_xlfn.XLOOKUP(E8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4127,7 +4122,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I8" s="1">
         <f>_xlfn.XLOOKUP(H8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4142,7 +4137,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C9" s="1" t="e">
         <f>_xlfn.XLOOKUP(B9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4152,7 +4147,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F9" s="1">
         <f>_xlfn.XLOOKUP(E9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4162,7 +4157,7 @@
         <v>10</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I9" s="1">
         <f>_xlfn.XLOOKUP(H9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4177,7 +4172,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C10" s="1" t="e">
         <f>_xlfn.XLOOKUP(B10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4187,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F10" s="1">
         <f>_xlfn.XLOOKUP(E10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4197,7 +4192,7 @@
         <v>10</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I10" s="1">
         <f>_xlfn.XLOOKUP(H10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4212,7 +4207,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C11" s="1" t="e">
         <f>_xlfn.XLOOKUP(B11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4222,7 +4217,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F11" s="1">
         <f>_xlfn.XLOOKUP(E11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4232,7 +4227,7 @@
         <v>20</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I11" s="1">
         <f>_xlfn.XLOOKUP(H11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4247,7 +4242,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C12" s="1" t="e">
         <f>_xlfn.XLOOKUP(B12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4257,7 +4252,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F12" s="1">
         <f>_xlfn.XLOOKUP(E12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4267,7 +4262,7 @@
         <v>20</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I12" s="1">
         <f>_xlfn.XLOOKUP(H12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4282,7 +4277,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C13" s="1" t="e">
         <f>_xlfn.XLOOKUP(B13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4292,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F13" s="1">
         <f>_xlfn.XLOOKUP(E13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4302,7 +4297,7 @@
         <v>20</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I13" s="1">
         <f>_xlfn.XLOOKUP(H13,[1]Item!$D:$D,[1]Item!$A:$A)</f>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="viplevel" sheetId="1" r:id="rId1"/>
@@ -267,190 +267,190 @@
     <t>privilegedFunctions</t>
   </si>
   <si>
-    <t>4320_164800</t>
-  </si>
-  <si>
-    <t>1990000_9800000</t>
-  </si>
-  <si>
-    <t>1990000_140000</t>
-  </si>
-  <si>
-    <t>1990000_4200000</t>
-  </si>
-  <si>
-    <t>1990000_1540000</t>
-  </si>
-  <si>
-    <t>1022502_1|1980000_10</t>
-  </si>
-  <si>
-    <t>4320_928500</t>
-  </si>
-  <si>
-    <t>1990000_19600000</t>
-  </si>
-  <si>
-    <t>1990000_280000</t>
-  </si>
-  <si>
-    <t>1990000_8400000</t>
-  </si>
-  <si>
-    <t>1990000_3080000</t>
-  </si>
-  <si>
-    <t>1022501_5|1980000_20</t>
-  </si>
-  <si>
-    <t>4320_5200000</t>
-  </si>
-  <si>
-    <t>1990000_29400000</t>
-  </si>
-  <si>
-    <t>1990000_420000</t>
-  </si>
-  <si>
-    <t>1990000_12600000</t>
-  </si>
-  <si>
-    <t>1990000_4620000</t>
-  </si>
-  <si>
-    <t>1010301_5|1980000_30</t>
-  </si>
-  <si>
-    <t>4320_40000000</t>
-  </si>
-  <si>
-    <t>1990000_49000000</t>
-  </si>
-  <si>
-    <t>1990000_700000</t>
-  </si>
-  <si>
-    <t>1990000_21000000</t>
-  </si>
-  <si>
-    <t>1990000_7700000</t>
-  </si>
-  <si>
-    <t>1031600_1|1022503_5|1980000_50</t>
-  </si>
-  <si>
-    <t>1_100</t>
+    <t>4320_1098680</t>
+  </si>
+  <si>
+    <t>1990000_300</t>
+  </si>
+  <si>
+    <t>1990000_10</t>
+  </si>
+  <si>
+    <t>1990000_200</t>
+  </si>
+  <si>
+    <t>1990000_50</t>
+  </si>
+  <si>
+    <t>1022501_1</t>
+  </si>
+  <si>
+    <t>4320_12380000</t>
+  </si>
+  <si>
+    <t>1990000_2900</t>
+  </si>
+  <si>
+    <t>1990000_0</t>
+  </si>
+  <si>
+    <t>1990000_1900</t>
+  </si>
+  <si>
+    <t>1990000_400</t>
+  </si>
+  <si>
+    <t>1020001_1</t>
+  </si>
+  <si>
+    <t>4320_104648340</t>
+  </si>
+  <si>
+    <t>1990000_28200</t>
+  </si>
+  <si>
+    <t>1990000_900</t>
+  </si>
+  <si>
+    <t>1990000_18800</t>
+  </si>
+  <si>
+    <t>1990000_4700</t>
+  </si>
+  <si>
+    <t>1022501_3</t>
+  </si>
+  <si>
+    <t>4320_1069785000</t>
+  </si>
+  <si>
+    <t>1990000_200900</t>
+  </si>
+  <si>
+    <t>1990000_6600</t>
+  </si>
+  <si>
+    <t>1990000_133900</t>
+  </si>
+  <si>
+    <t>1990000_33400</t>
+  </si>
+  <si>
+    <t>1031600_1|1020001_2</t>
+  </si>
+  <si>
+    <t>1_50</t>
   </si>
   <si>
     <t>-1_0</t>
   </si>
   <si>
-    <t>1990000_147000000</t>
-  </si>
-  <si>
-    <t>1990000_2100000</t>
-  </si>
-  <si>
-    <t>1990000_63000000</t>
-  </si>
-  <si>
-    <t>1990000_23100000</t>
-  </si>
-  <si>
-    <t>1031801_1|1022502_5|1980000_100</t>
+    <t>1990000_1668800</t>
+  </si>
+  <si>
+    <t>1990000_55600</t>
+  </si>
+  <si>
+    <t>1990000_1112500</t>
+  </si>
+  <si>
+    <t>1990000_278100</t>
+  </si>
+  <si>
+    <t>1031801_1|1022501_10</t>
+  </si>
+  <si>
+    <t>1_150</t>
+  </si>
+  <si>
+    <t>1990000_3030200</t>
+  </si>
+  <si>
+    <t>1990000_101000</t>
+  </si>
+  <si>
+    <t>1990000_2020100</t>
+  </si>
+  <si>
+    <t>1990000_505000</t>
+  </si>
+  <si>
+    <t>1032001_1|1020001_10</t>
   </si>
   <si>
     <t>1_200</t>
   </si>
   <si>
-    <t>1990000_196000000</t>
-  </si>
-  <si>
-    <t>1990000_2800000</t>
-  </si>
-  <si>
-    <t>1990000_84000000</t>
-  </si>
-  <si>
-    <t>1990000_30800000</t>
-  </si>
-  <si>
-    <t>1032001_1|1022503_10|1980000_1000</t>
-  </si>
-  <si>
-    <t>1_300</t>
-  </si>
-  <si>
-    <t>1990000_245000000</t>
-  </si>
-  <si>
-    <t>1990000_3500000</t>
-  </si>
-  <si>
-    <t>1990000_105000000</t>
-  </si>
-  <si>
-    <t>1990000_38500000</t>
-  </si>
-  <si>
-    <t>1031601_1|1032201_1|1022502_10|1980000_2000</t>
-  </si>
-  <si>
-    <t>1_400|2_250</t>
-  </si>
-  <si>
-    <t>1990000_490000000</t>
-  </si>
-  <si>
-    <t>1990000_7000000</t>
-  </si>
-  <si>
-    <t>1990000_210000000</t>
-  </si>
-  <si>
-    <t>1990000_77000000</t>
-  </si>
-  <si>
-    <t>1031802_1|1022503_20|1980000_3000</t>
-  </si>
-  <si>
-    <t>1_500|2_500</t>
-  </si>
-  <si>
-    <t>1990000_980000000</t>
-  </si>
-  <si>
-    <t>1990000_14000000</t>
-  </si>
-  <si>
-    <t>1990000_420000000</t>
-  </si>
-  <si>
-    <t>1990000_154000000</t>
-  </si>
-  <si>
-    <t>1032002_1|1022502_20|1980000_5000</t>
-  </si>
-  <si>
-    <t>1_500|2_750</t>
-  </si>
-  <si>
-    <t>1990000_2450000000</t>
-  </si>
-  <si>
-    <t>1990000_35000000</t>
-  </si>
-  <si>
-    <t>1990000_1050000000</t>
-  </si>
-  <si>
-    <t>1990000_385000000</t>
-  </si>
-  <si>
-    <t>1031602_1|1032202_1|1022503_20|1980000_10000</t>
-  </si>
-  <si>
-    <t>1_500|2_1000</t>
+    <t>1990000_8574300</t>
+  </si>
+  <si>
+    <t>1990000_285800</t>
+  </si>
+  <si>
+    <t>1990000_5716200</t>
+  </si>
+  <si>
+    <t>1990000_1429000</t>
+  </si>
+  <si>
+    <t>1031601_1|1022501_30</t>
+  </si>
+  <si>
+    <t>1_250|2_50</t>
+  </si>
+  <si>
+    <t>1990000_39354800</t>
+  </si>
+  <si>
+    <t>1990000_1311800</t>
+  </si>
+  <si>
+    <t>1990000_26236500</t>
+  </si>
+  <si>
+    <t>1990000_6559100</t>
+  </si>
+  <si>
+    <t>1031802_1|1020001_20</t>
+  </si>
+  <si>
+    <t>1_300|2_100</t>
+  </si>
+  <si>
+    <t>1990000_126373000</t>
+  </si>
+  <si>
+    <t>1990000_4212400</t>
+  </si>
+  <si>
+    <t>1990000_84248600</t>
+  </si>
+  <si>
+    <t>1990000_21062100</t>
+  </si>
+  <si>
+    <t>1032002_1|1022501_30</t>
+  </si>
+  <si>
+    <t>1_400|2_200</t>
+  </si>
+  <si>
+    <t>1990000_630179700</t>
+  </si>
+  <si>
+    <t>1990000_21005900</t>
+  </si>
+  <si>
+    <t>1990000_420119800</t>
+  </si>
+  <si>
+    <t>1990000_105029900</t>
+  </si>
+  <si>
+    <t>1031602_1|1020001_20</t>
+  </si>
+  <si>
+    <t>1_500|2_300</t>
   </si>
   <si>
     <t>刮刮卡</t>
@@ -1154,7 +1154,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1189,6 +1189,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -3251,7 +3254,8 @@
     <col min="1" max="1" width="10.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
     <col min="3" max="3" width="27.35" style="1" customWidth="1"/>
-    <col min="4" max="5" width="14.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.375" style="1" customWidth="1"/>
     <col min="7" max="8" width="21.25" style="1" customWidth="1"/>
     <col min="9" max="12" width="20.375" style="1" customWidth="1"/>
@@ -3420,7 +3424,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="10">
-        <v>1648000</v>
+        <v>5493400</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="1">
@@ -3470,7 +3474,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="10">
-        <v>18570000</v>
+        <v>61900000</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="1">
@@ -3520,7 +3524,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="10">
-        <v>156972500</v>
+        <v>523241700</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="1">
@@ -3570,7 +3574,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="10">
-        <v>1604677500</v>
+        <v>5348925000</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="1">
@@ -3622,15 +3626,15 @@
         <v>4</v>
       </c>
       <c r="C9" s="10">
-        <v>60000000000</v>
-      </c>
-      <c r="D9" s="11">
-        <v>30000</v>
+        <v>12626100000</v>
+      </c>
+      <c r="D9" s="12">
+        <v>928290000</v>
       </c>
       <c r="E9" s="1">
         <v>19005</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G9" s="1">
@@ -3676,15 +3680,15 @@
         <v>5</v>
       </c>
       <c r="C10" s="10">
-        <v>400000000000</v>
-      </c>
-      <c r="D10" s="11">
-        <v>200000</v>
+        <v>71453233400</v>
+      </c>
+      <c r="D10" s="12">
+        <v>4500950000</v>
       </c>
       <c r="E10" s="1">
         <v>19006</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G10" s="1">
@@ -3730,15 +3734,15 @@
         <v>6</v>
       </c>
       <c r="C11" s="10">
-        <v>2000000000000</v>
-      </c>
-      <c r="D11" s="11">
-        <v>1000000</v>
+        <v>364396583400</v>
+      </c>
+      <c r="D11" s="12">
+        <v>22607170000</v>
       </c>
       <c r="E11" s="1">
         <v>19007</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G11" s="1">
@@ -3784,15 +3788,15 @@
         <v>7</v>
       </c>
       <c r="C12" s="10">
-        <v>8400000000000</v>
-      </c>
-      <c r="D12" s="11">
-        <v>4200000</v>
+        <v>1316385583400</v>
+      </c>
+      <c r="D12" s="12">
+        <v>87654660000</v>
       </c>
       <c r="E12" s="1">
         <v>19008</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G12" s="1">
@@ -3838,15 +3842,15 @@
         <v>8</v>
       </c>
       <c r="C13" s="10">
-        <v>25600000000000</v>
-      </c>
-      <c r="D13" s="11">
-        <v>12800000</v>
+        <v>7001997166700</v>
+      </c>
+      <c r="D13" s="12">
+        <v>429867120000</v>
       </c>
       <c r="E13" s="1">
         <v>19009</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G13" s="1">
@@ -3895,7 +3899,7 @@
       <c r="E14" s="1">
         <v>19010</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G14" s="1">
@@ -3934,20 +3938,20 @@
       <c r="Y14"/>
     </row>
     <row r="16" spans="1:25">
-      <c r="C16" s="13"/>
+      <c r="C16" s="14"/>
     </row>
     <row r="17" spans="3:7">
-      <c r="C17" s="13"/>
+      <c r="C17" s="14"/>
     </row>
     <row r="18" spans="3:7">
-      <c r="C18" s="13"/>
+      <c r="C18" s="14"/>
     </row>
     <row r="19" spans="3:7">
-      <c r="C19" s="13"/>
+      <c r="C19" s="14"/>
       <c r="D19" s="10"/>
     </row>
     <row r="20" spans="3:7">
-      <c r="C20" s="13"/>
+      <c r="C20" s="14"/>
       <c r="D20" s="10"/>
     </row>
     <row r="21" spans="3:7">

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="108">
   <si>
     <t>id</t>
   </si>
@@ -282,6 +282,9 @@
     <t>1990000_50</t>
   </si>
   <si>
+    <t>1022501_1</t>
+  </si>
+  <si>
     <t>4320_12380000</t>
   </si>
   <si>
@@ -315,6 +318,9 @@
     <t>1990000_4700</t>
   </si>
   <si>
+    <t>1022501_3</t>
+  </si>
+  <si>
     <t>4320_1069785000</t>
   </si>
   <si>
@@ -330,10 +336,7 @@
     <t>1990000_33400</t>
   </si>
   <si>
-    <t>1031600_1|1020001_1</t>
-  </si>
-  <si>
-    <t>1_50</t>
+    <t>1031600_1|1020001_2</t>
   </si>
   <si>
     <t>-1_0</t>
@@ -351,7 +354,7 @@
     <t>1990000_278100</t>
   </si>
   <si>
-    <t>1031801_1|1020001_5</t>
+    <t>1031801_1|1022501_10</t>
   </si>
   <si>
     <t>1_150</t>
@@ -387,7 +390,7 @@
     <t>1990000_1429000</t>
   </si>
   <si>
-    <t>1031601_1|1020001_10</t>
+    <t>1031601_1|1022501_30</t>
   </si>
   <si>
     <t>1_250|2_50</t>
@@ -423,7 +426,7 @@
     <t>1990000_21062100</t>
   </si>
   <si>
-    <t>1032002_1|1020001_20</t>
+    <t>1032002_1|1022501_30</t>
   </si>
   <si>
     <t>1_400|2_200</t>
@@ -3445,6 +3448,9 @@
       <c r="L5" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="M5" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="O5" s="7"/>
       <c r="P5"/>
       <c r="Q5"/>
@@ -3472,7 +3478,7 @@
         <v>19002</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6" s="1">
         <v>10000</v>
@@ -3481,19 +3487,19 @@
         <v>10000</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6"/>
@@ -3522,7 +3528,7 @@
         <v>19003</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G7" s="1">
         <v>10000</v>
@@ -3531,19 +3537,19 @@
         <v>10000</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="O7" s="7"/>
       <c r="P7"/>
@@ -3572,7 +3578,7 @@
         <v>19004</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G8" s="1">
         <v>10000</v>
@@ -3581,23 +3587,21 @@
         <v>10000</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>57</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="O8" s="7"/>
       <c r="P8"/>
       <c r="Q8"/>
       <c r="R8"/>
@@ -3626,7 +3630,7 @@
         <v>19005</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -3635,22 +3639,22 @@
         <v>10000</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P9"/>
       <c r="Q9"/>
@@ -3680,7 +3684,7 @@
         <v>19006</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -3689,22 +3693,22 @@
         <v>10000</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P10"/>
       <c r="Q10"/>
@@ -3734,7 +3738,7 @@
         <v>19007</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -3743,22 +3747,22 @@
         <v>10000</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P11"/>
       <c r="Q11"/>
@@ -3788,7 +3792,7 @@
         <v>19008</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -3797,22 +3801,22 @@
         <v>10000</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P12"/>
       <c r="Q12"/>
@@ -3842,7 +3846,7 @@
         <v>19009</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -3851,22 +3855,22 @@
         <v>10000</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P13"/>
       <c r="Q13"/>
@@ -3891,7 +3895,7 @@
         <v>19010</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -3900,22 +3904,22 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
@@ -3983,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4" s="1">
         <f>_xlfn.XLOOKUP(B4,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3993,7 +3997,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F4" s="1">
         <f>_xlfn.XLOOKUP(E4,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4011,7 +4015,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="1">
         <f>_xlfn.XLOOKUP(B5,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4021,7 +4025,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F5" s="1">
         <f>_xlfn.XLOOKUP(E5,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4039,7 +4043,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="1">
         <f>_xlfn.XLOOKUP(B6,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4049,7 +4053,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F6" s="1">
         <f>_xlfn.XLOOKUP(E6,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4067,7 +4071,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="1" t="e">
         <f>_xlfn.XLOOKUP(B7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4077,7 +4081,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" s="1">
         <f>_xlfn.XLOOKUP(E7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4087,7 +4091,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I7" s="1">
         <f>_xlfn.XLOOKUP(H7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4102,7 +4106,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="1" t="e">
         <f>_xlfn.XLOOKUP(B8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4112,7 +4116,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F8" s="1">
         <f>_xlfn.XLOOKUP(E8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4122,7 +4126,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I8" s="1">
         <f>_xlfn.XLOOKUP(H8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4137,7 +4141,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C9" s="1" t="e">
         <f>_xlfn.XLOOKUP(B9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4147,7 +4151,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F9" s="1">
         <f>_xlfn.XLOOKUP(E9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4157,7 +4161,7 @@
         <v>10</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I9" s="1">
         <f>_xlfn.XLOOKUP(H9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4172,7 +4176,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="1" t="e">
         <f>_xlfn.XLOOKUP(B10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4182,7 +4186,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F10" s="1">
         <f>_xlfn.XLOOKUP(E10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4192,7 +4196,7 @@
         <v>10</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I10" s="1">
         <f>_xlfn.XLOOKUP(H10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4207,7 +4211,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" s="1" t="e">
         <f>_xlfn.XLOOKUP(B11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4217,7 +4221,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F11" s="1">
         <f>_xlfn.XLOOKUP(E11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4227,7 +4231,7 @@
         <v>20</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I11" s="1">
         <f>_xlfn.XLOOKUP(H11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4242,7 +4246,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C12" s="1" t="e">
         <f>_xlfn.XLOOKUP(B12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4252,7 +4256,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F12" s="1">
         <f>_xlfn.XLOOKUP(E12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4262,7 +4266,7 @@
         <v>20</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I12" s="1">
         <f>_xlfn.XLOOKUP(H12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4277,7 +4281,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" s="1" t="e">
         <f>_xlfn.XLOOKUP(B13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4287,7 +4291,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F13" s="1">
         <f>_xlfn.XLOOKUP(E13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4297,7 +4301,7 @@
         <v>20</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I13" s="1">
         <f>_xlfn.XLOOKUP(H13,[1]Item!$D:$D,[1]Item!$A:$A)</f>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -291,7 +291,7 @@
     <t>1990000_2900</t>
   </si>
   <si>
-    <t>1990000_0</t>
+    <t>1990000_90</t>
   </si>
   <si>
     <t>1990000_1900</t>
@@ -390,7 +390,7 @@
     <t>1990000_1429000</t>
   </si>
   <si>
-    <t>1031601_1|1022501_30</t>
+    <t>1031601_1|1032201_1|1022501_30</t>
   </si>
   <si>
     <t>1_250|2_50</t>
@@ -444,7 +444,7 @@
     <t>1990000_105029900</t>
   </si>
   <si>
-    <t>1031602_1|1020001_20</t>
+    <t>1031602_1|1032202_1|1020001_20</t>
   </si>
   <si>
     <t>1_500|2_300</t>
@@ -3245,7 +3245,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.625" style="1" customWidth="1"/>
@@ -3259,12 +3259,10 @@
     <col min="13" max="13" width="37.375" style="1" customWidth="1"/>
     <col min="14" max="14" width="21.7666666666667" style="1" customWidth="1"/>
     <col min="15" max="15" width="20.375" style="1" customWidth="1"/>
-    <col min="16" max="17" width="9" style="1"/>
-    <col min="18" max="18" width="9.25" style="1"/>
-    <col min="19" max="16384" width="9" style="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3311,7 +3309,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:18">
       <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
@@ -3358,7 +3356,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:18">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -3405,7 +3403,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:18">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="6"/>
@@ -3413,7 +3411,7 @@
       <c r="E4" s="6"/>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:18">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3455,15 +3453,8 @@
       <c r="P5"/>
       <c r="Q5"/>
       <c r="R5"/>
-      <c r="S5"/>
-      <c r="T5"/>
-      <c r="U5"/>
-      <c r="V5"/>
-      <c r="W5"/>
-      <c r="X5"/>
-      <c r="Y5"/>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:18">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -3505,15 +3496,8 @@
       <c r="P6"/>
       <c r="Q6"/>
       <c r="R6"/>
-      <c r="S6"/>
-      <c r="T6"/>
-      <c r="U6"/>
-      <c r="V6"/>
-      <c r="W6"/>
-      <c r="X6"/>
-      <c r="Y6"/>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:18">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -3555,15 +3539,8 @@
       <c r="P7"/>
       <c r="Q7"/>
       <c r="R7"/>
-      <c r="S7"/>
-      <c r="T7"/>
-      <c r="U7"/>
-      <c r="V7"/>
-      <c r="W7"/>
-      <c r="X7"/>
-      <c r="Y7"/>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:18">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -3605,15 +3582,8 @@
       <c r="P8"/>
       <c r="Q8"/>
       <c r="R8"/>
-      <c r="S8"/>
-      <c r="T8"/>
-      <c r="U8"/>
-      <c r="V8"/>
-      <c r="W8"/>
-      <c r="X8"/>
-      <c r="Y8"/>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:18">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -3659,15 +3629,8 @@
       <c r="P9"/>
       <c r="Q9"/>
       <c r="R9"/>
-      <c r="S9"/>
-      <c r="T9"/>
-      <c r="U9"/>
-      <c r="V9"/>
-      <c r="W9"/>
-      <c r="X9"/>
-      <c r="Y9"/>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:18">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -3713,15 +3676,8 @@
       <c r="P10"/>
       <c r="Q10"/>
       <c r="R10"/>
-      <c r="S10"/>
-      <c r="T10"/>
-      <c r="U10"/>
-      <c r="V10"/>
-      <c r="W10"/>
-      <c r="X10"/>
-      <c r="Y10"/>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:18">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -3767,15 +3723,8 @@
       <c r="P11"/>
       <c r="Q11"/>
       <c r="R11"/>
-      <c r="S11"/>
-      <c r="T11"/>
-      <c r="U11"/>
-      <c r="V11"/>
-      <c r="W11"/>
-      <c r="X11"/>
-      <c r="Y11"/>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:18">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -3821,15 +3770,8 @@
       <c r="P12"/>
       <c r="Q12"/>
       <c r="R12"/>
-      <c r="S12"/>
-      <c r="T12"/>
-      <c r="U12"/>
-      <c r="V12"/>
-      <c r="W12"/>
-      <c r="X12"/>
-      <c r="Y12"/>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:18">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -3875,15 +3817,8 @@
       <c r="P13"/>
       <c r="Q13"/>
       <c r="R13"/>
-      <c r="S13"/>
-      <c r="T13"/>
-      <c r="U13"/>
-      <c r="V13"/>
-      <c r="W13"/>
-      <c r="X13"/>
-      <c r="Y13"/>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:18">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -3924,15 +3859,8 @@
       <c r="P14"/>
       <c r="Q14"/>
       <c r="R14"/>
-      <c r="S14"/>
-      <c r="T14"/>
-      <c r="U14"/>
-      <c r="V14"/>
-      <c r="W14"/>
-      <c r="X14"/>
-      <c r="Y14"/>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:18">
       <c r="C16" s="14"/>
     </row>
     <row r="17" spans="3:7">

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -663,12 +663,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3591,7 +3591,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="10">
-        <v>12626100000</v>
+        <v>9282900000</v>
       </c>
       <c r="D9" s="12">
         <v>928290000</v>
@@ -3638,7 +3638,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="10">
-        <v>71453233400</v>
+        <v>45009500000</v>
       </c>
       <c r="D10" s="12">
         <v>4500950000</v>
@@ -3685,7 +3685,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="10">
-        <v>364396583400</v>
+        <v>226071700000</v>
       </c>
       <c r="D11" s="12">
         <v>22607170000</v>
@@ -3732,7 +3732,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="10">
-        <v>1316385583400</v>
+        <v>876546600000</v>
       </c>
       <c r="D12" s="12">
         <v>87654660000</v>
@@ -3779,7 +3779,7 @@
         <v>8</v>
       </c>
       <c r="C13" s="10">
-        <v>7001997166700</v>
+        <v>4298671200000</v>
       </c>
       <c r="D13" s="12">
         <v>429867120000</v>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -663,12 +663,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3591,7 +3591,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="10">
-        <v>9282900000</v>
+        <v>12626100000</v>
       </c>
       <c r="D9" s="12">
         <v>928290000</v>
@@ -3638,7 +3638,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="10">
-        <v>45009500000</v>
+        <v>71453233400</v>
       </c>
       <c r="D10" s="12">
         <v>4500950000</v>
@@ -3685,7 +3685,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="10">
-        <v>226071700000</v>
+        <v>364396583400</v>
       </c>
       <c r="D11" s="12">
         <v>22607170000</v>
@@ -3732,7 +3732,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="10">
-        <v>876546600000</v>
+        <v>1316385583400</v>
       </c>
       <c r="D12" s="12">
         <v>87654660000</v>
@@ -3779,7 +3779,7 @@
         <v>8</v>
       </c>
       <c r="C13" s="10">
-        <v>4298671200000</v>
+        <v>7001997166700</v>
       </c>
       <c r="D13" s="12">
         <v>429867120000</v>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="104">
   <si>
     <t>id</t>
   </si>
@@ -270,184 +270,172 @@
     <t>4320_1098680</t>
   </si>
   <si>
-    <t>1990000_300</t>
-  </si>
-  <si>
-    <t>1990000_10</t>
-  </si>
-  <si>
-    <t>1990000_200</t>
-  </si>
-  <si>
-    <t>1990000_50</t>
-  </si>
-  <si>
     <t>1022501_1</t>
   </si>
   <si>
     <t>4320_12380000</t>
   </si>
   <si>
-    <t>1990000_2900</t>
-  </si>
-  <si>
-    <t>1990000_90</t>
-  </si>
-  <si>
-    <t>1990000_1900</t>
-  </si>
-  <si>
-    <t>1990000_400</t>
+    <t>1990000_8888</t>
+  </si>
+  <si>
+    <t>1990000_3888</t>
+  </si>
+  <si>
+    <t>1990000_388</t>
   </si>
   <si>
     <t>1020001_1</t>
   </si>
   <si>
+    <t>1_500</t>
+  </si>
+  <si>
     <t>4320_104648340</t>
   </si>
   <si>
-    <t>1990000_28200</t>
-  </si>
-  <si>
-    <t>1990000_900</t>
-  </si>
-  <si>
-    <t>1990000_18800</t>
-  </si>
-  <si>
-    <t>1990000_4700</t>
+    <t>1990000_28888</t>
+  </si>
+  <si>
+    <t>1990000_1288</t>
+  </si>
+  <si>
+    <t>1990000_18888</t>
+  </si>
+  <si>
+    <t>1990000_4888</t>
   </si>
   <si>
     <t>1022501_3</t>
   </si>
   <si>
+    <t>1_1000</t>
+  </si>
+  <si>
     <t>4320_1069785000</t>
   </si>
   <si>
-    <t>1990000_200900</t>
-  </si>
-  <si>
-    <t>1990000_6600</t>
-  </si>
-  <si>
-    <t>1990000_133900</t>
-  </si>
-  <si>
-    <t>1990000_33400</t>
+    <t>1990000_188888</t>
+  </si>
+  <si>
+    <t>1990000_6888</t>
+  </si>
+  <si>
+    <t>1990000_138888</t>
+  </si>
+  <si>
+    <t>1990000_32888</t>
   </si>
   <si>
     <t>1031600_1|1020001_2</t>
   </si>
   <si>
+    <t>1_1500</t>
+  </si>
+  <si>
     <t>-1_0</t>
   </si>
   <si>
-    <t>1990000_1668800</t>
-  </si>
-  <si>
-    <t>1990000_55600</t>
-  </si>
-  <si>
-    <t>1990000_1112500</t>
-  </si>
-  <si>
-    <t>1990000_278100</t>
+    <t>1990000_1668888</t>
+  </si>
+  <si>
+    <t>1990000_58888</t>
+  </si>
+  <si>
+    <t>1990000_1098888</t>
+  </si>
+  <si>
+    <t>1990000_268888</t>
   </si>
   <si>
     <t>1031801_1|1022501_10</t>
   </si>
   <si>
-    <t>1_150</t>
-  </si>
-  <si>
-    <t>1990000_3030200</t>
-  </si>
-  <si>
-    <t>1990000_101000</t>
-  </si>
-  <si>
-    <t>1990000_2020100</t>
-  </si>
-  <si>
-    <t>1990000_505000</t>
+    <t>1_2000</t>
+  </si>
+  <si>
+    <t>1990000_3028888</t>
+  </si>
+  <si>
+    <t>1990000_109888</t>
+  </si>
+  <si>
+    <t>1990000_2019888</t>
+  </si>
+  <si>
+    <t>1990000_509888</t>
   </si>
   <si>
     <t>1032001_1|1020001_10</t>
   </si>
   <si>
-    <t>1_200</t>
-  </si>
-  <si>
-    <t>1990000_8574300</t>
-  </si>
-  <si>
-    <t>1990000_285800</t>
-  </si>
-  <si>
-    <t>1990000_5716200</t>
-  </si>
-  <si>
-    <t>1990000_1429000</t>
+    <t>1_2500</t>
+  </si>
+  <si>
+    <t>1990000_8568888</t>
+  </si>
+  <si>
+    <t>1990000_285888</t>
+  </si>
+  <si>
+    <t>1990000_5718888</t>
+  </si>
+  <si>
+    <t>1990000_1398888</t>
   </si>
   <si>
     <t>1031601_1|1032201_1|1022501_30</t>
   </si>
   <si>
-    <t>1_250|2_50</t>
-  </si>
-  <si>
-    <t>1990000_39354800</t>
-  </si>
-  <si>
-    <t>1990000_1311800</t>
-  </si>
-  <si>
-    <t>1990000_26236500</t>
-  </si>
-  <si>
-    <t>1990000_6559100</t>
+    <t>1_3000|2_50</t>
+  </si>
+  <si>
+    <t>1990000_39298888</t>
+  </si>
+  <si>
+    <t>1990000_26219888</t>
+  </si>
+  <si>
+    <t>1990000_6568888</t>
   </si>
   <si>
     <t>1031802_1|1020001_20</t>
   </si>
   <si>
-    <t>1_300|2_100</t>
-  </si>
-  <si>
-    <t>1990000_126373000</t>
-  </si>
-  <si>
-    <t>1990000_4212400</t>
-  </si>
-  <si>
-    <t>1990000_84248600</t>
-  </si>
-  <si>
-    <t>1990000_21062100</t>
+    <t>1_3500|2_100</t>
+  </si>
+  <si>
+    <t>1990000_126298888</t>
+  </si>
+  <si>
+    <t>1990000_3999888</t>
+  </si>
+  <si>
+    <t>1990000_83988888</t>
+  </si>
+  <si>
+    <t>1990000_20988888</t>
   </si>
   <si>
     <t>1032002_1|1022501_30</t>
   </si>
   <si>
-    <t>1_400|2_200</t>
-  </si>
-  <si>
-    <t>1990000_630179700</t>
-  </si>
-  <si>
-    <t>1990000_21005900</t>
-  </si>
-  <si>
-    <t>1990000_420119800</t>
-  </si>
-  <si>
-    <t>1990000_105029900</t>
+    <t>1_4000|2_200</t>
+  </si>
+  <si>
+    <t>1990000_629888888</t>
+  </si>
+  <si>
+    <t>1990000_419888888</t>
+  </si>
+  <si>
+    <t>1990000_103988888</t>
   </si>
   <si>
     <t>1031602_1|1032202_1|1020001_20</t>
   </si>
   <si>
-    <t>1_500|2_300</t>
+    <t>1_4500|2_300</t>
   </si>
   <si>
     <t>刮刮卡</t>
@@ -3250,11 +3238,11 @@
   <cols>
     <col min="1" max="1" width="10.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.35" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.375" style="1" customWidth="1"/>
-    <col min="7" max="8" width="21.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.35" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="17.75" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="14.875" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="17.375" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="21.25" style="1" hidden="1" customWidth="1"/>
     <col min="9" max="12" width="20.375" style="1" customWidth="1"/>
     <col min="13" max="13" width="37.375" style="1" customWidth="1"/>
     <col min="14" max="14" width="21.7666666666667" style="1" customWidth="1"/>
@@ -3434,20 +3422,8 @@
       <c r="H5" s="1">
         <v>10000</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="O5" s="7"/>
       <c r="P5"/>
@@ -3469,7 +3445,7 @@
         <v>19002</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G6" s="1">
         <v>10000</v>
@@ -3478,21 +3454,21 @@
         <v>10000</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O6" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="O6" s="7"/>
       <c r="P6"/>
       <c r="Q6"/>
       <c r="R6"/>
@@ -3512,7 +3488,7 @@
         <v>19003</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G7" s="1">
         <v>10000</v>
@@ -3521,21 +3497,23 @@
         <v>10000</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="O7" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="O7" s="7"/>
       <c r="P7"/>
       <c r="Q7"/>
       <c r="R7"/>
@@ -3555,7 +3533,7 @@
         <v>19004</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G8" s="1">
         <v>10000</v>
@@ -3564,21 +3542,23 @@
         <v>10000</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="O8" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="O8" s="7"/>
       <c r="P8"/>
       <c r="Q8"/>
       <c r="R8"/>
@@ -3600,7 +3580,7 @@
         <v>19005</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -3609,22 +3589,22 @@
         <v>10000</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="O9" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>65</v>
       </c>
       <c r="P9"/>
       <c r="Q9"/>
@@ -3647,7 +3627,7 @@
         <v>19006</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -3656,22 +3636,22 @@
         <v>10000</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="O10" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>71</v>
       </c>
       <c r="P10"/>
       <c r="Q10"/>
@@ -3694,7 +3674,7 @@
         <v>19007</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -3703,22 +3683,22 @@
         <v>10000</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="O11" s="7" t="s">
         <v>75</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>77</v>
       </c>
       <c r="P11"/>
       <c r="Q11"/>
@@ -3741,7 +3721,7 @@
         <v>19008</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -3750,22 +3730,22 @@
         <v>10000</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="O12" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="P12"/>
       <c r="Q12"/>
@@ -3788,7 +3768,7 @@
         <v>19009</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -3797,22 +3777,22 @@
         <v>10000</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="O13" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="P13"/>
       <c r="Q13"/>
@@ -3830,7 +3810,7 @@
         <v>19010</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -3839,22 +3819,22 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="O14" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>95</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
@@ -3915,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C4" s="1">
         <f>_xlfn.XLOOKUP(B4,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3925,7 +3905,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F4" s="1">
         <f>_xlfn.XLOOKUP(E4,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3943,7 +3923,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C5" s="1">
         <f>_xlfn.XLOOKUP(B5,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3953,7 +3933,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F5" s="1">
         <f>_xlfn.XLOOKUP(E5,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3971,7 +3951,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C6" s="1">
         <f>_xlfn.XLOOKUP(B6,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3981,7 +3961,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F6" s="1">
         <f>_xlfn.XLOOKUP(E6,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3999,7 +3979,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C7" s="1" t="e">
         <f>_xlfn.XLOOKUP(B7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4009,7 +3989,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F7" s="1">
         <f>_xlfn.XLOOKUP(E7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4019,7 +3999,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I7" s="1">
         <f>_xlfn.XLOOKUP(H7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4034,7 +4014,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C8" s="1" t="e">
         <f>_xlfn.XLOOKUP(B8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4044,7 +4024,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F8" s="1">
         <f>_xlfn.XLOOKUP(E8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4054,7 +4034,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I8" s="1">
         <f>_xlfn.XLOOKUP(H8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4069,7 +4049,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C9" s="1" t="e">
         <f>_xlfn.XLOOKUP(B9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4079,7 +4059,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F9" s="1">
         <f>_xlfn.XLOOKUP(E9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4089,7 +4069,7 @@
         <v>10</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I9" s="1">
         <f>_xlfn.XLOOKUP(H9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4104,7 +4084,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C10" s="1" t="e">
         <f>_xlfn.XLOOKUP(B10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4114,7 +4094,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F10" s="1">
         <f>_xlfn.XLOOKUP(E10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4124,7 +4104,7 @@
         <v>10</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I10" s="1">
         <f>_xlfn.XLOOKUP(H10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4139,7 +4119,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C11" s="1" t="e">
         <f>_xlfn.XLOOKUP(B11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4149,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F11" s="1">
         <f>_xlfn.XLOOKUP(E11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4159,7 +4139,7 @@
         <v>20</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I11" s="1">
         <f>_xlfn.XLOOKUP(H11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4174,7 +4154,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C12" s="1" t="e">
         <f>_xlfn.XLOOKUP(B12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4184,7 +4164,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F12" s="1">
         <f>_xlfn.XLOOKUP(E12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4194,7 +4174,7 @@
         <v>20</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I12" s="1">
         <f>_xlfn.XLOOKUP(H12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4209,7 +4189,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C13" s="1" t="e">
         <f>_xlfn.XLOOKUP(B13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4219,7 +4199,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F13" s="1">
         <f>_xlfn.XLOOKUP(E13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4229,7 +4209,7 @@
         <v>20</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I13" s="1">
         <f>_xlfn.XLOOKUP(H13,[1]Item!$D:$D,[1]Item!$A:$A)</f>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="108">
   <si>
     <t>id</t>
   </si>
@@ -270,19 +270,31 @@
     <t>4320_1098680</t>
   </si>
   <si>
-    <t>1022501_1</t>
+    <t>1990000_18888</t>
+  </si>
+  <si>
+    <t>1990000_688</t>
+  </si>
+  <si>
+    <t>1990000_1288</t>
+  </si>
+  <si>
+    <t>1990000_3888</t>
   </si>
   <si>
     <t>4320_12380000</t>
   </si>
   <si>
-    <t>1990000_8888</t>
-  </si>
-  <si>
-    <t>1990000_3888</t>
-  </si>
-  <si>
-    <t>1990000_388</t>
+    <t>1990000_58888</t>
+  </si>
+  <si>
+    <t>1990000_1938</t>
+  </si>
+  <si>
+    <t>1990000_3878</t>
+  </si>
+  <si>
+    <t>1990000_9678</t>
   </si>
   <si>
     <t>1020001_1</t>
@@ -294,19 +306,13 @@
     <t>4320_104648340</t>
   </si>
   <si>
-    <t>1990000_28888</t>
-  </si>
-  <si>
-    <t>1990000_1288</t>
-  </si>
-  <si>
-    <t>1990000_18888</t>
-  </si>
-  <si>
-    <t>1990000_4888</t>
-  </si>
-  <si>
-    <t>1022501_3</t>
+    <t>1990000_565888</t>
+  </si>
+  <si>
+    <t>1990000_37688</t>
+  </si>
+  <si>
+    <t>1990000_94188</t>
   </si>
   <si>
     <t>1_1000</t>
@@ -315,19 +321,19 @@
     <t>4320_1069785000</t>
   </si>
   <si>
-    <t>1990000_188888</t>
-  </si>
-  <si>
-    <t>1990000_6888</t>
-  </si>
-  <si>
-    <t>1990000_138888</t>
-  </si>
-  <si>
-    <t>1990000_32888</t>
-  </si>
-  <si>
-    <t>1031600_1|1020001_2</t>
+    <t>1990000_4828888</t>
+  </si>
+  <si>
+    <t>1990000_134888</t>
+  </si>
+  <si>
+    <t>1990000_268888</t>
+  </si>
+  <si>
+    <t>1990000_678888</t>
+  </si>
+  <si>
+    <t>1031600_1|1020001_1</t>
   </si>
   <si>
     <t>1_1500</t>
@@ -336,34 +342,34 @@
     <t>-1_0</t>
   </si>
   <si>
-    <t>1990000_1668888</t>
-  </si>
-  <si>
-    <t>1990000_58888</t>
-  </si>
-  <si>
-    <t>1990000_1098888</t>
-  </si>
-  <si>
-    <t>1990000_268888</t>
-  </si>
-  <si>
-    <t>1031801_1|1022501_10</t>
+    <t>1990000_33488888</t>
+  </si>
+  <si>
+    <t>1990000_1118888</t>
+  </si>
+  <si>
+    <t>1990000_2238888</t>
+  </si>
+  <si>
+    <t>1990000_5568888</t>
+  </si>
+  <si>
+    <t>1031801_1|1020001_5</t>
   </si>
   <si>
     <t>1_2000</t>
   </si>
   <si>
-    <t>1990000_3028888</t>
-  </si>
-  <si>
-    <t>1990000_109888</t>
-  </si>
-  <si>
-    <t>1990000_2019888</t>
-  </si>
-  <si>
-    <t>1990000_509888</t>
+    <t>1990000_68688888</t>
+  </si>
+  <si>
+    <t>1990000_2828888</t>
+  </si>
+  <si>
+    <t>1990000_4848888</t>
+  </si>
+  <si>
+    <t>1990000_18188888</t>
   </si>
   <si>
     <t>1032001_1|1020001_10</t>
@@ -372,70 +378,76 @@
     <t>1_2500</t>
   </si>
   <si>
-    <t>1990000_8568888</t>
-  </si>
-  <si>
-    <t>1990000_285888</t>
-  </si>
-  <si>
-    <t>1990000_5718888</t>
-  </si>
-  <si>
-    <t>1990000_1398888</t>
-  </si>
-  <si>
-    <t>1031601_1|1032201_1|1022501_30</t>
-  </si>
-  <si>
-    <t>1_3000|2_50</t>
-  </si>
-  <si>
-    <t>1990000_39298888</t>
-  </si>
-  <si>
-    <t>1990000_26219888</t>
-  </si>
-  <si>
-    <t>1990000_6568888</t>
+    <t>1990000_171888888</t>
+  </si>
+  <si>
+    <t>1990000_5728888</t>
+  </si>
+  <si>
+    <t>1990000_11488888</t>
+  </si>
+  <si>
+    <t>1990000_28688888</t>
+  </si>
+  <si>
+    <t>1031601_1|1020001_10</t>
+  </si>
+  <si>
+    <t>1_3000|2_600</t>
+  </si>
+  <si>
+    <t>1990000_787888888</t>
+  </si>
+  <si>
+    <t>1990000_26288888</t>
+  </si>
+  <si>
+    <t>1990000_52588888</t>
+  </si>
+  <si>
+    <t>1990000_131888888</t>
   </si>
   <si>
     <t>1031802_1|1020001_20</t>
   </si>
   <si>
-    <t>1_3500|2_100</t>
-  </si>
-  <si>
-    <t>1990000_126298888</t>
-  </si>
-  <si>
-    <t>1990000_3999888</t>
-  </si>
-  <si>
-    <t>1990000_83988888</t>
-  </si>
-  <si>
-    <t>1990000_20988888</t>
-  </si>
-  <si>
-    <t>1032002_1|1022501_30</t>
-  </si>
-  <si>
-    <t>1_4000|2_200</t>
-  </si>
-  <si>
-    <t>1990000_629888888</t>
-  </si>
-  <si>
-    <t>1990000_419888888</t>
-  </si>
-  <si>
-    <t>1990000_103988888</t>
-  </si>
-  <si>
-    <t>1031602_1|1032202_1|1020001_20</t>
-  </si>
-  <si>
-    <t>1_4500|2_300</t>
+    <t>1_3500|2_800</t>
+  </si>
+  <si>
+    <t>1990000_2538888888</t>
+  </si>
+  <si>
+    <t>1990000_84288888</t>
+  </si>
+  <si>
+    <t>1990000_168888888</t>
+  </si>
+  <si>
+    <t>1990000_421888888</t>
+  </si>
+  <si>
+    <t>1032002_1|1020001_20</t>
+  </si>
+  <si>
+    <t>1_4000|2_1000</t>
+  </si>
+  <si>
+    <t>1990000_12688888888</t>
+  </si>
+  <si>
+    <t>1990000_428888888</t>
+  </si>
+  <si>
+    <t>1990000_848888888</t>
+  </si>
+  <si>
+    <t>1990000_2188888888</t>
+  </si>
+  <si>
+    <t>1031602_1|1020001_20</t>
+  </si>
+  <si>
+    <t>1_4500|2_1500</t>
   </si>
   <si>
     <t>刮刮卡</t>
@@ -651,12 +663,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3422,9 +3434,19 @@
       <c r="H5" s="1">
         <v>10000</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="J5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5" s="1"/>
       <c r="O5" s="7"/>
       <c r="P5"/>
       <c r="Q5"/>
@@ -3445,7 +3467,7 @@
         <v>19002</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G6" s="1">
         <v>10000</v>
@@ -3454,20 +3476,22 @@
         <v>10000</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="K6" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="P6"/>
       <c r="Q6"/>
@@ -3488,7 +3512,7 @@
         <v>19003</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G7" s="1">
         <v>10000</v>
@@ -3497,22 +3521,22 @@
         <v>10000</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="O7" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="P7"/>
       <c r="Q7"/>
@@ -3533,7 +3557,7 @@
         <v>19004</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G8" s="1">
         <v>10000</v>
@@ -3542,22 +3566,22 @@
         <v>10000</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P8"/>
       <c r="Q8"/>
@@ -3580,7 +3604,7 @@
         <v>19005</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -3589,22 +3613,22 @@
         <v>10000</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P9"/>
       <c r="Q9"/>
@@ -3627,7 +3651,7 @@
         <v>19006</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -3636,22 +3660,22 @@
         <v>10000</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P10"/>
       <c r="Q10"/>
@@ -3674,7 +3698,7 @@
         <v>19007</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -3683,22 +3707,22 @@
         <v>10000</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P11"/>
       <c r="Q11"/>
@@ -3721,7 +3745,7 @@
         <v>19008</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -3730,22 +3754,22 @@
         <v>10000</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P12"/>
       <c r="Q12"/>
@@ -3768,7 +3792,7 @@
         <v>19009</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -3777,22 +3801,22 @@
         <v>10000</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="P13"/>
       <c r="Q13"/>
@@ -3810,7 +3834,7 @@
         <v>19010</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -3819,22 +3843,22 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
@@ -3895,7 +3919,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C4" s="1">
         <f>_xlfn.XLOOKUP(B4,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3905,7 +3929,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F4" s="1">
         <f>_xlfn.XLOOKUP(E4,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3923,7 +3947,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C5" s="1">
         <f>_xlfn.XLOOKUP(B5,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3933,7 +3957,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F5" s="1">
         <f>_xlfn.XLOOKUP(E5,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3951,7 +3975,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C6" s="1">
         <f>_xlfn.XLOOKUP(B6,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3961,7 +3985,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F6" s="1">
         <f>_xlfn.XLOOKUP(E6,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3979,7 +4003,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C7" s="1" t="e">
         <f>_xlfn.XLOOKUP(B7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3989,7 +4013,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F7" s="1">
         <f>_xlfn.XLOOKUP(E7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3999,7 +4023,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I7" s="1">
         <f>_xlfn.XLOOKUP(H7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4014,7 +4038,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C8" s="1" t="e">
         <f>_xlfn.XLOOKUP(B8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4024,7 +4048,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F8" s="1">
         <f>_xlfn.XLOOKUP(E8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4034,7 +4058,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I8" s="1">
         <f>_xlfn.XLOOKUP(H8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4049,7 +4073,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C9" s="1" t="e">
         <f>_xlfn.XLOOKUP(B9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4059,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F9" s="1">
         <f>_xlfn.XLOOKUP(E9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4069,7 +4093,7 @@
         <v>10</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I9" s="1">
         <f>_xlfn.XLOOKUP(H9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4084,7 +4108,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C10" s="1" t="e">
         <f>_xlfn.XLOOKUP(B10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4094,7 +4118,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F10" s="1">
         <f>_xlfn.XLOOKUP(E10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4104,7 +4128,7 @@
         <v>10</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I10" s="1">
         <f>_xlfn.XLOOKUP(H10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4119,7 +4143,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C11" s="1" t="e">
         <f>_xlfn.XLOOKUP(B11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4129,7 +4153,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F11" s="1">
         <f>_xlfn.XLOOKUP(E11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4139,7 +4163,7 @@
         <v>20</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I11" s="1">
         <f>_xlfn.XLOOKUP(H11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4154,7 +4178,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C12" s="1" t="e">
         <f>_xlfn.XLOOKUP(B12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4164,7 +4188,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F12" s="1">
         <f>_xlfn.XLOOKUP(E12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4174,7 +4198,7 @@
         <v>20</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I12" s="1">
         <f>_xlfn.XLOOKUP(H12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4189,7 +4213,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C13" s="1" t="e">
         <f>_xlfn.XLOOKUP(B13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4199,7 +4223,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F13" s="1">
         <f>_xlfn.XLOOKUP(E13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4209,7 +4233,7 @@
         <v>20</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I13" s="1">
         <f>_xlfn.XLOOKUP(H13,[1]Item!$D:$D,[1]Item!$A:$A)</f>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="105">
   <si>
     <t>id</t>
   </si>
@@ -270,43 +270,34 @@
     <t>4320_1098680</t>
   </si>
   <si>
+    <t>1990000_0</t>
+  </si>
+  <si>
+    <t>1020001_1</t>
+  </si>
+  <si>
+    <t>4320_12380000</t>
+  </si>
+  <si>
+    <t>1990000_58888</t>
+  </si>
+  <si>
+    <t>1990000_3878</t>
+  </si>
+  <si>
+    <t>1990000_9678</t>
+  </si>
+  <si>
+    <t>1_500</t>
+  </si>
+  <si>
+    <t>4320_104648340</t>
+  </si>
+  <si>
+    <t>1990000_565888</t>
+  </si>
+  <si>
     <t>1990000_18888</t>
-  </si>
-  <si>
-    <t>1990000_688</t>
-  </si>
-  <si>
-    <t>1990000_1288</t>
-  </si>
-  <si>
-    <t>1990000_3888</t>
-  </si>
-  <si>
-    <t>4320_12380000</t>
-  </si>
-  <si>
-    <t>1990000_58888</t>
-  </si>
-  <si>
-    <t>1990000_1938</t>
-  </si>
-  <si>
-    <t>1990000_3878</t>
-  </si>
-  <si>
-    <t>1990000_9678</t>
-  </si>
-  <si>
-    <t>1020001_1</t>
-  </si>
-  <si>
-    <t>1_500</t>
-  </si>
-  <si>
-    <t>4320_104648340</t>
-  </si>
-  <si>
-    <t>1990000_565888</t>
   </si>
   <si>
     <t>1990000_37688</t>
@@ -1291,1702 +1282,542 @@
         </row>
         <row r="5">
           <cell r="A5">
-            <v>1010101</v>
+            <v>1990000</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5" t="str">
-            <v>金币礼包</v>
+            <v>金币</v>
           </cell>
         </row>
         <row r="6">
           <cell r="A6">
-            <v>1010201</v>
+            <v>1980000</v>
           </cell>
         </row>
         <row r="6">
           <cell r="D6" t="str">
-            <v>钻石礼包</v>
+            <v>钻石</v>
           </cell>
         </row>
         <row r="7">
           <cell r="A7">
-            <v>1010301</v>
+            <v>1020001</v>
           </cell>
         </row>
         <row r="7">
           <cell r="D7" t="str">
-            <v>赌场工具（普通）</v>
+            <v>白金卡</v>
           </cell>
         </row>
         <row r="8">
           <cell r="A8">
-            <v>1010302</v>
+            <v>1022501</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8" t="str">
-            <v>赌场工具（精良）</v>
+            <v>祈福卡</v>
           </cell>
         </row>
         <row r="9">
           <cell r="A9">
-            <v>1010303</v>
+            <v>1022502</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9" t="str">
-            <v>赌场工具（优秀）</v>
+            <v>刮刮卡</v>
           </cell>
         </row>
         <row r="10">
           <cell r="A10">
-            <v>1010304</v>
+            <v>1022503</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10" t="str">
-            <v>赌场工具（绝佳）</v>
+            <v>夺宝优惠券</v>
           </cell>
         </row>
         <row r="11">
           <cell r="A11">
-            <v>1010305</v>
+            <v>1010301</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11" t="str">
-            <v>赌场工具（传奇）</v>
+            <v>赌场工具（普通）</v>
           </cell>
         </row>
         <row r="12">
           <cell r="A12">
-            <v>1010311</v>
+            <v>1010302</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12" t="str">
-            <v>拼图随机礼包(一星)</v>
+            <v>赌场工具（精良）</v>
           </cell>
         </row>
         <row r="13">
           <cell r="A13">
-            <v>1010312</v>
+            <v>1010303</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13" t="str">
-            <v>拼图随机礼包(二星)</v>
+            <v>赌场工具（优秀）</v>
           </cell>
         </row>
         <row r="14">
           <cell r="A14">
-            <v>1010313</v>
+            <v>1010304</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14" t="str">
-            <v>拼图随机礼包(三星)</v>
+            <v>赌场工具（绝佳）</v>
           </cell>
         </row>
         <row r="15">
           <cell r="A15">
-            <v>1010314</v>
+            <v>1010305</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15" t="str">
-            <v>拼图随机礼包(四星)</v>
+            <v>赌场工具（传奇）</v>
           </cell>
         </row>
         <row r="16">
           <cell r="A16">
-            <v>1010315</v>
+            <v>1031001</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16" t="str">
-            <v>拼图随机礼包(五星)</v>
+            <v>头像2</v>
           </cell>
         </row>
         <row r="17">
           <cell r="A17">
-            <v>1020001</v>
+            <v>1031002</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17" t="str">
-            <v>白金卡</v>
+            <v>头像3</v>
           </cell>
         </row>
         <row r="18">
           <cell r="A18">
-            <v>1020002</v>
+            <v>1031201</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18" t="str">
-            <v>测试道具2</v>
+            <v>头像框2</v>
           </cell>
         </row>
         <row r="19">
           <cell r="A19">
-            <v>1020003</v>
+            <v>1031202</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19" t="str">
-            <v>测试道具3</v>
+            <v>头像框3</v>
           </cell>
         </row>
         <row r="20">
           <cell r="A20">
-            <v>1020004</v>
+            <v>1031350</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20" t="str">
-            <v>测试道具4</v>
+            <v>头像框-每日奖金</v>
           </cell>
         </row>
         <row r="21">
           <cell r="A21">
-            <v>1020005</v>
+            <v>1031351</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21" t="str">
-            <v>测试道具5</v>
+            <v>头像框-首充专属</v>
           </cell>
         </row>
         <row r="22">
           <cell r="A22">
-            <v>1020006</v>
+            <v>1021401</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22" t="str">
-            <v>测试道具6</v>
+            <v>国旗2</v>
           </cell>
         </row>
         <row r="23">
           <cell r="A23">
-            <v>1030011</v>
+            <v>1021402</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23" t="str">
-            <v>图鉴1-图片</v>
+            <v>国旗3</v>
           </cell>
         </row>
         <row r="24">
           <cell r="A24">
-            <v>1030012</v>
+            <v>1031600</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24" t="str">
-            <v>图鉴2-图片</v>
+            <v>头衔1-财富贵族</v>
           </cell>
         </row>
         <row r="25">
           <cell r="A25">
-            <v>1030013</v>
+            <v>1031601</v>
           </cell>
         </row>
         <row r="25">
           <cell r="D25" t="str">
-            <v>图鉴3-图片</v>
+            <v>头衔2-一夜暴富</v>
           </cell>
         </row>
         <row r="26">
           <cell r="A26">
-            <v>1030014</v>
+            <v>1031602</v>
           </cell>
         </row>
         <row r="26">
           <cell r="D26" t="str">
-            <v>图鉴4-图片</v>
+            <v>头衔3-四方来财</v>
           </cell>
         </row>
         <row r="27">
           <cell r="A27">
-            <v>1030015</v>
+            <v>1031801</v>
           </cell>
         </row>
         <row r="27">
           <cell r="D27" t="str">
-            <v>图鉴5-图片</v>
+            <v>筹码2-翡翠贵族</v>
           </cell>
         </row>
         <row r="28">
           <cell r="A28">
-            <v>1030016</v>
+            <v>1031802</v>
           </cell>
         </row>
         <row r="28">
           <cell r="D28" t="str">
-            <v>图鉴6-图片</v>
+            <v>筹码3-水晶皇室</v>
           </cell>
         </row>
         <row r="29">
           <cell r="A29">
-            <v>1030017</v>
+            <v>1032001</v>
           </cell>
         </row>
         <row r="29">
           <cell r="D29" t="str">
-            <v>图鉴7-图片</v>
+            <v>牌背2-神秘塔罗</v>
           </cell>
         </row>
         <row r="30">
           <cell r="A30">
-            <v>1030018</v>
+            <v>1032002</v>
           </cell>
         </row>
         <row r="30">
           <cell r="D30" t="str">
-            <v>图鉴8-图片</v>
+            <v>牌背3-命运之手</v>
           </cell>
         </row>
         <row r="31">
           <cell r="A31">
-            <v>1030101</v>
+            <v>1032201</v>
           </cell>
         </row>
         <row r="31">
           <cell r="D31" t="str">
-            <v>图鉴1-碎片1</v>
+            <v>大厅背景2-决赛之夜</v>
           </cell>
         </row>
         <row r="32">
           <cell r="A32">
-            <v>1030102</v>
+            <v>1032202</v>
           </cell>
         </row>
         <row r="32">
           <cell r="D32" t="str">
-            <v>图鉴1-碎片2</v>
+            <v>大厅背景3-度假海滩</v>
           </cell>
         </row>
         <row r="33">
           <cell r="A33">
-            <v>1030103</v>
+            <v>1022504</v>
           </cell>
         </row>
         <row r="33">
           <cell r="D33" t="str">
-            <v>图鉴1-碎片3</v>
+            <v>积分</v>
           </cell>
         </row>
         <row r="34">
           <cell r="A34">
-            <v>1030104</v>
+            <v>1023001</v>
           </cell>
         </row>
         <row r="34">
           <cell r="D34" t="str">
-            <v>图鉴1-碎片4</v>
+            <v>1星扳手</v>
           </cell>
         </row>
         <row r="35">
           <cell r="A35">
-            <v>1030105</v>
+            <v>1023002</v>
           </cell>
         </row>
         <row r="35">
           <cell r="D35" t="str">
-            <v>图鉴1-碎片5</v>
+            <v>2星扳手</v>
           </cell>
         </row>
         <row r="36">
           <cell r="A36">
-            <v>1030106</v>
+            <v>1023003</v>
           </cell>
         </row>
         <row r="36">
           <cell r="D36" t="str">
-            <v>图鉴1-碎片6</v>
+            <v>3星扳手</v>
           </cell>
         </row>
         <row r="37">
           <cell r="A37">
-            <v>1030107</v>
+            <v>1023004</v>
           </cell>
         </row>
         <row r="37">
           <cell r="D37" t="str">
-            <v>图鉴1-碎片7</v>
+            <v>4星扳手</v>
           </cell>
         </row>
         <row r="38">
           <cell r="A38">
-            <v>1030108</v>
+            <v>1023005</v>
           </cell>
         </row>
         <row r="38">
           <cell r="D38" t="str">
-            <v>图鉴1-碎片8</v>
+            <v>5星扳手</v>
           </cell>
         </row>
         <row r="39">
           <cell r="A39">
-            <v>1030109</v>
+            <v>1023101</v>
           </cell>
         </row>
         <row r="39">
           <cell r="D39" t="str">
-            <v>图鉴1-碎片9</v>
+            <v>1星筹码</v>
           </cell>
         </row>
         <row r="40">
           <cell r="A40">
-            <v>1030110</v>
+            <v>1023102</v>
           </cell>
         </row>
         <row r="40">
           <cell r="D40" t="str">
-            <v>图鉴1-碎片10</v>
+            <v>2星筹码</v>
           </cell>
         </row>
         <row r="41">
           <cell r="A41">
-            <v>1030111</v>
+            <v>1023103</v>
           </cell>
         </row>
         <row r="41">
           <cell r="D41" t="str">
-            <v>图鉴1-碎片11</v>
+            <v>3星筹码</v>
           </cell>
         </row>
         <row r="42">
           <cell r="A42">
-            <v>1030112</v>
+            <v>1023104</v>
           </cell>
         </row>
         <row r="42">
           <cell r="D42" t="str">
-            <v>图鉴1-碎片12</v>
+            <v>4星筹码</v>
           </cell>
         </row>
         <row r="43">
           <cell r="A43">
-            <v>1030121</v>
+            <v>1023105</v>
           </cell>
         </row>
         <row r="43">
           <cell r="D43" t="str">
-            <v>图鉴2-碎片1</v>
+            <v>5星筹码</v>
           </cell>
         </row>
         <row r="44">
           <cell r="A44">
-            <v>1030122</v>
+            <v>1023201</v>
           </cell>
         </row>
         <row r="44">
           <cell r="D44" t="str">
-            <v>图鉴2-碎片2</v>
+            <v>1星螺母</v>
           </cell>
         </row>
         <row r="45">
           <cell r="A45">
-            <v>1030123</v>
+            <v>1023202</v>
           </cell>
         </row>
         <row r="45">
           <cell r="D45" t="str">
-            <v>图鉴2-碎片3</v>
+            <v>2星螺母</v>
           </cell>
         </row>
         <row r="46">
           <cell r="A46">
-            <v>1030124</v>
+            <v>1023203</v>
           </cell>
         </row>
         <row r="46">
           <cell r="D46" t="str">
-            <v>图鉴2-碎片4</v>
+            <v>3星螺母</v>
           </cell>
         </row>
         <row r="47">
           <cell r="A47">
-            <v>1030125</v>
+            <v>1023204</v>
           </cell>
         </row>
         <row r="47">
           <cell r="D47" t="str">
-            <v>图鉴2-碎片5</v>
+            <v>4星螺母</v>
           </cell>
         </row>
         <row r="48">
           <cell r="A48">
-            <v>1030126</v>
+            <v>1023205</v>
           </cell>
         </row>
         <row r="48">
           <cell r="D48" t="str">
-            <v>图鉴2-碎片6</v>
+            <v>5星螺母</v>
           </cell>
         </row>
         <row r="49">
           <cell r="A49">
-            <v>1030127</v>
+            <v>1023301</v>
           </cell>
         </row>
         <row r="49">
           <cell r="D49" t="str">
-            <v>图鉴2-碎片7</v>
+            <v>1星木材</v>
           </cell>
         </row>
         <row r="50">
           <cell r="A50">
-            <v>1030128</v>
+            <v>1023302</v>
           </cell>
         </row>
         <row r="50">
           <cell r="D50" t="str">
-            <v>图鉴2-碎片8</v>
+            <v>2星木材</v>
           </cell>
         </row>
         <row r="51">
           <cell r="A51">
-            <v>1030129</v>
+            <v>1023303</v>
           </cell>
         </row>
         <row r="51">
           <cell r="D51" t="str">
-            <v>图鉴2-碎片9</v>
+            <v>3星木材</v>
           </cell>
         </row>
         <row r="52">
           <cell r="A52">
-            <v>1030130</v>
+            <v>1023304</v>
           </cell>
         </row>
         <row r="52">
           <cell r="D52" t="str">
-            <v>图鉴2-碎片10</v>
+            <v>4星木材</v>
           </cell>
         </row>
         <row r="53">
           <cell r="A53">
-            <v>1030131</v>
+            <v>1023305</v>
           </cell>
         </row>
         <row r="53">
           <cell r="D53" t="str">
-            <v>图鉴2-碎片11</v>
+            <v>5星木材</v>
           </cell>
         </row>
         <row r="54">
           <cell r="A54">
-            <v>1030132</v>
+            <v>1023401</v>
           </cell>
         </row>
         <row r="54">
           <cell r="D54" t="str">
-            <v>图鉴2-碎片12</v>
+            <v>1星酒瓶</v>
           </cell>
         </row>
         <row r="55">
           <cell r="A55">
-            <v>1030141</v>
+            <v>1023402</v>
           </cell>
         </row>
         <row r="55">
           <cell r="D55" t="str">
-            <v>图鉴3-碎片1</v>
+            <v>2星酒瓶</v>
           </cell>
         </row>
         <row r="56">
           <cell r="A56">
-            <v>1030142</v>
+            <v>1023403</v>
           </cell>
         </row>
         <row r="56">
           <cell r="D56" t="str">
-            <v>图鉴3-碎片2</v>
+            <v>3星酒瓶</v>
           </cell>
         </row>
         <row r="57">
           <cell r="A57">
-            <v>1030143</v>
+            <v>1023404</v>
           </cell>
         </row>
         <row r="57">
           <cell r="D57" t="str">
-            <v>图鉴3-碎片3</v>
+            <v>4星酒瓶</v>
           </cell>
         </row>
         <row r="58">
           <cell r="A58">
-            <v>1030144</v>
+            <v>1023405</v>
           </cell>
         </row>
         <row r="58">
           <cell r="D58" t="str">
-            <v>图鉴3-碎片4</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59">
-            <v>1030145</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="D59" t="str">
-            <v>图鉴3-碎片5</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60">
-            <v>1030146</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="D60" t="str">
-            <v>图鉴3-碎片6</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61">
-            <v>1030147</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="D61" t="str">
-            <v>图鉴3-碎片7</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62">
-            <v>1030148</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="D62" t="str">
-            <v>图鉴3-碎片8</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="A63">
-            <v>1030149</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="D63" t="str">
-            <v>图鉴3-碎片9</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="A64">
-            <v>1030150</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="D64" t="str">
-            <v>图鉴3-碎片10</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="A65">
-            <v>1030151</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="D65" t="str">
-            <v>图鉴3-碎片11</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="A66">
-            <v>1030152</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="D66" t="str">
-            <v>图鉴3-碎片12</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="A67">
-            <v>1030161</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="D67" t="str">
-            <v>图鉴4-碎片1</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="A68">
-            <v>1030162</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="D68" t="str">
-            <v>图鉴4-碎片2</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="A69">
-            <v>1030163</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="D69" t="str">
-            <v>图鉴4-碎片3</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="A70">
-            <v>1030164</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="D70" t="str">
-            <v>图鉴4-碎片4</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="A71">
-            <v>1030165</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="D71" t="str">
-            <v>图鉴4-碎片5</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="A72">
-            <v>1030166</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="D72" t="str">
-            <v>图鉴4-碎片6</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="A73">
-            <v>1030167</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="D73" t="str">
-            <v>图鉴4-碎片7</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="A74">
-            <v>1030168</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="D74" t="str">
-            <v>图鉴4-碎片8</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="A75">
-            <v>1030169</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="D75" t="str">
-            <v>图鉴4-碎片9</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="A76">
-            <v>1030170</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="D76" t="str">
-            <v>图鉴4-碎片10</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="A77">
-            <v>1030171</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="D77" t="str">
-            <v>图鉴4-碎片11</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="A78">
-            <v>1030172</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="D78" t="str">
-            <v>图鉴4-碎片12</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="A79">
-            <v>1030181</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="D79" t="str">
-            <v>图鉴5-碎片1</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="A80">
-            <v>1030182</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="D80" t="str">
-            <v>图鉴5-碎片2</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="A81">
-            <v>1030183</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="D81" t="str">
-            <v>图鉴5-碎片3</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="A82">
-            <v>1030184</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="D82" t="str">
-            <v>图鉴5-碎片4</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="A83">
-            <v>1030185</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="D83" t="str">
-            <v>图鉴5-碎片5</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="A84">
-            <v>1030186</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="D84" t="str">
-            <v>图鉴5-碎片6</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="A85">
-            <v>1030187</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="D85" t="str">
-            <v>图鉴5-碎片7</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="A86">
-            <v>1030188</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="D86" t="str">
-            <v>图鉴5-碎片8</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="A87">
-            <v>1030189</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="D87" t="str">
-            <v>图鉴5-碎片9</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="A88">
-            <v>1030190</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="D88" t="str">
-            <v>图鉴5-碎片10</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="A89">
-            <v>1030191</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="D89" t="str">
-            <v>图鉴5-碎片11</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="A90">
-            <v>1030192</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="D90" t="str">
-            <v>图鉴5-碎片12</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="A91">
-            <v>1030201</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="D91" t="str">
-            <v>图鉴6-碎片1</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="A92">
-            <v>1030202</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="D92" t="str">
-            <v>图鉴6-碎片2</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="A93">
-            <v>1030203</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="D93" t="str">
-            <v>图鉴6-碎片3</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="A94">
-            <v>1030204</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="D94" t="str">
-            <v>图鉴6-碎片4</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="A95">
-            <v>1030205</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="D95" t="str">
-            <v>图鉴6-碎片5</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="A96">
-            <v>1030206</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="D96" t="str">
-            <v>图鉴6-碎片6</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="A97">
-            <v>1030207</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="D97" t="str">
-            <v>图鉴6-碎片7</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="A98">
-            <v>1030208</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="D98" t="str">
-            <v>图鉴6-碎片8</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="A99">
-            <v>1030209</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="D99" t="str">
-            <v>图鉴6-碎片9</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="A100">
-            <v>1030210</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="D100" t="str">
-            <v>图鉴6-碎片10</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="A101">
-            <v>1030211</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="D101" t="str">
-            <v>图鉴6-碎片11</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="A102">
-            <v>1030212</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="D102" t="str">
-            <v>图鉴6-碎片12</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="A103">
-            <v>1030221</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="D103" t="str">
-            <v>图鉴7-碎片1</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="A104">
-            <v>1030222</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="D104" t="str">
-            <v>图鉴7-碎片2</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="A105">
-            <v>1030223</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="D105" t="str">
-            <v>图鉴7-碎片3</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="A106">
-            <v>1030224</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="D106" t="str">
-            <v>图鉴7-碎片4</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="A107">
-            <v>1030225</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="D107" t="str">
-            <v>图鉴7-碎片5</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="A108">
-            <v>1030226</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="D108" t="str">
-            <v>图鉴7-碎片6</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="A109">
-            <v>1030227</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="D109" t="str">
-            <v>图鉴7-碎片7</v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="A110">
-            <v>1030228</v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="D110" t="str">
-            <v>图鉴7-碎片8</v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="A111">
-            <v>1030229</v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="D111" t="str">
-            <v>图鉴7-碎片9</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="A112">
-            <v>1030230</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="D112" t="str">
-            <v>图鉴7-碎片10</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="A113">
-            <v>1030231</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="D113" t="str">
-            <v>图鉴7-碎片11</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="A114">
-            <v>1030232</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="D114" t="str">
-            <v>图鉴7-碎片12</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="A115">
-            <v>1030241</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="D115" t="str">
-            <v>图鉴8-碎片1</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="A116">
-            <v>1030242</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="D116" t="str">
-            <v>图鉴8-碎片2</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="A117">
-            <v>1030243</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="D117" t="str">
-            <v>图鉴8-碎片3</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="A118">
-            <v>1030244</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="D118" t="str">
-            <v>图鉴8-碎片4</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="A119">
-            <v>1030245</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="D119" t="str">
-            <v>图鉴8-碎片5</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="A120">
-            <v>1030246</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="D120" t="str">
-            <v>图鉴8-碎片6</v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="A121">
-            <v>1030247</v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="D121" t="str">
-            <v>图鉴8-碎片7</v>
-          </cell>
-        </row>
-        <row r="122">
-          <cell r="A122">
-            <v>1030248</v>
-          </cell>
-        </row>
-        <row r="122">
-          <cell r="D122" t="str">
-            <v>图鉴8-碎片8</v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="A123">
-            <v>1030249</v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="D123" t="str">
-            <v>图鉴8-碎片9</v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="A124">
-            <v>1030250</v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="D124" t="str">
-            <v>图鉴8-碎片10</v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="A125">
-            <v>1030251</v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="D125" t="str">
-            <v>图鉴8-碎片11</v>
-          </cell>
-        </row>
-        <row r="126">
-          <cell r="A126">
-            <v>1030252</v>
-          </cell>
-        </row>
-        <row r="126">
-          <cell r="D126" t="str">
-            <v>图鉴8-碎片12</v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="A127">
-            <v>1031001</v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="D127" t="str">
-            <v>头像2</v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="A128">
-            <v>1031002</v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="D128" t="str">
-            <v>头像3</v>
-          </cell>
-        </row>
-        <row r="129">
-          <cell r="A129">
-            <v>1031201</v>
-          </cell>
-        </row>
-        <row r="129">
-          <cell r="D129" t="str">
-            <v>头像框2</v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="A130">
-            <v>1031202</v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="D130" t="str">
-            <v>头像框3</v>
-          </cell>
-        </row>
-        <row r="131">
-          <cell r="A131">
-            <v>1031350</v>
-          </cell>
-        </row>
-        <row r="131">
-          <cell r="D131" t="str">
-            <v>头像框-每日奖金</v>
-          </cell>
-        </row>
-        <row r="132">
-          <cell r="A132">
-            <v>1031351</v>
-          </cell>
-        </row>
-        <row r="132">
-          <cell r="D132" t="str">
-            <v>头像框-首充专属</v>
-          </cell>
-        </row>
-        <row r="133">
-          <cell r="A133">
-            <v>1021401</v>
-          </cell>
-        </row>
-        <row r="133">
-          <cell r="D133" t="str">
-            <v>国旗2</v>
-          </cell>
-        </row>
-        <row r="134">
-          <cell r="A134">
-            <v>1021402</v>
-          </cell>
-        </row>
-        <row r="134">
-          <cell r="D134" t="str">
-            <v>国旗3</v>
-          </cell>
-        </row>
-        <row r="135">
-          <cell r="A135">
-            <v>1031600</v>
-          </cell>
-        </row>
-        <row r="135">
-          <cell r="D135" t="str">
-            <v>头衔1-财富贵族</v>
-          </cell>
-        </row>
-        <row r="136">
-          <cell r="A136">
-            <v>1031601</v>
-          </cell>
-        </row>
-        <row r="136">
-          <cell r="D136" t="str">
-            <v>头衔2-一夜暴富</v>
-          </cell>
-        </row>
-        <row r="137">
-          <cell r="A137">
-            <v>1031602</v>
-          </cell>
-        </row>
-        <row r="137">
-          <cell r="D137" t="str">
-            <v>头衔3-四方来财</v>
-          </cell>
-        </row>
-        <row r="138">
-          <cell r="A138">
-            <v>1031801</v>
-          </cell>
-        </row>
-        <row r="138">
-          <cell r="D138" t="str">
-            <v>筹码2-翡翠贵族</v>
-          </cell>
-        </row>
-        <row r="139">
-          <cell r="A139">
-            <v>1031802</v>
-          </cell>
-        </row>
-        <row r="139">
-          <cell r="D139" t="str">
-            <v>筹码3-水晶皇室</v>
-          </cell>
-        </row>
-        <row r="140">
-          <cell r="A140">
-            <v>1032001</v>
-          </cell>
-        </row>
-        <row r="140">
-          <cell r="D140" t="str">
-            <v>牌背2-神秘塔罗</v>
-          </cell>
-        </row>
-        <row r="141">
-          <cell r="A141">
-            <v>1032002</v>
-          </cell>
-        </row>
-        <row r="141">
-          <cell r="D141" t="str">
-            <v>牌背3-命运之手</v>
-          </cell>
-        </row>
-        <row r="142">
-          <cell r="A142">
-            <v>1032201</v>
-          </cell>
-        </row>
-        <row r="142">
-          <cell r="D142" t="str">
-            <v>大厅背景2-决赛之夜</v>
-          </cell>
-        </row>
-        <row r="143">
-          <cell r="A143">
-            <v>1032202</v>
-          </cell>
-        </row>
-        <row r="143">
-          <cell r="D143" t="str">
-            <v>大厅背景3-度假海滩</v>
-          </cell>
-        </row>
-        <row r="144">
-          <cell r="A144">
-            <v>1022501</v>
-          </cell>
-        </row>
-        <row r="144">
-          <cell r="D144" t="str">
-            <v>祈福卡</v>
-          </cell>
-        </row>
-        <row r="145">
-          <cell r="A145">
-            <v>1022502</v>
-          </cell>
-        </row>
-        <row r="145">
-          <cell r="D145" t="str">
-            <v>刮刮卡</v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="A146">
-            <v>1022503</v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="D146" t="str">
-            <v>夺宝优惠券</v>
-          </cell>
-        </row>
-        <row r="147">
-          <cell r="A147">
-            <v>1022504</v>
-          </cell>
-        </row>
-        <row r="147">
-          <cell r="D147" t="str">
-            <v>积分</v>
-          </cell>
-        </row>
-        <row r="148">
-          <cell r="A148">
-            <v>1023001</v>
-          </cell>
-        </row>
-        <row r="148">
-          <cell r="D148" t="str">
-            <v>1星扳手</v>
-          </cell>
-        </row>
-        <row r="149">
-          <cell r="A149">
-            <v>1023002</v>
-          </cell>
-        </row>
-        <row r="149">
-          <cell r="D149" t="str">
-            <v>2星扳手</v>
-          </cell>
-        </row>
-        <row r="150">
-          <cell r="A150">
-            <v>1023003</v>
-          </cell>
-        </row>
-        <row r="150">
-          <cell r="D150" t="str">
-            <v>3星扳手</v>
-          </cell>
-        </row>
-        <row r="151">
-          <cell r="A151">
-            <v>1023004</v>
-          </cell>
-        </row>
-        <row r="151">
-          <cell r="D151" t="str">
-            <v>4星扳手</v>
-          </cell>
-        </row>
-        <row r="152">
-          <cell r="A152">
-            <v>1023005</v>
-          </cell>
-        </row>
-        <row r="152">
-          <cell r="D152" t="str">
-            <v>5星扳手</v>
-          </cell>
-        </row>
-        <row r="153">
-          <cell r="A153">
-            <v>1023101</v>
-          </cell>
-        </row>
-        <row r="153">
-          <cell r="D153" t="str">
-            <v>1星筹码</v>
-          </cell>
-        </row>
-        <row r="154">
-          <cell r="A154">
-            <v>1023102</v>
-          </cell>
-        </row>
-        <row r="154">
-          <cell r="D154" t="str">
-            <v>2星筹码</v>
-          </cell>
-        </row>
-        <row r="155">
-          <cell r="A155">
-            <v>1023103</v>
-          </cell>
-        </row>
-        <row r="155">
-          <cell r="D155" t="str">
-            <v>3星筹码</v>
-          </cell>
-        </row>
-        <row r="156">
-          <cell r="A156">
-            <v>1023104</v>
-          </cell>
-        </row>
-        <row r="156">
-          <cell r="D156" t="str">
-            <v>4星筹码</v>
-          </cell>
-        </row>
-        <row r="157">
-          <cell r="A157">
-            <v>1023105</v>
-          </cell>
-        </row>
-        <row r="157">
-          <cell r="D157" t="str">
-            <v>5星筹码</v>
-          </cell>
-        </row>
-        <row r="158">
-          <cell r="A158">
-            <v>1023201</v>
-          </cell>
-        </row>
-        <row r="158">
-          <cell r="D158" t="str">
-            <v>1星螺母</v>
-          </cell>
-        </row>
-        <row r="159">
-          <cell r="A159">
-            <v>1023202</v>
-          </cell>
-        </row>
-        <row r="159">
-          <cell r="D159" t="str">
-            <v>2星螺母</v>
-          </cell>
-        </row>
-        <row r="160">
-          <cell r="A160">
-            <v>1023203</v>
-          </cell>
-        </row>
-        <row r="160">
-          <cell r="D160" t="str">
-            <v>3星螺母</v>
-          </cell>
-        </row>
-        <row r="161">
-          <cell r="A161">
-            <v>1023204</v>
-          </cell>
-        </row>
-        <row r="161">
-          <cell r="D161" t="str">
-            <v>4星螺母</v>
-          </cell>
-        </row>
-        <row r="162">
-          <cell r="A162">
-            <v>1023205</v>
-          </cell>
-        </row>
-        <row r="162">
-          <cell r="D162" t="str">
-            <v>5星螺母</v>
-          </cell>
-        </row>
-        <row r="163">
-          <cell r="A163">
-            <v>1023301</v>
-          </cell>
-        </row>
-        <row r="163">
-          <cell r="D163" t="str">
-            <v>1星木材</v>
-          </cell>
-        </row>
-        <row r="164">
-          <cell r="A164">
-            <v>1023302</v>
-          </cell>
-        </row>
-        <row r="164">
-          <cell r="D164" t="str">
-            <v>2星木材</v>
-          </cell>
-        </row>
-        <row r="165">
-          <cell r="A165">
-            <v>1023303</v>
-          </cell>
-        </row>
-        <row r="165">
-          <cell r="D165" t="str">
-            <v>3星木材</v>
-          </cell>
-        </row>
-        <row r="166">
-          <cell r="A166">
-            <v>1023304</v>
-          </cell>
-        </row>
-        <row r="166">
-          <cell r="D166" t="str">
-            <v>4星木材</v>
-          </cell>
-        </row>
-        <row r="167">
-          <cell r="A167">
-            <v>1023305</v>
-          </cell>
-        </row>
-        <row r="167">
-          <cell r="D167" t="str">
-            <v>5星木材</v>
-          </cell>
-        </row>
-        <row r="168">
-          <cell r="A168">
-            <v>1023401</v>
-          </cell>
-        </row>
-        <row r="168">
-          <cell r="D168" t="str">
-            <v>1星酒瓶</v>
-          </cell>
-        </row>
-        <row r="169">
-          <cell r="A169">
-            <v>1023402</v>
-          </cell>
-        </row>
-        <row r="169">
-          <cell r="D169" t="str">
-            <v>2星酒瓶</v>
-          </cell>
-        </row>
-        <row r="170">
-          <cell r="A170">
-            <v>1023403</v>
-          </cell>
-        </row>
-        <row r="170">
-          <cell r="D170" t="str">
-            <v>3星酒瓶</v>
-          </cell>
-        </row>
-        <row r="171">
-          <cell r="A171">
-            <v>1023404</v>
-          </cell>
-        </row>
-        <row r="171">
-          <cell r="D171" t="str">
-            <v>4星酒瓶</v>
-          </cell>
-        </row>
-        <row r="172">
-          <cell r="A172">
-            <v>1023405</v>
-          </cell>
-        </row>
-        <row r="172">
-          <cell r="D172" t="str">
             <v>5星酒瓶</v>
-          </cell>
-        </row>
-        <row r="173">
-          <cell r="A173">
-            <v>1990000</v>
-          </cell>
-        </row>
-        <row r="173">
-          <cell r="D173" t="str">
-            <v>金币</v>
-          </cell>
-        </row>
-        <row r="174">
-          <cell r="A174">
-            <v>1980000</v>
-          </cell>
-        </row>
-        <row r="174">
-          <cell r="D174" t="str">
-            <v>钻石</v>
           </cell>
         </row>
       </sheetData>
@@ -3250,11 +2081,11 @@
   <cols>
     <col min="1" max="1" width="10.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.35" style="1" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="17.75" style="1" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="14.875" style="1" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="17.375" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="8" width="21.25" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="27.35" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.375" style="1" customWidth="1"/>
+    <col min="7" max="8" width="21.25" style="1" customWidth="1"/>
     <col min="9" max="12" width="20.375" style="1" customWidth="1"/>
     <col min="13" max="13" width="37.375" style="1" customWidth="1"/>
     <col min="14" max="14" width="21.7666666666667" style="1" customWidth="1"/>
@@ -3438,15 +2269,17 @@
         <v>36</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="M5" s="1"/>
       <c r="O5" s="7"/>
       <c r="P5"/>
       <c r="Q5"/>
@@ -3467,7 +2300,7 @@
         <v>19002</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G6" s="1">
         <v>10000</v>
@@ -3476,22 +2309,22 @@
         <v>10000</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="M6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O6" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="P6"/>
       <c r="Q6"/>
@@ -3512,7 +2345,7 @@
         <v>19003</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G7" s="1">
         <v>10000</v>
@@ -3521,22 +2354,22 @@
         <v>10000</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O7" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>51</v>
       </c>
       <c r="P7"/>
       <c r="Q7"/>
@@ -3557,7 +2390,7 @@
         <v>19004</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G8" s="1">
         <v>10000</v>
@@ -3566,22 +2399,22 @@
         <v>10000</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="O8" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="P8"/>
       <c r="Q8"/>
@@ -3604,7 +2437,7 @@
         <v>19005</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -3613,22 +2446,22 @@
         <v>10000</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="O9" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>65</v>
       </c>
       <c r="P9"/>
       <c r="Q9"/>
@@ -3651,7 +2484,7 @@
         <v>19006</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -3660,22 +2493,22 @@
         <v>10000</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="O10" s="7" t="s">
         <v>68</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>71</v>
       </c>
       <c r="P10"/>
       <c r="Q10"/>
@@ -3698,7 +2531,7 @@
         <v>19007</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -3707,22 +2540,22 @@
         <v>10000</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="O11" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>77</v>
       </c>
       <c r="P11"/>
       <c r="Q11"/>
@@ -3745,7 +2578,7 @@
         <v>19008</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -3754,22 +2587,22 @@
         <v>10000</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="O12" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="P12"/>
       <c r="Q12"/>
@@ -3792,7 +2625,7 @@
         <v>19009</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -3801,22 +2634,22 @@
         <v>10000</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="O13" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="P13"/>
       <c r="Q13"/>
@@ -3834,7 +2667,7 @@
         <v>19010</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -3843,22 +2676,22 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="O14" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>95</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
@@ -3919,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C4" s="1">
         <f>_xlfn.XLOOKUP(B4,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3929,7 +2762,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F4" s="1">
         <f>_xlfn.XLOOKUP(E4,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3947,7 +2780,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C5" s="1">
         <f>_xlfn.XLOOKUP(B5,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3957,7 +2790,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F5" s="1">
         <f>_xlfn.XLOOKUP(E5,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3975,7 +2808,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C6" s="1">
         <f>_xlfn.XLOOKUP(B6,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3985,7 +2818,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F6" s="1">
         <f>_xlfn.XLOOKUP(E6,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4003,7 +2836,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C7" s="1" t="e">
         <f>_xlfn.XLOOKUP(B7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4013,7 +2846,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F7" s="1">
         <f>_xlfn.XLOOKUP(E7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4023,7 +2856,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I7" s="1">
         <f>_xlfn.XLOOKUP(H7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4038,7 +2871,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C8" s="1" t="e">
         <f>_xlfn.XLOOKUP(B8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4048,7 +2881,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F8" s="1">
         <f>_xlfn.XLOOKUP(E8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4058,7 +2891,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I8" s="1">
         <f>_xlfn.XLOOKUP(H8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4073,7 +2906,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C9" s="1" t="e">
         <f>_xlfn.XLOOKUP(B9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4083,7 +2916,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F9" s="1">
         <f>_xlfn.XLOOKUP(E9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4093,7 +2926,7 @@
         <v>10</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I9" s="1">
         <f>_xlfn.XLOOKUP(H9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4108,7 +2941,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C10" s="1" t="e">
         <f>_xlfn.XLOOKUP(B10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4118,7 +2951,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F10" s="1">
         <f>_xlfn.XLOOKUP(E10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4128,7 +2961,7 @@
         <v>10</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I10" s="1">
         <f>_xlfn.XLOOKUP(H10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4143,7 +2976,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C11" s="1" t="e">
         <f>_xlfn.XLOOKUP(B11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4153,7 +2986,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F11" s="1">
         <f>_xlfn.XLOOKUP(E11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4163,7 +2996,7 @@
         <v>20</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I11" s="1">
         <f>_xlfn.XLOOKUP(H11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4178,7 +3011,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C12" s="1" t="e">
         <f>_xlfn.XLOOKUP(B12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4188,7 +3021,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F12" s="1">
         <f>_xlfn.XLOOKUP(E12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4198,7 +3031,7 @@
         <v>20</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I12" s="1">
         <f>_xlfn.XLOOKUP(H12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4213,7 +3046,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C13" s="1" t="e">
         <f>_xlfn.XLOOKUP(B13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4223,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F13" s="1">
         <f>_xlfn.XLOOKUP(E13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4233,7 +3066,7 @@
         <v>20</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I13" s="1">
         <f>_xlfn.XLOOKUP(H13,[1]Item!$D:$D,[1]Item!$A:$A)</f>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="104">
   <si>
     <t>id</t>
   </si>
@@ -268,9 +268,6 @@
   </si>
   <si>
     <t>4320_1098680</t>
-  </si>
-  <si>
-    <t>1990000_0</t>
   </si>
   <si>
     <t>1020001_1</t>
@@ -2265,20 +2262,12 @@
       <c r="H5" s="1">
         <v>10000</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="O5" s="7"/>
       <c r="P5"/>
@@ -2300,7 +2289,7 @@
         <v>19002</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G6" s="1">
         <v>10000</v>
@@ -2309,22 +2298,20 @@
         <v>10000</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="L6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L6" s="1" t="s">
+      <c r="O6" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>42</v>
       </c>
       <c r="P6"/>
       <c r="Q6"/>
@@ -2345,7 +2332,7 @@
         <v>19003</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G7" s="1">
         <v>10000</v>
@@ -2354,22 +2341,22 @@
         <v>10000</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="M7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O7" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>48</v>
       </c>
       <c r="P7"/>
       <c r="Q7"/>
@@ -2390,7 +2377,7 @@
         <v>19004</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G8" s="1">
         <v>10000</v>
@@ -2399,22 +2386,22 @@
         <v>10000</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="O8" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="P8"/>
       <c r="Q8"/>
@@ -2437,7 +2424,7 @@
         <v>19005</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -2446,22 +2433,22 @@
         <v>10000</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="O9" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>62</v>
       </c>
       <c r="P9"/>
       <c r="Q9"/>
@@ -2484,7 +2471,7 @@
         <v>19006</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -2493,22 +2480,22 @@
         <v>10000</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="O10" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>68</v>
       </c>
       <c r="P10"/>
       <c r="Q10"/>
@@ -2531,7 +2518,7 @@
         <v>19007</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -2540,22 +2527,22 @@
         <v>10000</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="O11" s="7" t="s">
         <v>73</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>74</v>
       </c>
       <c r="P11"/>
       <c r="Q11"/>
@@ -2578,7 +2565,7 @@
         <v>19008</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -2587,22 +2574,22 @@
         <v>10000</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="O12" s="7" t="s">
         <v>79</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>80</v>
       </c>
       <c r="P12"/>
       <c r="Q12"/>
@@ -2625,7 +2612,7 @@
         <v>19009</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -2634,22 +2621,22 @@
         <v>10000</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="O13" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>86</v>
       </c>
       <c r="P13"/>
       <c r="Q13"/>
@@ -2667,7 +2654,7 @@
         <v>19010</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -2676,22 +2663,22 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="O14" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>92</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
@@ -2752,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C4" s="1">
         <f>_xlfn.XLOOKUP(B4,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2762,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F4" s="1">
         <f>_xlfn.XLOOKUP(E4,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2780,7 +2767,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" s="1">
         <f>_xlfn.XLOOKUP(B5,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2790,7 +2777,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F5" s="1">
         <f>_xlfn.XLOOKUP(E5,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2808,7 +2795,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" s="1">
         <f>_xlfn.XLOOKUP(B6,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2818,7 +2805,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F6" s="1">
         <f>_xlfn.XLOOKUP(E6,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2836,7 +2823,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" s="1" t="e">
         <f>_xlfn.XLOOKUP(B7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2846,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F7" s="1">
         <f>_xlfn.XLOOKUP(E7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2856,7 +2843,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I7" s="1">
         <f>_xlfn.XLOOKUP(H7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2871,7 +2858,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" s="1" t="e">
         <f>_xlfn.XLOOKUP(B8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2881,7 +2868,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F8" s="1">
         <f>_xlfn.XLOOKUP(E8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2891,7 +2878,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I8" s="1">
         <f>_xlfn.XLOOKUP(H8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2906,7 +2893,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C9" s="1" t="e">
         <f>_xlfn.XLOOKUP(B9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2916,7 +2903,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F9" s="1">
         <f>_xlfn.XLOOKUP(E9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2926,7 +2913,7 @@
         <v>10</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I9" s="1">
         <f>_xlfn.XLOOKUP(H9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2941,7 +2928,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C10" s="1" t="e">
         <f>_xlfn.XLOOKUP(B10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2951,7 +2938,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F10" s="1">
         <f>_xlfn.XLOOKUP(E10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2961,7 +2948,7 @@
         <v>10</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I10" s="1">
         <f>_xlfn.XLOOKUP(H10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2976,7 +2963,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C11" s="1" t="e">
         <f>_xlfn.XLOOKUP(B11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2986,7 +2973,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F11" s="1">
         <f>_xlfn.XLOOKUP(E11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2996,7 +2983,7 @@
         <v>20</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I11" s="1">
         <f>_xlfn.XLOOKUP(H11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3011,7 +2998,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C12" s="1" t="e">
         <f>_xlfn.XLOOKUP(B12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3021,7 +3008,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F12" s="1">
         <f>_xlfn.XLOOKUP(E12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3031,7 +3018,7 @@
         <v>20</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I12" s="1">
         <f>_xlfn.XLOOKUP(H12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3046,7 +3033,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C13" s="1" t="e">
         <f>_xlfn.XLOOKUP(B13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3056,7 +3043,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F13" s="1">
         <f>_xlfn.XLOOKUP(E13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3066,7 +3053,7 @@
         <v>20</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I13" s="1">
         <f>_xlfn.XLOOKUP(H13,[1]Item!$D:$D,[1]Item!$A:$A)</f>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -270,94 +270,100 @@
     <t>4320_1098680</t>
   </si>
   <si>
+    <t>1022501_1</t>
+  </si>
+  <si>
+    <t>4320_12380000</t>
+  </si>
+  <si>
+    <t>1990000_8888</t>
+  </si>
+  <si>
+    <t>1990000_3888</t>
+  </si>
+  <si>
+    <t>1990000_388</t>
+  </si>
+  <si>
     <t>1020001_1</t>
   </si>
   <si>
-    <t>4320_12380000</t>
+    <t>1_500</t>
+  </si>
+  <si>
+    <t>4320_104648340</t>
+  </si>
+  <si>
+    <t>1990000_28888</t>
+  </si>
+  <si>
+    <t>1990000_1288</t>
+  </si>
+  <si>
+    <t>1990000_18888</t>
+  </si>
+  <si>
+    <t>1990000_4888</t>
+  </si>
+  <si>
+    <t>1022501_3</t>
+  </si>
+  <si>
+    <t>1_1000</t>
+  </si>
+  <si>
+    <t>4320_1069785000</t>
+  </si>
+  <si>
+    <t>1990000_188888</t>
+  </si>
+  <si>
+    <t>1990000_6888</t>
+  </si>
+  <si>
+    <t>1990000_138888</t>
+  </si>
+  <si>
+    <t>1990000_32888</t>
+  </si>
+  <si>
+    <t>1031600_1|1020001_2</t>
+  </si>
+  <si>
+    <t>1_1500</t>
+  </si>
+  <si>
+    <t>-1_0</t>
+  </si>
+  <si>
+    <t>1990000_1668888</t>
   </si>
   <si>
     <t>1990000_58888</t>
   </si>
   <si>
-    <t>1990000_3878</t>
-  </si>
-  <si>
-    <t>1990000_9678</t>
-  </si>
-  <si>
-    <t>1_500</t>
-  </si>
-  <si>
-    <t>4320_104648340</t>
-  </si>
-  <si>
-    <t>1990000_565888</t>
-  </si>
-  <si>
-    <t>1990000_18888</t>
-  </si>
-  <si>
-    <t>1990000_37688</t>
-  </si>
-  <si>
-    <t>1990000_94188</t>
-  </si>
-  <si>
-    <t>1_1000</t>
-  </si>
-  <si>
-    <t>4320_1069785000</t>
-  </si>
-  <si>
-    <t>1990000_4828888</t>
-  </si>
-  <si>
-    <t>1990000_134888</t>
+    <t>1990000_1098888</t>
   </si>
   <si>
     <t>1990000_268888</t>
   </si>
   <si>
-    <t>1990000_678888</t>
-  </si>
-  <si>
-    <t>1031600_1|1020001_1</t>
-  </si>
-  <si>
-    <t>1_1500</t>
-  </si>
-  <si>
-    <t>-1_0</t>
-  </si>
-  <si>
-    <t>1990000_33488888</t>
-  </si>
-  <si>
-    <t>1990000_1118888</t>
-  </si>
-  <si>
-    <t>1990000_2238888</t>
-  </si>
-  <si>
-    <t>1990000_5568888</t>
-  </si>
-  <si>
-    <t>1031801_1|1020001_5</t>
+    <t>1031801_1|1022501_10</t>
   </si>
   <si>
     <t>1_2000</t>
   </si>
   <si>
-    <t>1990000_68688888</t>
-  </si>
-  <si>
-    <t>1990000_2828888</t>
-  </si>
-  <si>
-    <t>1990000_4848888</t>
-  </si>
-  <si>
-    <t>1990000_18188888</t>
+    <t>1990000_3028888</t>
+  </si>
+  <si>
+    <t>1990000_109888</t>
+  </si>
+  <si>
+    <t>1990000_2019888</t>
+  </si>
+  <si>
+    <t>1990000_509888</t>
   </si>
   <si>
     <t>1032001_1|1020001_10</t>
@@ -366,76 +372,70 @@
     <t>1_2500</t>
   </si>
   <si>
-    <t>1990000_171888888</t>
-  </si>
-  <si>
-    <t>1990000_5728888</t>
-  </si>
-  <si>
-    <t>1990000_11488888</t>
-  </si>
-  <si>
-    <t>1990000_28688888</t>
-  </si>
-  <si>
-    <t>1031601_1|1020001_10</t>
-  </si>
-  <si>
-    <t>1_3000|2_600</t>
-  </si>
-  <si>
-    <t>1990000_787888888</t>
-  </si>
-  <si>
-    <t>1990000_26288888</t>
-  </si>
-  <si>
-    <t>1990000_52588888</t>
-  </si>
-  <si>
-    <t>1990000_131888888</t>
+    <t>1990000_8568888</t>
+  </si>
+  <si>
+    <t>1990000_285888</t>
+  </si>
+  <si>
+    <t>1990000_5718888</t>
+  </si>
+  <si>
+    <t>1990000_1398888</t>
+  </si>
+  <si>
+    <t>1031601_1|1032201_1|1022501_30</t>
+  </si>
+  <si>
+    <t>1_3000|2_50</t>
+  </si>
+  <si>
+    <t>1990000_39298888</t>
+  </si>
+  <si>
+    <t>1990000_26219888</t>
+  </si>
+  <si>
+    <t>1990000_6568888</t>
   </si>
   <si>
     <t>1031802_1|1020001_20</t>
   </si>
   <si>
-    <t>1_3500|2_800</t>
-  </si>
-  <si>
-    <t>1990000_2538888888</t>
-  </si>
-  <si>
-    <t>1990000_84288888</t>
-  </si>
-  <si>
-    <t>1990000_168888888</t>
-  </si>
-  <si>
-    <t>1990000_421888888</t>
-  </si>
-  <si>
-    <t>1032002_1|1020001_20</t>
-  </si>
-  <si>
-    <t>1_4000|2_1000</t>
-  </si>
-  <si>
-    <t>1990000_12688888888</t>
-  </si>
-  <si>
-    <t>1990000_428888888</t>
-  </si>
-  <si>
-    <t>1990000_848888888</t>
-  </si>
-  <si>
-    <t>1990000_2188888888</t>
-  </si>
-  <si>
-    <t>1031602_1|1020001_20</t>
-  </si>
-  <si>
-    <t>1_4500|2_1500</t>
+    <t>1_3500|2_100</t>
+  </si>
+  <si>
+    <t>1990000_126298888</t>
+  </si>
+  <si>
+    <t>1990000_3999888</t>
+  </si>
+  <si>
+    <t>1990000_83988888</t>
+  </si>
+  <si>
+    <t>1990000_20988888</t>
+  </si>
+  <si>
+    <t>1032002_1|1022501_30</t>
+  </si>
+  <si>
+    <t>1_4000|2_200</t>
+  </si>
+  <si>
+    <t>1990000_629888888</t>
+  </si>
+  <si>
+    <t>1990000_419888888</t>
+  </si>
+  <si>
+    <t>1990000_103988888</t>
+  </si>
+  <si>
+    <t>1031602_1|1032202_1|1020001_20</t>
+  </si>
+  <si>
+    <t>1_4500|2_300</t>
   </si>
   <si>
     <t>刮刮卡</t>
@@ -651,12 +651,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1279,542 +1279,1702 @@
         </row>
         <row r="5">
           <cell r="A5">
-            <v>1990000</v>
+            <v>1010101</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5" t="str">
-            <v>金币</v>
+            <v>金币礼包</v>
           </cell>
         </row>
         <row r="6">
           <cell r="A6">
-            <v>1980000</v>
+            <v>1010201</v>
           </cell>
         </row>
         <row r="6">
           <cell r="D6" t="str">
-            <v>钻石</v>
+            <v>钻石礼包</v>
           </cell>
         </row>
         <row r="7">
           <cell r="A7">
-            <v>1020001</v>
+            <v>1010301</v>
           </cell>
         </row>
         <row r="7">
           <cell r="D7" t="str">
-            <v>白金卡</v>
+            <v>赌场工具（普通）</v>
           </cell>
         </row>
         <row r="8">
           <cell r="A8">
-            <v>1022501</v>
+            <v>1010302</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8" t="str">
-            <v>祈福卡</v>
+            <v>赌场工具（精良）</v>
           </cell>
         </row>
         <row r="9">
           <cell r="A9">
-            <v>1022502</v>
+            <v>1010303</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9" t="str">
-            <v>刮刮卡</v>
+            <v>赌场工具（优秀）</v>
           </cell>
         </row>
         <row r="10">
           <cell r="A10">
-            <v>1022503</v>
+            <v>1010304</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10" t="str">
-            <v>夺宝优惠券</v>
+            <v>赌场工具（绝佳）</v>
           </cell>
         </row>
         <row r="11">
           <cell r="A11">
-            <v>1010301</v>
+            <v>1010305</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11" t="str">
-            <v>赌场工具（普通）</v>
+            <v>赌场工具（传奇）</v>
           </cell>
         </row>
         <row r="12">
           <cell r="A12">
-            <v>1010302</v>
+            <v>1010311</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12" t="str">
-            <v>赌场工具（精良）</v>
+            <v>拼图随机礼包(一星)</v>
           </cell>
         </row>
         <row r="13">
           <cell r="A13">
-            <v>1010303</v>
+            <v>1010312</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13" t="str">
-            <v>赌场工具（优秀）</v>
+            <v>拼图随机礼包(二星)</v>
           </cell>
         </row>
         <row r="14">
           <cell r="A14">
-            <v>1010304</v>
+            <v>1010313</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14" t="str">
-            <v>赌场工具（绝佳）</v>
+            <v>拼图随机礼包(三星)</v>
           </cell>
         </row>
         <row r="15">
           <cell r="A15">
-            <v>1010305</v>
+            <v>1010314</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15" t="str">
-            <v>赌场工具（传奇）</v>
+            <v>拼图随机礼包(四星)</v>
           </cell>
         </row>
         <row r="16">
           <cell r="A16">
-            <v>1031001</v>
+            <v>1010315</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16" t="str">
-            <v>头像2</v>
+            <v>拼图随机礼包(五星)</v>
           </cell>
         </row>
         <row r="17">
           <cell r="A17">
-            <v>1031002</v>
+            <v>1020001</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17" t="str">
-            <v>头像3</v>
+            <v>白金卡</v>
           </cell>
         </row>
         <row r="18">
           <cell r="A18">
-            <v>1031201</v>
+            <v>1020002</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18" t="str">
-            <v>头像框2</v>
+            <v>测试道具2</v>
           </cell>
         </row>
         <row r="19">
           <cell r="A19">
-            <v>1031202</v>
+            <v>1020003</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19" t="str">
-            <v>头像框3</v>
+            <v>测试道具3</v>
           </cell>
         </row>
         <row r="20">
           <cell r="A20">
-            <v>1031350</v>
+            <v>1020004</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20" t="str">
-            <v>头像框-每日奖金</v>
+            <v>测试道具4</v>
           </cell>
         </row>
         <row r="21">
           <cell r="A21">
-            <v>1031351</v>
+            <v>1020005</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21" t="str">
-            <v>头像框-首充专属</v>
+            <v>测试道具5</v>
           </cell>
         </row>
         <row r="22">
           <cell r="A22">
-            <v>1021401</v>
+            <v>1020006</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22" t="str">
-            <v>国旗2</v>
+            <v>测试道具6</v>
           </cell>
         </row>
         <row r="23">
           <cell r="A23">
-            <v>1021402</v>
+            <v>1030011</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23" t="str">
-            <v>国旗3</v>
+            <v>图鉴1-图片</v>
           </cell>
         </row>
         <row r="24">
           <cell r="A24">
-            <v>1031600</v>
+            <v>1030012</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24" t="str">
-            <v>头衔1-财富贵族</v>
+            <v>图鉴2-图片</v>
           </cell>
         </row>
         <row r="25">
           <cell r="A25">
-            <v>1031601</v>
+            <v>1030013</v>
           </cell>
         </row>
         <row r="25">
           <cell r="D25" t="str">
-            <v>头衔2-一夜暴富</v>
+            <v>图鉴3-图片</v>
           </cell>
         </row>
         <row r="26">
           <cell r="A26">
-            <v>1031602</v>
+            <v>1030014</v>
           </cell>
         </row>
         <row r="26">
           <cell r="D26" t="str">
-            <v>头衔3-四方来财</v>
+            <v>图鉴4-图片</v>
           </cell>
         </row>
         <row r="27">
           <cell r="A27">
-            <v>1031801</v>
+            <v>1030015</v>
           </cell>
         </row>
         <row r="27">
           <cell r="D27" t="str">
-            <v>筹码2-翡翠贵族</v>
+            <v>图鉴5-图片</v>
           </cell>
         </row>
         <row r="28">
           <cell r="A28">
-            <v>1031802</v>
+            <v>1030016</v>
           </cell>
         </row>
         <row r="28">
           <cell r="D28" t="str">
-            <v>筹码3-水晶皇室</v>
+            <v>图鉴6-图片</v>
           </cell>
         </row>
         <row r="29">
           <cell r="A29">
-            <v>1032001</v>
+            <v>1030017</v>
           </cell>
         </row>
         <row r="29">
           <cell r="D29" t="str">
-            <v>牌背2-神秘塔罗</v>
+            <v>图鉴7-图片</v>
           </cell>
         </row>
         <row r="30">
           <cell r="A30">
-            <v>1032002</v>
+            <v>1030018</v>
           </cell>
         </row>
         <row r="30">
           <cell r="D30" t="str">
-            <v>牌背3-命运之手</v>
+            <v>图鉴8-图片</v>
           </cell>
         </row>
         <row r="31">
           <cell r="A31">
-            <v>1032201</v>
+            <v>1030101</v>
           </cell>
         </row>
         <row r="31">
           <cell r="D31" t="str">
-            <v>大厅背景2-决赛之夜</v>
+            <v>图鉴1-碎片1</v>
           </cell>
         </row>
         <row r="32">
           <cell r="A32">
-            <v>1032202</v>
+            <v>1030102</v>
           </cell>
         </row>
         <row r="32">
           <cell r="D32" t="str">
-            <v>大厅背景3-度假海滩</v>
+            <v>图鉴1-碎片2</v>
           </cell>
         </row>
         <row r="33">
           <cell r="A33">
-            <v>1022504</v>
+            <v>1030103</v>
           </cell>
         </row>
         <row r="33">
           <cell r="D33" t="str">
-            <v>积分</v>
+            <v>图鉴1-碎片3</v>
           </cell>
         </row>
         <row r="34">
           <cell r="A34">
-            <v>1023001</v>
+            <v>1030104</v>
           </cell>
         </row>
         <row r="34">
           <cell r="D34" t="str">
-            <v>1星扳手</v>
+            <v>图鉴1-碎片4</v>
           </cell>
         </row>
         <row r="35">
           <cell r="A35">
-            <v>1023002</v>
+            <v>1030105</v>
           </cell>
         </row>
         <row r="35">
           <cell r="D35" t="str">
-            <v>2星扳手</v>
+            <v>图鉴1-碎片5</v>
           </cell>
         </row>
         <row r="36">
           <cell r="A36">
-            <v>1023003</v>
+            <v>1030106</v>
           </cell>
         </row>
         <row r="36">
           <cell r="D36" t="str">
-            <v>3星扳手</v>
+            <v>图鉴1-碎片6</v>
           </cell>
         </row>
         <row r="37">
           <cell r="A37">
-            <v>1023004</v>
+            <v>1030107</v>
           </cell>
         </row>
         <row r="37">
           <cell r="D37" t="str">
-            <v>4星扳手</v>
+            <v>图鉴1-碎片7</v>
           </cell>
         </row>
         <row r="38">
           <cell r="A38">
-            <v>1023005</v>
+            <v>1030108</v>
           </cell>
         </row>
         <row r="38">
           <cell r="D38" t="str">
-            <v>5星扳手</v>
+            <v>图鉴1-碎片8</v>
           </cell>
         </row>
         <row r="39">
           <cell r="A39">
-            <v>1023101</v>
+            <v>1030109</v>
           </cell>
         </row>
         <row r="39">
           <cell r="D39" t="str">
-            <v>1星筹码</v>
+            <v>图鉴1-碎片9</v>
           </cell>
         </row>
         <row r="40">
           <cell r="A40">
-            <v>1023102</v>
+            <v>1030110</v>
           </cell>
         </row>
         <row r="40">
           <cell r="D40" t="str">
-            <v>2星筹码</v>
+            <v>图鉴1-碎片10</v>
           </cell>
         </row>
         <row r="41">
           <cell r="A41">
-            <v>1023103</v>
+            <v>1030111</v>
           </cell>
         </row>
         <row r="41">
           <cell r="D41" t="str">
-            <v>3星筹码</v>
+            <v>图鉴1-碎片11</v>
           </cell>
         </row>
         <row r="42">
           <cell r="A42">
-            <v>1023104</v>
+            <v>1030112</v>
           </cell>
         </row>
         <row r="42">
           <cell r="D42" t="str">
-            <v>4星筹码</v>
+            <v>图鉴1-碎片12</v>
           </cell>
         </row>
         <row r="43">
           <cell r="A43">
-            <v>1023105</v>
+            <v>1030121</v>
           </cell>
         </row>
         <row r="43">
           <cell r="D43" t="str">
-            <v>5星筹码</v>
+            <v>图鉴2-碎片1</v>
           </cell>
         </row>
         <row r="44">
           <cell r="A44">
-            <v>1023201</v>
+            <v>1030122</v>
           </cell>
         </row>
         <row r="44">
           <cell r="D44" t="str">
-            <v>1星螺母</v>
+            <v>图鉴2-碎片2</v>
           </cell>
         </row>
         <row r="45">
           <cell r="A45">
-            <v>1023202</v>
+            <v>1030123</v>
           </cell>
         </row>
         <row r="45">
           <cell r="D45" t="str">
-            <v>2星螺母</v>
+            <v>图鉴2-碎片3</v>
           </cell>
         </row>
         <row r="46">
           <cell r="A46">
-            <v>1023203</v>
+            <v>1030124</v>
           </cell>
         </row>
         <row r="46">
           <cell r="D46" t="str">
-            <v>3星螺母</v>
+            <v>图鉴2-碎片4</v>
           </cell>
         </row>
         <row r="47">
           <cell r="A47">
-            <v>1023204</v>
+            <v>1030125</v>
           </cell>
         </row>
         <row r="47">
           <cell r="D47" t="str">
-            <v>4星螺母</v>
+            <v>图鉴2-碎片5</v>
           </cell>
         </row>
         <row r="48">
           <cell r="A48">
-            <v>1023205</v>
+            <v>1030126</v>
           </cell>
         </row>
         <row r="48">
           <cell r="D48" t="str">
-            <v>5星螺母</v>
+            <v>图鉴2-碎片6</v>
           </cell>
         </row>
         <row r="49">
           <cell r="A49">
-            <v>1023301</v>
+            <v>1030127</v>
           </cell>
         </row>
         <row r="49">
           <cell r="D49" t="str">
-            <v>1星木材</v>
+            <v>图鉴2-碎片7</v>
           </cell>
         </row>
         <row r="50">
           <cell r="A50">
-            <v>1023302</v>
+            <v>1030128</v>
           </cell>
         </row>
         <row r="50">
           <cell r="D50" t="str">
-            <v>2星木材</v>
+            <v>图鉴2-碎片8</v>
           </cell>
         </row>
         <row r="51">
           <cell r="A51">
-            <v>1023303</v>
+            <v>1030129</v>
           </cell>
         </row>
         <row r="51">
           <cell r="D51" t="str">
-            <v>3星木材</v>
+            <v>图鉴2-碎片9</v>
           </cell>
         </row>
         <row r="52">
           <cell r="A52">
-            <v>1023304</v>
+            <v>1030130</v>
           </cell>
         </row>
         <row r="52">
           <cell r="D52" t="str">
-            <v>4星木材</v>
+            <v>图鉴2-碎片10</v>
           </cell>
         </row>
         <row r="53">
           <cell r="A53">
-            <v>1023305</v>
+            <v>1030131</v>
           </cell>
         </row>
         <row r="53">
           <cell r="D53" t="str">
-            <v>5星木材</v>
+            <v>图鉴2-碎片11</v>
           </cell>
         </row>
         <row r="54">
           <cell r="A54">
-            <v>1023401</v>
+            <v>1030132</v>
           </cell>
         </row>
         <row r="54">
           <cell r="D54" t="str">
-            <v>1星酒瓶</v>
+            <v>图鉴2-碎片12</v>
           </cell>
         </row>
         <row r="55">
           <cell r="A55">
-            <v>1023402</v>
+            <v>1030141</v>
           </cell>
         </row>
         <row r="55">
           <cell r="D55" t="str">
-            <v>2星酒瓶</v>
+            <v>图鉴3-碎片1</v>
           </cell>
         </row>
         <row r="56">
           <cell r="A56">
-            <v>1023403</v>
+            <v>1030142</v>
           </cell>
         </row>
         <row r="56">
           <cell r="D56" t="str">
-            <v>3星酒瓶</v>
+            <v>图鉴3-碎片2</v>
           </cell>
         </row>
         <row r="57">
           <cell r="A57">
-            <v>1023404</v>
+            <v>1030143</v>
           </cell>
         </row>
         <row r="57">
           <cell r="D57" t="str">
-            <v>4星酒瓶</v>
+            <v>图鉴3-碎片3</v>
           </cell>
         </row>
         <row r="58">
           <cell r="A58">
-            <v>1023405</v>
+            <v>1030144</v>
           </cell>
         </row>
         <row r="58">
           <cell r="D58" t="str">
+            <v>图鉴3-碎片4</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59">
+            <v>1030145</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="D59" t="str">
+            <v>图鉴3-碎片5</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60">
+            <v>1030146</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="D60" t="str">
+            <v>图鉴3-碎片6</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61">
+            <v>1030147</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="D61" t="str">
+            <v>图鉴3-碎片7</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62">
+            <v>1030148</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="D62" t="str">
+            <v>图鉴3-碎片8</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63">
+            <v>1030149</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="D63" t="str">
+            <v>图鉴3-碎片9</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64">
+            <v>1030150</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="D64" t="str">
+            <v>图鉴3-碎片10</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65">
+            <v>1030151</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="D65" t="str">
+            <v>图鉴3-碎片11</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66">
+            <v>1030152</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="D66" t="str">
+            <v>图鉴3-碎片12</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67">
+            <v>1030161</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="D67" t="str">
+            <v>图鉴4-碎片1</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68">
+            <v>1030162</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="D68" t="str">
+            <v>图鉴4-碎片2</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69">
+            <v>1030163</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="D69" t="str">
+            <v>图鉴4-碎片3</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70">
+            <v>1030164</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="D70" t="str">
+            <v>图鉴4-碎片4</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71">
+            <v>1030165</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="D71" t="str">
+            <v>图鉴4-碎片5</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72">
+            <v>1030166</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="D72" t="str">
+            <v>图鉴4-碎片6</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="A73">
+            <v>1030167</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="D73" t="str">
+            <v>图鉴4-碎片7</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="A74">
+            <v>1030168</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="D74" t="str">
+            <v>图鉴4-碎片8</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="A75">
+            <v>1030169</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="D75" t="str">
+            <v>图鉴4-碎片9</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="A76">
+            <v>1030170</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="D76" t="str">
+            <v>图鉴4-碎片10</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="A77">
+            <v>1030171</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="D77" t="str">
+            <v>图鉴4-碎片11</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="A78">
+            <v>1030172</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="D78" t="str">
+            <v>图鉴4-碎片12</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="A79">
+            <v>1030181</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="D79" t="str">
+            <v>图鉴5-碎片1</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="A80">
+            <v>1030182</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="D80" t="str">
+            <v>图鉴5-碎片2</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="A81">
+            <v>1030183</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="D81" t="str">
+            <v>图鉴5-碎片3</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="A82">
+            <v>1030184</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="D82" t="str">
+            <v>图鉴5-碎片4</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="A83">
+            <v>1030185</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="D83" t="str">
+            <v>图鉴5-碎片5</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="A84">
+            <v>1030186</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="D84" t="str">
+            <v>图鉴5-碎片6</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="A85">
+            <v>1030187</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="D85" t="str">
+            <v>图鉴5-碎片7</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="A86">
+            <v>1030188</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="D86" t="str">
+            <v>图鉴5-碎片8</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="A87">
+            <v>1030189</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="D87" t="str">
+            <v>图鉴5-碎片9</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="A88">
+            <v>1030190</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="D88" t="str">
+            <v>图鉴5-碎片10</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="A89">
+            <v>1030191</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="D89" t="str">
+            <v>图鉴5-碎片11</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="A90">
+            <v>1030192</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="D90" t="str">
+            <v>图鉴5-碎片12</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="A91">
+            <v>1030201</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="D91" t="str">
+            <v>图鉴6-碎片1</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="A92">
+            <v>1030202</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="D92" t="str">
+            <v>图鉴6-碎片2</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="A93">
+            <v>1030203</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="D93" t="str">
+            <v>图鉴6-碎片3</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="A94">
+            <v>1030204</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="D94" t="str">
+            <v>图鉴6-碎片4</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="A95">
+            <v>1030205</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="D95" t="str">
+            <v>图鉴6-碎片5</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="A96">
+            <v>1030206</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="D96" t="str">
+            <v>图鉴6-碎片6</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="A97">
+            <v>1030207</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="D97" t="str">
+            <v>图鉴6-碎片7</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="A98">
+            <v>1030208</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="D98" t="str">
+            <v>图鉴6-碎片8</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="A99">
+            <v>1030209</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="D99" t="str">
+            <v>图鉴6-碎片9</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="A100">
+            <v>1030210</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="D100" t="str">
+            <v>图鉴6-碎片10</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="A101">
+            <v>1030211</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="D101" t="str">
+            <v>图鉴6-碎片11</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="A102">
+            <v>1030212</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="D102" t="str">
+            <v>图鉴6-碎片12</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="A103">
+            <v>1030221</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="D103" t="str">
+            <v>图鉴7-碎片1</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="A104">
+            <v>1030222</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="D104" t="str">
+            <v>图鉴7-碎片2</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="A105">
+            <v>1030223</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="D105" t="str">
+            <v>图鉴7-碎片3</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="A106">
+            <v>1030224</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="D106" t="str">
+            <v>图鉴7-碎片4</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="A107">
+            <v>1030225</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="D107" t="str">
+            <v>图鉴7-碎片5</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="A108">
+            <v>1030226</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="D108" t="str">
+            <v>图鉴7-碎片6</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="A109">
+            <v>1030227</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="D109" t="str">
+            <v>图鉴7-碎片7</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="A110">
+            <v>1030228</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="D110" t="str">
+            <v>图鉴7-碎片8</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="A111">
+            <v>1030229</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="D111" t="str">
+            <v>图鉴7-碎片9</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="A112">
+            <v>1030230</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="D112" t="str">
+            <v>图鉴7-碎片10</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="A113">
+            <v>1030231</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="D113" t="str">
+            <v>图鉴7-碎片11</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="A114">
+            <v>1030232</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="D114" t="str">
+            <v>图鉴7-碎片12</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="A115">
+            <v>1030241</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="D115" t="str">
+            <v>图鉴8-碎片1</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="A116">
+            <v>1030242</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="D116" t="str">
+            <v>图鉴8-碎片2</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="A117">
+            <v>1030243</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="D117" t="str">
+            <v>图鉴8-碎片3</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="A118">
+            <v>1030244</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="D118" t="str">
+            <v>图鉴8-碎片4</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="A119">
+            <v>1030245</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="D119" t="str">
+            <v>图鉴8-碎片5</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="A120">
+            <v>1030246</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="D120" t="str">
+            <v>图鉴8-碎片6</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="A121">
+            <v>1030247</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="D121" t="str">
+            <v>图鉴8-碎片7</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="A122">
+            <v>1030248</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="D122" t="str">
+            <v>图鉴8-碎片8</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="A123">
+            <v>1030249</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="D123" t="str">
+            <v>图鉴8-碎片9</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="A124">
+            <v>1030250</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="D124" t="str">
+            <v>图鉴8-碎片10</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="A125">
+            <v>1030251</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="D125" t="str">
+            <v>图鉴8-碎片11</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="A126">
+            <v>1030252</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="D126" t="str">
+            <v>图鉴8-碎片12</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="A127">
+            <v>1031001</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="D127" t="str">
+            <v>头像2</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="A128">
+            <v>1031002</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="D128" t="str">
+            <v>头像3</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="A129">
+            <v>1031201</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="D129" t="str">
+            <v>头像框2</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="A130">
+            <v>1031202</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="D130" t="str">
+            <v>头像框3</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="A131">
+            <v>1031350</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="D131" t="str">
+            <v>头像框-每日奖金</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="A132">
+            <v>1031351</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="D132" t="str">
+            <v>头像框-首充专属</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="A133">
+            <v>1021401</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="D133" t="str">
+            <v>国旗2</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="A134">
+            <v>1021402</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="D134" t="str">
+            <v>国旗3</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="A135">
+            <v>1031600</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="D135" t="str">
+            <v>头衔1-财富贵族</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="A136">
+            <v>1031601</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="D136" t="str">
+            <v>头衔2-一夜暴富</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="A137">
+            <v>1031602</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="D137" t="str">
+            <v>头衔3-四方来财</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="A138">
+            <v>1031801</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="D138" t="str">
+            <v>筹码2-翡翠贵族</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="A139">
+            <v>1031802</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="D139" t="str">
+            <v>筹码3-水晶皇室</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="A140">
+            <v>1032001</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="D140" t="str">
+            <v>牌背2-神秘塔罗</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="A141">
+            <v>1032002</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="D141" t="str">
+            <v>牌背3-命运之手</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="A142">
+            <v>1032201</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="D142" t="str">
+            <v>大厅背景2-决赛之夜</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="A143">
+            <v>1032202</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="D143" t="str">
+            <v>大厅背景3-度假海滩</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="A144">
+            <v>1022501</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="D144" t="str">
+            <v>祈福卡</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="A145">
+            <v>1022502</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="D145" t="str">
+            <v>刮刮卡</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="A146">
+            <v>1022503</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="D146" t="str">
+            <v>夺宝优惠券</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="A147">
+            <v>1022504</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="D147" t="str">
+            <v>积分</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="A148">
+            <v>1023001</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="D148" t="str">
+            <v>1星扳手</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="A149">
+            <v>1023002</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="D149" t="str">
+            <v>2星扳手</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="A150">
+            <v>1023003</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="D150" t="str">
+            <v>3星扳手</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="A151">
+            <v>1023004</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="D151" t="str">
+            <v>4星扳手</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="A152">
+            <v>1023005</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="D152" t="str">
+            <v>5星扳手</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="A153">
+            <v>1023101</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="D153" t="str">
+            <v>1星筹码</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="A154">
+            <v>1023102</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="D154" t="str">
+            <v>2星筹码</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="A155">
+            <v>1023103</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="D155" t="str">
+            <v>3星筹码</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="A156">
+            <v>1023104</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="D156" t="str">
+            <v>4星筹码</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="A157">
+            <v>1023105</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="D157" t="str">
+            <v>5星筹码</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="A158">
+            <v>1023201</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="D158" t="str">
+            <v>1星螺母</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="A159">
+            <v>1023202</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="D159" t="str">
+            <v>2星螺母</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="A160">
+            <v>1023203</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="D160" t="str">
+            <v>3星螺母</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="A161">
+            <v>1023204</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="D161" t="str">
+            <v>4星螺母</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="A162">
+            <v>1023205</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="D162" t="str">
+            <v>5星螺母</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="A163">
+            <v>1023301</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="D163" t="str">
+            <v>1星木材</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="A164">
+            <v>1023302</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="D164" t="str">
+            <v>2星木材</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="A165">
+            <v>1023303</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="D165" t="str">
+            <v>3星木材</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="A166">
+            <v>1023304</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="D166" t="str">
+            <v>4星木材</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="A167">
+            <v>1023305</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="D167" t="str">
+            <v>5星木材</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="A168">
+            <v>1023401</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="D168" t="str">
+            <v>1星酒瓶</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="A169">
+            <v>1023402</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="D169" t="str">
+            <v>2星酒瓶</v>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="A170">
+            <v>1023403</v>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="D170" t="str">
+            <v>3星酒瓶</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="A171">
+            <v>1023404</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="D171" t="str">
+            <v>4星酒瓶</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="A172">
+            <v>1023405</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="D172" t="str">
             <v>5星酒瓶</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="A173">
+            <v>1990000</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="D173" t="str">
+            <v>金币</v>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="A174">
+            <v>1980000</v>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="D174" t="str">
+            <v>钻石</v>
           </cell>
         </row>
       </sheetData>
@@ -2078,11 +3238,11 @@
   <cols>
     <col min="1" max="1" width="10.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.35" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.375" style="1" customWidth="1"/>
-    <col min="7" max="8" width="21.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.35" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="17.75" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="14.875" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="17.375" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="21.25" style="1" hidden="1" customWidth="1"/>
     <col min="9" max="12" width="20.375" style="1" customWidth="1"/>
     <col min="13" max="13" width="37.375" style="1" customWidth="1"/>
     <col min="14" max="14" width="21.7666666666667" style="1" customWidth="1"/>
@@ -2262,10 +3422,6 @@
       <c r="H5" s="1">
         <v>10000</v>
       </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
       <c r="M5" s="1" t="s">
         <v>36</v>
       </c>
@@ -2308,10 +3464,10 @@
         <v>40</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P6"/>
       <c r="Q6"/>
@@ -2332,7 +3488,7 @@
         <v>19003</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7" s="1">
         <v>10000</v>
@@ -2341,22 +3497,22 @@
         <v>10000</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P7"/>
       <c r="Q7"/>
@@ -2377,7 +3533,7 @@
         <v>19004</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G8" s="1">
         <v>10000</v>
@@ -2386,22 +3542,22 @@
         <v>10000</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P8"/>
       <c r="Q8"/>
@@ -2424,7 +3580,7 @@
         <v>19005</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -2433,22 +3589,22 @@
         <v>10000</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P9"/>
       <c r="Q9"/>
@@ -2471,7 +3627,7 @@
         <v>19006</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -2480,22 +3636,22 @@
         <v>10000</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P10"/>
       <c r="Q10"/>
@@ -2518,7 +3674,7 @@
         <v>19007</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -2527,22 +3683,22 @@
         <v>10000</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P11"/>
       <c r="Q11"/>
@@ -2565,7 +3721,7 @@
         <v>19008</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -2574,22 +3730,22 @@
         <v>10000</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P12"/>
       <c r="Q12"/>
@@ -2612,7 +3768,7 @@
         <v>19009</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -2621,22 +3777,22 @@
         <v>10000</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P13"/>
       <c r="Q13"/>
@@ -2654,7 +3810,7 @@
         <v>19010</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -2663,10 +3819,10 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>88</v>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="86">
   <si>
     <t>id</t>
   </si>
@@ -276,13 +276,7 @@
     <t>4320_12380000</t>
   </si>
   <si>
-    <t>1990000_58888</t>
-  </si>
-  <si>
-    <t>1990000_3878</t>
-  </si>
-  <si>
-    <t>1990000_9678</t>
+    <t>1990000_58000</t>
   </si>
   <si>
     <t>1_500</t>
@@ -291,16 +285,10 @@
     <t>4320_104648340</t>
   </si>
   <si>
-    <t>1990000_565888</t>
-  </si>
-  <si>
-    <t>1990000_18888</t>
-  </si>
-  <si>
-    <t>1990000_37688</t>
-  </si>
-  <si>
-    <t>1990000_94188</t>
+    <t>1990000_565000</t>
+  </si>
+  <si>
+    <t>1990000_188000</t>
   </si>
   <si>
     <t>1_1000</t>
@@ -309,16 +297,10 @@
     <t>4320_1069785000</t>
   </si>
   <si>
-    <t>1990000_4828888</t>
-  </si>
-  <si>
-    <t>1990000_134888</t>
-  </si>
-  <si>
-    <t>1990000_268888</t>
-  </si>
-  <si>
-    <t>1990000_678888</t>
+    <t>1990000_4020000</t>
+  </si>
+  <si>
+    <t>1990000_1340000</t>
   </si>
   <si>
     <t>1031600_1|1020001_1</t>
@@ -330,16 +312,10 @@
     <t>-1_0</t>
   </si>
   <si>
-    <t>1990000_33488888</t>
-  </si>
-  <si>
-    <t>1990000_1118888</t>
-  </si>
-  <si>
-    <t>1990000_2238888</t>
-  </si>
-  <si>
-    <t>1990000_5568888</t>
+    <t>1990000_33400000</t>
+  </si>
+  <si>
+    <t>1990000_11100000</t>
   </si>
   <si>
     <t>1031801_1|1020001_5</t>
@@ -348,16 +324,10 @@
     <t>1_2000</t>
   </si>
   <si>
-    <t>1990000_68688888</t>
-  </si>
-  <si>
-    <t>1990000_2828888</t>
-  </si>
-  <si>
-    <t>1990000_4848888</t>
-  </si>
-  <si>
-    <t>1990000_18188888</t>
+    <t>1990000_60600000</t>
+  </si>
+  <si>
+    <t>1990000_20200000</t>
   </si>
   <si>
     <t>1032001_1|1020001_10</t>
@@ -366,16 +336,10 @@
     <t>1_2500</t>
   </si>
   <si>
-    <t>1990000_171888888</t>
-  </si>
-  <si>
-    <t>1990000_5728888</t>
-  </si>
-  <si>
-    <t>1990000_11488888</t>
-  </si>
-  <si>
-    <t>1990000_28688888</t>
+    <t>1990000_171000000</t>
+  </si>
+  <si>
+    <t>1990000_57200000</t>
   </si>
   <si>
     <t>1031601_1|1020001_10</t>
@@ -384,16 +348,10 @@
     <t>1_3000|2_600</t>
   </si>
   <si>
-    <t>1990000_787888888</t>
-  </si>
-  <si>
-    <t>1990000_26288888</t>
-  </si>
-  <si>
-    <t>1990000_52588888</t>
-  </si>
-  <si>
-    <t>1990000_131888888</t>
+    <t>1990000_787000000</t>
+  </si>
+  <si>
+    <t>1990000_262000000</t>
   </si>
   <si>
     <t>1031802_1|1020001_20</t>
@@ -402,16 +360,10 @@
     <t>1_3500|2_800</t>
   </si>
   <si>
-    <t>1990000_2538888888</t>
-  </si>
-  <si>
-    <t>1990000_84288888</t>
-  </si>
-  <si>
-    <t>1990000_168888888</t>
-  </si>
-  <si>
-    <t>1990000_421888888</t>
+    <t>1990000_2530000000</t>
+  </si>
+  <si>
+    <t>1990000_842000000</t>
   </si>
   <si>
     <t>1032002_1|1020001_20</t>
@@ -420,16 +372,10 @@
     <t>1_4000|2_1000</t>
   </si>
   <si>
-    <t>1990000_12688888888</t>
-  </si>
-  <si>
-    <t>1990000_428888888</t>
-  </si>
-  <si>
-    <t>1990000_848888888</t>
-  </si>
-  <si>
-    <t>1990000_2188888888</t>
+    <t>1990000_12600000000</t>
+  </si>
+  <si>
+    <t>1990000_4200000000</t>
   </si>
   <si>
     <t>1031602_1|1020001_20</t>
@@ -651,12 +597,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2262,10 +2208,6 @@
       <c r="H5" s="1">
         <v>10000</v>
       </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
       <c r="M5" s="1" t="s">
         <v>36</v>
       </c>
@@ -2300,18 +2242,17 @@
       <c r="I6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J6" s="1"/>
       <c r="K6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>36</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P6"/>
       <c r="Q6"/>
@@ -2332,7 +2273,7 @@
         <v>19003</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G7" s="1">
         <v>10000</v>
@@ -2341,22 +2282,22 @@
         <v>10000</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>36</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="P7"/>
       <c r="Q7"/>
@@ -2377,7 +2318,7 @@
         <v>19004</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G8" s="1">
         <v>10000</v>
@@ -2386,22 +2327,22 @@
         <v>10000</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="P8"/>
       <c r="Q8"/>
@@ -2424,7 +2365,7 @@
         <v>19005</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -2433,22 +2374,22 @@
         <v>10000</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="P9"/>
       <c r="Q9"/>
@@ -2471,7 +2412,7 @@
         <v>19006</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -2480,22 +2421,22 @@
         <v>10000</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="P10"/>
       <c r="Q10"/>
@@ -2518,7 +2459,7 @@
         <v>19007</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -2527,22 +2468,22 @@
         <v>10000</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="P11"/>
       <c r="Q11"/>
@@ -2565,7 +2506,7 @@
         <v>19008</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -2574,22 +2515,22 @@
         <v>10000</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="P12"/>
       <c r="Q12"/>
@@ -2612,7 +2553,7 @@
         <v>19009</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -2621,22 +2562,22 @@
         <v>10000</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P13"/>
       <c r="Q13"/>
@@ -2654,7 +2595,7 @@
         <v>19010</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -2663,22 +2604,22 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
@@ -2739,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="C4" s="1">
         <f>_xlfn.XLOOKUP(B4,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2749,7 +2690,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F4" s="1">
         <f>_xlfn.XLOOKUP(E4,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2767,7 +2708,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="C5" s="1">
         <f>_xlfn.XLOOKUP(B5,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2777,7 +2718,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F5" s="1">
         <f>_xlfn.XLOOKUP(E5,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2795,7 +2736,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1">
         <f>_xlfn.XLOOKUP(B6,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2805,7 +2746,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F6" s="1">
         <f>_xlfn.XLOOKUP(E6,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2823,7 +2764,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C7" s="1" t="e">
         <f>_xlfn.XLOOKUP(B7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2833,7 +2774,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F7" s="1">
         <f>_xlfn.XLOOKUP(E7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2843,7 +2784,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="I7" s="1">
         <f>_xlfn.XLOOKUP(H7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2858,7 +2799,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="C8" s="1" t="e">
         <f>_xlfn.XLOOKUP(B8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2868,7 +2809,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F8" s="1">
         <f>_xlfn.XLOOKUP(E8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2878,7 +2819,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="I8" s="1">
         <f>_xlfn.XLOOKUP(H8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2893,7 +2834,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C9" s="1" t="e">
         <f>_xlfn.XLOOKUP(B9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2903,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F9" s="1">
         <f>_xlfn.XLOOKUP(E9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2913,7 +2854,7 @@
         <v>10</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="I9" s="1">
         <f>_xlfn.XLOOKUP(H9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2928,7 +2869,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="C10" s="1" t="e">
         <f>_xlfn.XLOOKUP(B10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2938,7 +2879,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F10" s="1">
         <f>_xlfn.XLOOKUP(E10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2948,7 +2889,7 @@
         <v>10</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="I10" s="1">
         <f>_xlfn.XLOOKUP(H10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2963,7 +2904,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C11" s="1" t="e">
         <f>_xlfn.XLOOKUP(B11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2973,7 +2914,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F11" s="1">
         <f>_xlfn.XLOOKUP(E11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2983,7 +2924,7 @@
         <v>20</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="I11" s="1">
         <f>_xlfn.XLOOKUP(H11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -2998,7 +2939,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="C12" s="1" t="e">
         <f>_xlfn.XLOOKUP(B12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3008,7 +2949,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F12" s="1">
         <f>_xlfn.XLOOKUP(E12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3018,7 +2959,7 @@
         <v>20</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="I12" s="1">
         <f>_xlfn.XLOOKUP(H12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3033,7 +2974,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="C13" s="1" t="e">
         <f>_xlfn.XLOOKUP(B13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3043,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F13" s="1">
         <f>_xlfn.XLOOKUP(E13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3053,7 +2994,7 @@
         <v>20</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="I13" s="1">
         <f>_xlfn.XLOOKUP(H13,[1]Item!$D:$D,[1]Item!$A:$A)</f>

--- a/table/resources/sample/viplevel.xlsx
+++ b/table/resources/sample/viplevel.xlsx
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="86">
   <si>
     <t>id</t>
   </si>
@@ -270,22 +270,13 @@
     <t>4320_1098680</t>
   </si>
   <si>
-    <t>1022501_1</t>
+    <t>1020001_1</t>
   </si>
   <si>
     <t>4320_12380000</t>
   </si>
   <si>
-    <t>1990000_8888</t>
-  </si>
-  <si>
-    <t>1990000_3888</t>
-  </si>
-  <si>
-    <t>1990000_388</t>
-  </si>
-  <si>
-    <t>1020001_1</t>
+    <t>1990000_58000</t>
   </si>
   <si>
     <t>1_500</t>
@@ -294,19 +285,10 @@
     <t>4320_104648340</t>
   </si>
   <si>
-    <t>1990000_28888</t>
-  </si>
-  <si>
-    <t>1990000_1288</t>
-  </si>
-  <si>
-    <t>1990000_18888</t>
-  </si>
-  <si>
-    <t>1990000_4888</t>
-  </si>
-  <si>
-    <t>1022501_3</t>
+    <t>1990000_565000</t>
+  </si>
+  <si>
+    <t>1990000_188000</t>
   </si>
   <si>
     <t>1_1000</t>
@@ -315,19 +297,13 @@
     <t>4320_1069785000</t>
   </si>
   <si>
-    <t>1990000_188888</t>
-  </si>
-  <si>
-    <t>1990000_6888</t>
-  </si>
-  <si>
-    <t>1990000_138888</t>
-  </si>
-  <si>
-    <t>1990000_32888</t>
-  </si>
-  <si>
-    <t>1031600_1|1020001_2</t>
+    <t>1990000_4020000</t>
+  </si>
+  <si>
+    <t>1990000_1340000</t>
+  </si>
+  <si>
+    <t>1031600_1|1020001_1</t>
   </si>
   <si>
     <t>1_1500</t>
@@ -336,34 +312,22 @@
     <t>-1_0</t>
   </si>
   <si>
-    <t>1990000_1668888</t>
-  </si>
-  <si>
-    <t>1990000_58888</t>
-  </si>
-  <si>
-    <t>1990000_1098888</t>
-  </si>
-  <si>
-    <t>1990000_268888</t>
-  </si>
-  <si>
-    <t>1031801_1|1022501_10</t>
+    <t>1990000_33400000</t>
+  </si>
+  <si>
+    <t>1990000_11100000</t>
+  </si>
+  <si>
+    <t>1031801_1|1020001_5</t>
   </si>
   <si>
     <t>1_2000</t>
   </si>
   <si>
-    <t>1990000_3028888</t>
-  </si>
-  <si>
-    <t>1990000_109888</t>
-  </si>
-  <si>
-    <t>1990000_2019888</t>
-  </si>
-  <si>
-    <t>1990000_509888</t>
+    <t>1990000_60600000</t>
+  </si>
+  <si>
+    <t>1990000_20200000</t>
   </si>
   <si>
     <t>1032001_1|1020001_10</t>
@@ -372,70 +336,52 @@
     <t>1_2500</t>
   </si>
   <si>
-    <t>1990000_8568888</t>
-  </si>
-  <si>
-    <t>1990000_285888</t>
-  </si>
-  <si>
-    <t>1990000_5718888</t>
-  </si>
-  <si>
-    <t>1990000_1398888</t>
-  </si>
-  <si>
-    <t>1031601_1|1032201_1|1022501_30</t>
-  </si>
-  <si>
-    <t>1_3000|2_50</t>
-  </si>
-  <si>
-    <t>1990000_39298888</t>
-  </si>
-  <si>
-    <t>1990000_26219888</t>
-  </si>
-  <si>
-    <t>1990000_6568888</t>
+    <t>1990000_171000000</t>
+  </si>
+  <si>
+    <t>1990000_57200000</t>
+  </si>
+  <si>
+    <t>1031601_1|1020001_10</t>
+  </si>
+  <si>
+    <t>1_3000|2_600</t>
+  </si>
+  <si>
+    <t>1990000_787000000</t>
+  </si>
+  <si>
+    <t>1990000_262000000</t>
   </si>
   <si>
     <t>1031802_1|1020001_20</t>
   </si>
   <si>
-    <t>1_3500|2_100</t>
-  </si>
-  <si>
-    <t>1990000_126298888</t>
-  </si>
-  <si>
-    <t>1990000_3999888</t>
-  </si>
-  <si>
-    <t>1990000_83988888</t>
-  </si>
-  <si>
-    <t>1990000_20988888</t>
-  </si>
-  <si>
-    <t>1032002_1|1022501_30</t>
-  </si>
-  <si>
-    <t>1_4000|2_200</t>
-  </si>
-  <si>
-    <t>1990000_629888888</t>
-  </si>
-  <si>
-    <t>1990000_419888888</t>
-  </si>
-  <si>
-    <t>1990000_103988888</t>
-  </si>
-  <si>
-    <t>1031602_1|1032202_1|1020001_20</t>
-  </si>
-  <si>
-    <t>1_4500|2_300</t>
+    <t>1_3500|2_800</t>
+  </si>
+  <si>
+    <t>1990000_2530000000</t>
+  </si>
+  <si>
+    <t>1990000_842000000</t>
+  </si>
+  <si>
+    <t>1032002_1|1020001_20</t>
+  </si>
+  <si>
+    <t>1_4000|2_1000</t>
+  </si>
+  <si>
+    <t>1990000_12600000000</t>
+  </si>
+  <si>
+    <t>1990000_4200000000</t>
+  </si>
+  <si>
+    <t>1031602_1|1020001_20</t>
+  </si>
+  <si>
+    <t>1_4500|2_1500</t>
   </si>
   <si>
     <t>刮刮卡</t>
@@ -1279,1702 +1225,542 @@
         </row>
         <row r="5">
           <cell r="A5">
-            <v>1010101</v>
+            <v>1990000</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5" t="str">
-            <v>金币礼包</v>
+            <v>金币</v>
           </cell>
         </row>
         <row r="6">
           <cell r="A6">
-            <v>1010201</v>
+            <v>1980000</v>
           </cell>
         </row>
         <row r="6">
           <cell r="D6" t="str">
-            <v>钻石礼包</v>
+            <v>钻石</v>
           </cell>
         </row>
         <row r="7">
           <cell r="A7">
-            <v>1010301</v>
+            <v>1020001</v>
           </cell>
         </row>
         <row r="7">
           <cell r="D7" t="str">
-            <v>赌场工具（普通）</v>
+            <v>白金卡</v>
           </cell>
         </row>
         <row r="8">
           <cell r="A8">
-            <v>1010302</v>
+            <v>1022501</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8" t="str">
-            <v>赌场工具（精良）</v>
+            <v>祈福卡</v>
           </cell>
         </row>
         <row r="9">
           <cell r="A9">
-            <v>1010303</v>
+            <v>1022502</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9" t="str">
-            <v>赌场工具（优秀）</v>
+            <v>刮刮卡</v>
           </cell>
         </row>
         <row r="10">
           <cell r="A10">
-            <v>1010304</v>
+            <v>1022503</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10" t="str">
-            <v>赌场工具（绝佳）</v>
+            <v>夺宝优惠券</v>
           </cell>
         </row>
         <row r="11">
           <cell r="A11">
-            <v>1010305</v>
+            <v>1010301</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11" t="str">
-            <v>赌场工具（传奇）</v>
+            <v>赌场工具（普通）</v>
           </cell>
         </row>
         <row r="12">
           <cell r="A12">
-            <v>1010311</v>
+            <v>1010302</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12" t="str">
-            <v>拼图随机礼包(一星)</v>
+            <v>赌场工具（精良）</v>
           </cell>
         </row>
         <row r="13">
           <cell r="A13">
-            <v>1010312</v>
+            <v>1010303</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13" t="str">
-            <v>拼图随机礼包(二星)</v>
+            <v>赌场工具（优秀）</v>
           </cell>
         </row>
         <row r="14">
           <cell r="A14">
-            <v>1010313</v>
+            <v>1010304</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14" t="str">
-            <v>拼图随机礼包(三星)</v>
+            <v>赌场工具（绝佳）</v>
           </cell>
         </row>
         <row r="15">
           <cell r="A15">
-            <v>1010314</v>
+            <v>1010305</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15" t="str">
-            <v>拼图随机礼包(四星)</v>
+            <v>赌场工具（传奇）</v>
           </cell>
         </row>
         <row r="16">
           <cell r="A16">
-            <v>1010315</v>
+            <v>1031001</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16" t="str">
-            <v>拼图随机礼包(五星)</v>
+            <v>头像2</v>
           </cell>
         </row>
         <row r="17">
           <cell r="A17">
-            <v>1020001</v>
+            <v>1031002</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17" t="str">
-            <v>白金卡</v>
+            <v>头像3</v>
           </cell>
         </row>
         <row r="18">
           <cell r="A18">
-            <v>1020002</v>
+            <v>1031201</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18" t="str">
-            <v>测试道具2</v>
+            <v>头像框2</v>
           </cell>
         </row>
         <row r="19">
           <cell r="A19">
-            <v>1020003</v>
+            <v>1031202</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19" t="str">
-            <v>测试道具3</v>
+            <v>头像框3</v>
           </cell>
         </row>
         <row r="20">
           <cell r="A20">
-            <v>1020004</v>
+            <v>1031350</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20" t="str">
-            <v>测试道具4</v>
+            <v>头像框-每日奖金</v>
           </cell>
         </row>
         <row r="21">
           <cell r="A21">
-            <v>1020005</v>
+            <v>1031351</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21" t="str">
-            <v>测试道具5</v>
+            <v>头像框-首充专属</v>
           </cell>
         </row>
         <row r="22">
           <cell r="A22">
-            <v>1020006</v>
+            <v>1021401</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22" t="str">
-            <v>测试道具6</v>
+            <v>国旗2</v>
           </cell>
         </row>
         <row r="23">
           <cell r="A23">
-            <v>1030011</v>
+            <v>1021402</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23" t="str">
-            <v>图鉴1-图片</v>
+            <v>国旗3</v>
           </cell>
         </row>
         <row r="24">
           <cell r="A24">
-            <v>1030012</v>
+            <v>1031600</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24" t="str">
-            <v>图鉴2-图片</v>
+            <v>头衔1-财富贵族</v>
           </cell>
         </row>
         <row r="25">
           <cell r="A25">
-            <v>1030013</v>
+            <v>1031601</v>
           </cell>
         </row>
         <row r="25">
           <cell r="D25" t="str">
-            <v>图鉴3-图片</v>
+            <v>头衔2-一夜暴富</v>
           </cell>
         </row>
         <row r="26">
           <cell r="A26">
-            <v>1030014</v>
+            <v>1031602</v>
           </cell>
         </row>
         <row r="26">
           <cell r="D26" t="str">
-            <v>图鉴4-图片</v>
+            <v>头衔3-四方来财</v>
           </cell>
         </row>
         <row r="27">
           <cell r="A27">
-            <v>1030015</v>
+            <v>1031801</v>
           </cell>
         </row>
         <row r="27">
           <cell r="D27" t="str">
-            <v>图鉴5-图片</v>
+            <v>筹码2-翡翠贵族</v>
           </cell>
         </row>
         <row r="28">
           <cell r="A28">
-            <v>1030016</v>
+            <v>1031802</v>
           </cell>
         </row>
         <row r="28">
           <cell r="D28" t="str">
-            <v>图鉴6-图片</v>
+            <v>筹码3-水晶皇室</v>
           </cell>
         </row>
         <row r="29">
           <cell r="A29">
-            <v>1030017</v>
+            <v>1032001</v>
           </cell>
         </row>
         <row r="29">
           <cell r="D29" t="str">
-            <v>图鉴7-图片</v>
+            <v>牌背2-神秘塔罗</v>
           </cell>
         </row>
         <row r="30">
           <cell r="A30">
-            <v>1030018</v>
+            <v>1032002</v>
           </cell>
         </row>
         <row r="30">
           <cell r="D30" t="str">
-            <v>图鉴8-图片</v>
+            <v>牌背3-命运之手</v>
           </cell>
         </row>
         <row r="31">
           <cell r="A31">
-            <v>1030101</v>
+            <v>1032201</v>
           </cell>
         </row>
         <row r="31">
           <cell r="D31" t="str">
-            <v>图鉴1-碎片1</v>
+            <v>大厅背景2-决赛之夜</v>
           </cell>
         </row>
         <row r="32">
           <cell r="A32">
-            <v>1030102</v>
+            <v>1032202</v>
           </cell>
         </row>
         <row r="32">
           <cell r="D32" t="str">
-            <v>图鉴1-碎片2</v>
+            <v>大厅背景3-度假海滩</v>
           </cell>
         </row>
         <row r="33">
           <cell r="A33">
-            <v>1030103</v>
+            <v>1022504</v>
           </cell>
         </row>
         <row r="33">
           <cell r="D33" t="str">
-            <v>图鉴1-碎片3</v>
+            <v>积分</v>
           </cell>
         </row>
         <row r="34">
           <cell r="A34">
-            <v>1030104</v>
+            <v>1023001</v>
           </cell>
         </row>
         <row r="34">
           <cell r="D34" t="str">
-            <v>图鉴1-碎片4</v>
+            <v>1星扳手</v>
           </cell>
         </row>
         <row r="35">
           <cell r="A35">
-            <v>1030105</v>
+            <v>1023002</v>
           </cell>
         </row>
         <row r="35">
           <cell r="D35" t="str">
-            <v>图鉴1-碎片5</v>
+            <v>2星扳手</v>
           </cell>
         </row>
         <row r="36">
           <cell r="A36">
-            <v>1030106</v>
+            <v>1023003</v>
           </cell>
         </row>
         <row r="36">
           <cell r="D36" t="str">
-            <v>图鉴1-碎片6</v>
+            <v>3星扳手</v>
           </cell>
         </row>
         <row r="37">
           <cell r="A37">
-            <v>1030107</v>
+            <v>1023004</v>
           </cell>
         </row>
         <row r="37">
           <cell r="D37" t="str">
-            <v>图鉴1-碎片7</v>
+            <v>4星扳手</v>
           </cell>
         </row>
         <row r="38">
           <cell r="A38">
-            <v>1030108</v>
+            <v>1023005</v>
           </cell>
         </row>
         <row r="38">
           <cell r="D38" t="str">
-            <v>图鉴1-碎片8</v>
+            <v>5星扳手</v>
           </cell>
         </row>
         <row r="39">
           <cell r="A39">
-            <v>1030109</v>
+            <v>1023101</v>
           </cell>
         </row>
         <row r="39">
           <cell r="D39" t="str">
-            <v>图鉴1-碎片9</v>
+            <v>1星筹码</v>
           </cell>
         </row>
         <row r="40">
           <cell r="A40">
-            <v>1030110</v>
+            <v>1023102</v>
           </cell>
         </row>
         <row r="40">
           <cell r="D40" t="str">
-            <v>图鉴1-碎片10</v>
+            <v>2星筹码</v>
           </cell>
         </row>
         <row r="41">
           <cell r="A41">
-            <v>1030111</v>
+            <v>1023103</v>
           </cell>
         </row>
         <row r="41">
           <cell r="D41" t="str">
-            <v>图鉴1-碎片11</v>
+            <v>3星筹码</v>
           </cell>
         </row>
         <row r="42">
           <cell r="A42">
-            <v>1030112</v>
+            <v>1023104</v>
           </cell>
         </row>
         <row r="42">
           <cell r="D42" t="str">
-            <v>图鉴1-碎片12</v>
+            <v>4星筹码</v>
           </cell>
         </row>
         <row r="43">
           <cell r="A43">
-            <v>1030121</v>
+            <v>1023105</v>
           </cell>
         </row>
         <row r="43">
           <cell r="D43" t="str">
-            <v>图鉴2-碎片1</v>
+            <v>5星筹码</v>
           </cell>
         </row>
         <row r="44">
           <cell r="A44">
-            <v>1030122</v>
+            <v>1023201</v>
           </cell>
         </row>
         <row r="44">
           <cell r="D44" t="str">
-            <v>图鉴2-碎片2</v>
+            <v>1星螺母</v>
           </cell>
         </row>
         <row r="45">
           <cell r="A45">
-            <v>1030123</v>
+            <v>1023202</v>
           </cell>
         </row>
         <row r="45">
           <cell r="D45" t="str">
-            <v>图鉴2-碎片3</v>
+            <v>2星螺母</v>
           </cell>
         </row>
         <row r="46">
           <cell r="A46">
-            <v>1030124</v>
+            <v>1023203</v>
           </cell>
         </row>
         <row r="46">
           <cell r="D46" t="str">
-            <v>图鉴2-碎片4</v>
+            <v>3星螺母</v>
           </cell>
         </row>
         <row r="47">
           <cell r="A47">
-            <v>1030125</v>
+            <v>1023204</v>
           </cell>
         </row>
         <row r="47">
           <cell r="D47" t="str">
-            <v>图鉴2-碎片5</v>
+            <v>4星螺母</v>
           </cell>
         </row>
         <row r="48">
           <cell r="A48">
-            <v>1030126</v>
+            <v>1023205</v>
           </cell>
         </row>
         <row r="48">
           <cell r="D48" t="str">
-            <v>图鉴2-碎片6</v>
+            <v>5星螺母</v>
           </cell>
         </row>
         <row r="49">
           <cell r="A49">
-            <v>1030127</v>
+            <v>1023301</v>
           </cell>
         </row>
         <row r="49">
           <cell r="D49" t="str">
-            <v>图鉴2-碎片7</v>
+            <v>1星木材</v>
           </cell>
         </row>
         <row r="50">
           <cell r="A50">
-            <v>1030128</v>
+            <v>1023302</v>
           </cell>
         </row>
         <row r="50">
           <cell r="D50" t="str">
-            <v>图鉴2-碎片8</v>
+            <v>2星木材</v>
           </cell>
         </row>
         <row r="51">
           <cell r="A51">
-            <v>1030129</v>
+            <v>1023303</v>
           </cell>
         </row>
         <row r="51">
           <cell r="D51" t="str">
-            <v>图鉴2-碎片9</v>
+            <v>3星木材</v>
           </cell>
         </row>
         <row r="52">
           <cell r="A52">
-            <v>1030130</v>
+            <v>1023304</v>
           </cell>
         </row>
         <row r="52">
           <cell r="D52" t="str">
-            <v>图鉴2-碎片10</v>
+            <v>4星木材</v>
           </cell>
         </row>
         <row r="53">
           <cell r="A53">
-            <v>1030131</v>
+            <v>1023305</v>
           </cell>
         </row>
         <row r="53">
           <cell r="D53" t="str">
-            <v>图鉴2-碎片11</v>
+            <v>5星木材</v>
           </cell>
         </row>
         <row r="54">
           <cell r="A54">
-            <v>1030132</v>
+            <v>1023401</v>
           </cell>
         </row>
         <row r="54">
           <cell r="D54" t="str">
-            <v>图鉴2-碎片12</v>
+            <v>1星酒瓶</v>
           </cell>
         </row>
         <row r="55">
           <cell r="A55">
-            <v>1030141</v>
+            <v>1023402</v>
           </cell>
         </row>
         <row r="55">
           <cell r="D55" t="str">
-            <v>图鉴3-碎片1</v>
+            <v>2星酒瓶</v>
           </cell>
         </row>
         <row r="56">
           <cell r="A56">
-            <v>1030142</v>
+            <v>1023403</v>
           </cell>
         </row>
         <row r="56">
           <cell r="D56" t="str">
-            <v>图鉴3-碎片2</v>
+            <v>3星酒瓶</v>
           </cell>
         </row>
         <row r="57">
           <cell r="A57">
-            <v>1030143</v>
+            <v>1023404</v>
           </cell>
         </row>
         <row r="57">
           <cell r="D57" t="str">
-            <v>图鉴3-碎片3</v>
+            <v>4星酒瓶</v>
           </cell>
         </row>
         <row r="58">
           <cell r="A58">
-            <v>1030144</v>
+            <v>1023405</v>
           </cell>
         </row>
         <row r="58">
           <cell r="D58" t="str">
-            <v>图鉴3-碎片4</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59">
-            <v>1030145</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="D59" t="str">
-            <v>图鉴3-碎片5</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60">
-            <v>1030146</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="D60" t="str">
-            <v>图鉴3-碎片6</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61">
-            <v>1030147</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="D61" t="str">
-            <v>图鉴3-碎片7</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62">
-            <v>1030148</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="D62" t="str">
-            <v>图鉴3-碎片8</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="A63">
-            <v>1030149</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="D63" t="str">
-            <v>图鉴3-碎片9</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="A64">
-            <v>1030150</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="D64" t="str">
-            <v>图鉴3-碎片10</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="A65">
-            <v>1030151</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="D65" t="str">
-            <v>图鉴3-碎片11</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="A66">
-            <v>1030152</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="D66" t="str">
-            <v>图鉴3-碎片12</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="A67">
-            <v>1030161</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="D67" t="str">
-            <v>图鉴4-碎片1</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="A68">
-            <v>1030162</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="D68" t="str">
-            <v>图鉴4-碎片2</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="A69">
-            <v>1030163</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="D69" t="str">
-            <v>图鉴4-碎片3</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="A70">
-            <v>1030164</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="D70" t="str">
-            <v>图鉴4-碎片4</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="A71">
-            <v>1030165</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="D71" t="str">
-            <v>图鉴4-碎片5</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="A72">
-            <v>1030166</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="D72" t="str">
-            <v>图鉴4-碎片6</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="A73">
-            <v>1030167</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="D73" t="str">
-            <v>图鉴4-碎片7</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="A74">
-            <v>1030168</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="D74" t="str">
-            <v>图鉴4-碎片8</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="A75">
-            <v>1030169</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="D75" t="str">
-            <v>图鉴4-碎片9</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="A76">
-            <v>1030170</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="D76" t="str">
-            <v>图鉴4-碎片10</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="A77">
-            <v>1030171</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="D77" t="str">
-            <v>图鉴4-碎片11</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="A78">
-            <v>1030172</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="D78" t="str">
-            <v>图鉴4-碎片12</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="A79">
-            <v>1030181</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="D79" t="str">
-            <v>图鉴5-碎片1</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="A80">
-            <v>1030182</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="D80" t="str">
-            <v>图鉴5-碎片2</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="A81">
-            <v>1030183</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="D81" t="str">
-            <v>图鉴5-碎片3</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="A82">
-            <v>1030184</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="D82" t="str">
-            <v>图鉴5-碎片4</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="A83">
-            <v>1030185</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="D83" t="str">
-            <v>图鉴5-碎片5</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="A84">
-            <v>1030186</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="D84" t="str">
-            <v>图鉴5-碎片6</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="A85">
-            <v>1030187</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="D85" t="str">
-            <v>图鉴5-碎片7</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="A86">
-            <v>1030188</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="D86" t="str">
-            <v>图鉴5-碎片8</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="A87">
-            <v>1030189</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="D87" t="str">
-            <v>图鉴5-碎片9</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="A88">
-            <v>1030190</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="D88" t="str">
-            <v>图鉴5-碎片10</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="A89">
-            <v>1030191</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="D89" t="str">
-            <v>图鉴5-碎片11</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="A90">
-            <v>1030192</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="D90" t="str">
-            <v>图鉴5-碎片12</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="A91">
-            <v>1030201</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="D91" t="str">
-            <v>图鉴6-碎片1</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="A92">
-            <v>1030202</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="D92" t="str">
-            <v>图鉴6-碎片2</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="A93">
-            <v>1030203</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="D93" t="str">
-            <v>图鉴6-碎片3</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="A94">
-            <v>1030204</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="D94" t="str">
-            <v>图鉴6-碎片4</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="A95">
-            <v>1030205</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="D95" t="str">
-            <v>图鉴6-碎片5</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="A96">
-            <v>1030206</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="D96" t="str">
-            <v>图鉴6-碎片6</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="A97">
-            <v>1030207</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="D97" t="str">
-            <v>图鉴6-碎片7</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="A98">
-            <v>1030208</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="D98" t="str">
-            <v>图鉴6-碎片8</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="A99">
-            <v>1030209</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="D99" t="str">
-            <v>图鉴6-碎片9</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="A100">
-            <v>1030210</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="D100" t="str">
-            <v>图鉴6-碎片10</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="A101">
-            <v>1030211</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="D101" t="str">
-            <v>图鉴6-碎片11</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="A102">
-            <v>1030212</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="D102" t="str">
-            <v>图鉴6-碎片12</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="A103">
-            <v>1030221</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="D103" t="str">
-            <v>图鉴7-碎片1</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="A104">
-            <v>1030222</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="D104" t="str">
-            <v>图鉴7-碎片2</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="A105">
-            <v>1030223</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="D105" t="str">
-            <v>图鉴7-碎片3</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="A106">
-            <v>1030224</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="D106" t="str">
-            <v>图鉴7-碎片4</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="A107">
-            <v>1030225</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="D107" t="str">
-            <v>图鉴7-碎片5</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="A108">
-            <v>1030226</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="D108" t="str">
-            <v>图鉴7-碎片6</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="A109">
-            <v>1030227</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="D109" t="str">
-            <v>图鉴7-碎片7</v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="A110">
-            <v>1030228</v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="D110" t="str">
-            <v>图鉴7-碎片8</v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="A111">
-            <v>1030229</v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="D111" t="str">
-            <v>图鉴7-碎片9</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="A112">
-            <v>1030230</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="D112" t="str">
-            <v>图鉴7-碎片10</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="A113">
-            <v>1030231</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="D113" t="str">
-            <v>图鉴7-碎片11</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="A114">
-            <v>1030232</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="D114" t="str">
-            <v>图鉴7-碎片12</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="A115">
-            <v>1030241</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="D115" t="str">
-            <v>图鉴8-碎片1</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="A116">
-            <v>1030242</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="D116" t="str">
-            <v>图鉴8-碎片2</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="A117">
-            <v>1030243</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="D117" t="str">
-            <v>图鉴8-碎片3</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="A118">
-            <v>1030244</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="D118" t="str">
-            <v>图鉴8-碎片4</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="A119">
-            <v>1030245</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="D119" t="str">
-            <v>图鉴8-碎片5</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="A120">
-            <v>1030246</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="D120" t="str">
-            <v>图鉴8-碎片6</v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="A121">
-            <v>1030247</v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="D121" t="str">
-            <v>图鉴8-碎片7</v>
-          </cell>
-        </row>
-        <row r="122">
-          <cell r="A122">
-            <v>1030248</v>
-          </cell>
-        </row>
-        <row r="122">
-          <cell r="D122" t="str">
-            <v>图鉴8-碎片8</v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="A123">
-            <v>1030249</v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="D123" t="str">
-            <v>图鉴8-碎片9</v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="A124">
-            <v>1030250</v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="D124" t="str">
-            <v>图鉴8-碎片10</v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="A125">
-            <v>1030251</v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="D125" t="str">
-            <v>图鉴8-碎片11</v>
-          </cell>
-        </row>
-        <row r="126">
-          <cell r="A126">
-            <v>1030252</v>
-          </cell>
-        </row>
-        <row r="126">
-          <cell r="D126" t="str">
-            <v>图鉴8-碎片12</v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="A127">
-            <v>1031001</v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="D127" t="str">
-            <v>头像2</v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="A128">
-            <v>1031002</v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="D128" t="str">
-            <v>头像3</v>
-          </cell>
-        </row>
-        <row r="129">
-          <cell r="A129">
-            <v>1031201</v>
-          </cell>
-        </row>
-        <row r="129">
-          <cell r="D129" t="str">
-            <v>头像框2</v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="A130">
-            <v>1031202</v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="D130" t="str">
-            <v>头像框3</v>
-          </cell>
-        </row>
-        <row r="131">
-          <cell r="A131">
-            <v>1031350</v>
-          </cell>
-        </row>
-        <row r="131">
-          <cell r="D131" t="str">
-            <v>头像框-每日奖金</v>
-          </cell>
-        </row>
-        <row r="132">
-          <cell r="A132">
-            <v>1031351</v>
-          </cell>
-        </row>
-        <row r="132">
-          <cell r="D132" t="str">
-            <v>头像框-首充专属</v>
-          </cell>
-        </row>
-        <row r="133">
-          <cell r="A133">
-            <v>1021401</v>
-          </cell>
-        </row>
-        <row r="133">
-          <cell r="D133" t="str">
-            <v>国旗2</v>
-          </cell>
-        </row>
-        <row r="134">
-          <cell r="A134">
-            <v>1021402</v>
-          </cell>
-        </row>
-        <row r="134">
-          <cell r="D134" t="str">
-            <v>国旗3</v>
-          </cell>
-        </row>
-        <row r="135">
-          <cell r="A135">
-            <v>1031600</v>
-          </cell>
-        </row>
-        <row r="135">
-          <cell r="D135" t="str">
-            <v>头衔1-财富贵族</v>
-          </cell>
-        </row>
-        <row r="136">
-          <cell r="A136">
-            <v>1031601</v>
-          </cell>
-        </row>
-        <row r="136">
-          <cell r="D136" t="str">
-            <v>头衔2-一夜暴富</v>
-          </cell>
-        </row>
-        <row r="137">
-          <cell r="A137">
-            <v>1031602</v>
-          </cell>
-        </row>
-        <row r="137">
-          <cell r="D137" t="str">
-            <v>头衔3-四方来财</v>
-          </cell>
-        </row>
-        <row r="138">
-          <cell r="A138">
-            <v>1031801</v>
-          </cell>
-        </row>
-        <row r="138">
-          <cell r="D138" t="str">
-            <v>筹码2-翡翠贵族</v>
-          </cell>
-        </row>
-        <row r="139">
-          <cell r="A139">
-            <v>1031802</v>
-          </cell>
-        </row>
-        <row r="139">
-          <cell r="D139" t="str">
-            <v>筹码3-水晶皇室</v>
-          </cell>
-        </row>
-        <row r="140">
-          <cell r="A140">
-            <v>1032001</v>
-          </cell>
-        </row>
-        <row r="140">
-          <cell r="D140" t="str">
-            <v>牌背2-神秘塔罗</v>
-          </cell>
-        </row>
-        <row r="141">
-          <cell r="A141">
-            <v>1032002</v>
-          </cell>
-        </row>
-        <row r="141">
-          <cell r="D141" t="str">
-            <v>牌背3-命运之手</v>
-          </cell>
-        </row>
-        <row r="142">
-          <cell r="A142">
-            <v>1032201</v>
-          </cell>
-        </row>
-        <row r="142">
-          <cell r="D142" t="str">
-            <v>大厅背景2-决赛之夜</v>
-          </cell>
-        </row>
-        <row r="143">
-          <cell r="A143">
-            <v>1032202</v>
-          </cell>
-        </row>
-        <row r="143">
-          <cell r="D143" t="str">
-            <v>大厅背景3-度假海滩</v>
-          </cell>
-        </row>
-        <row r="144">
-          <cell r="A144">
-            <v>1022501</v>
-          </cell>
-        </row>
-        <row r="144">
-          <cell r="D144" t="str">
-            <v>祈福卡</v>
-          </cell>
-        </row>
-        <row r="145">
-          <cell r="A145">
-            <v>1022502</v>
-          </cell>
-        </row>
-        <row r="145">
-          <cell r="D145" t="str">
-            <v>刮刮卡</v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="A146">
-            <v>1022503</v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="D146" t="str">
-            <v>夺宝优惠券</v>
-          </cell>
-        </row>
-        <row r="147">
-          <cell r="A147">
-            <v>1022504</v>
-          </cell>
-        </row>
-        <row r="147">
-          <cell r="D147" t="str">
-            <v>积分</v>
-          </cell>
-        </row>
-        <row r="148">
-          <cell r="A148">
-            <v>1023001</v>
-          </cell>
-        </row>
-        <row r="148">
-          <cell r="D148" t="str">
-            <v>1星扳手</v>
-          </cell>
-        </row>
-        <row r="149">
-          <cell r="A149">
-            <v>1023002</v>
-          </cell>
-        </row>
-        <row r="149">
-          <cell r="D149" t="str">
-            <v>2星扳手</v>
-          </cell>
-        </row>
-        <row r="150">
-          <cell r="A150">
-            <v>1023003</v>
-          </cell>
-        </row>
-        <row r="150">
-          <cell r="D150" t="str">
-            <v>3星扳手</v>
-          </cell>
-        </row>
-        <row r="151">
-          <cell r="A151">
-            <v>1023004</v>
-          </cell>
-        </row>
-        <row r="151">
-          <cell r="D151" t="str">
-            <v>4星扳手</v>
-          </cell>
-        </row>
-        <row r="152">
-          <cell r="A152">
-            <v>1023005</v>
-          </cell>
-        </row>
-        <row r="152">
-          <cell r="D152" t="str">
-            <v>5星扳手</v>
-          </cell>
-        </row>
-        <row r="153">
-          <cell r="A153">
-            <v>1023101</v>
-          </cell>
-        </row>
-        <row r="153">
-          <cell r="D153" t="str">
-            <v>1星筹码</v>
-          </cell>
-        </row>
-        <row r="154">
-          <cell r="A154">
-            <v>1023102</v>
-          </cell>
-        </row>
-        <row r="154">
-          <cell r="D154" t="str">
-            <v>2星筹码</v>
-          </cell>
-        </row>
-        <row r="155">
-          <cell r="A155">
-            <v>1023103</v>
-          </cell>
-        </row>
-        <row r="155">
-          <cell r="D155" t="str">
-            <v>3星筹码</v>
-          </cell>
-        </row>
-        <row r="156">
-          <cell r="A156">
-            <v>1023104</v>
-          </cell>
-        </row>
-        <row r="156">
-          <cell r="D156" t="str">
-            <v>4星筹码</v>
-          </cell>
-        </row>
-        <row r="157">
-          <cell r="A157">
-            <v>1023105</v>
-          </cell>
-        </row>
-        <row r="157">
-          <cell r="D157" t="str">
-            <v>5星筹码</v>
-          </cell>
-        </row>
-        <row r="158">
-          <cell r="A158">
-            <v>1023201</v>
-          </cell>
-        </row>
-        <row r="158">
-          <cell r="D158" t="str">
-            <v>1星螺母</v>
-          </cell>
-        </row>
-        <row r="159">
-          <cell r="A159">
-            <v>1023202</v>
-          </cell>
-        </row>
-        <row r="159">
-          <cell r="D159" t="str">
-            <v>2星螺母</v>
-          </cell>
-        </row>
-        <row r="160">
-          <cell r="A160">
-            <v>1023203</v>
-          </cell>
-        </row>
-        <row r="160">
-          <cell r="D160" t="str">
-            <v>3星螺母</v>
-          </cell>
-        </row>
-        <row r="161">
-          <cell r="A161">
-            <v>1023204</v>
-          </cell>
-        </row>
-        <row r="161">
-          <cell r="D161" t="str">
-            <v>4星螺母</v>
-          </cell>
-        </row>
-        <row r="162">
-          <cell r="A162">
-            <v>1023205</v>
-          </cell>
-        </row>
-        <row r="162">
-          <cell r="D162" t="str">
-            <v>5星螺母</v>
-          </cell>
-        </row>
-        <row r="163">
-          <cell r="A163">
-            <v>1023301</v>
-          </cell>
-        </row>
-        <row r="163">
-          <cell r="D163" t="str">
-            <v>1星木材</v>
-          </cell>
-        </row>
-        <row r="164">
-          <cell r="A164">
-            <v>1023302</v>
-          </cell>
-        </row>
-        <row r="164">
-          <cell r="D164" t="str">
-            <v>2星木材</v>
-          </cell>
-        </row>
-        <row r="165">
-          <cell r="A165">
-            <v>1023303</v>
-          </cell>
-        </row>
-        <row r="165">
-          <cell r="D165" t="str">
-            <v>3星木材</v>
-          </cell>
-        </row>
-        <row r="166">
-          <cell r="A166">
-            <v>1023304</v>
-          </cell>
-        </row>
-        <row r="166">
-          <cell r="D166" t="str">
-            <v>4星木材</v>
-          </cell>
-        </row>
-        <row r="167">
-          <cell r="A167">
-            <v>1023305</v>
-          </cell>
-        </row>
-        <row r="167">
-          <cell r="D167" t="str">
-            <v>5星木材</v>
-          </cell>
-        </row>
-        <row r="168">
-          <cell r="A168">
-            <v>1023401</v>
-          </cell>
-        </row>
-        <row r="168">
-          <cell r="D168" t="str">
-            <v>1星酒瓶</v>
-          </cell>
-        </row>
-        <row r="169">
-          <cell r="A169">
-            <v>1023402</v>
-          </cell>
-        </row>
-        <row r="169">
-          <cell r="D169" t="str">
-            <v>2星酒瓶</v>
-          </cell>
-        </row>
-        <row r="170">
-          <cell r="A170">
-            <v>1023403</v>
-          </cell>
-        </row>
-        <row r="170">
-          <cell r="D170" t="str">
-            <v>3星酒瓶</v>
-          </cell>
-        </row>
-        <row r="171">
-          <cell r="A171">
-            <v>1023404</v>
-          </cell>
-        </row>
-        <row r="171">
-          <cell r="D171" t="str">
-            <v>4星酒瓶</v>
-          </cell>
-        </row>
-        <row r="172">
-          <cell r="A172">
-            <v>1023405</v>
-          </cell>
-        </row>
-        <row r="172">
-          <cell r="D172" t="str">
             <v>5星酒瓶</v>
-          </cell>
-        </row>
-        <row r="173">
-          <cell r="A173">
-            <v>1990000</v>
-          </cell>
-        </row>
-        <row r="173">
-          <cell r="D173" t="str">
-            <v>金币</v>
-          </cell>
-        </row>
-        <row r="174">
-          <cell r="A174">
-            <v>1980000</v>
-          </cell>
-        </row>
-        <row r="174">
-          <cell r="D174" t="str">
-            <v>钻石</v>
           </cell>
         </row>
       </sheetData>
@@ -3238,11 +2024,11 @@
   <cols>
     <col min="1" max="1" width="10.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.35" style="1" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="17.75" style="1" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="14.875" style="1" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="17.375" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="8" width="21.25" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="27.35" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.375" style="1" customWidth="1"/>
+    <col min="7" max="8" width="21.25" style="1" customWidth="1"/>
     <col min="9" max="12" width="20.375" style="1" customWidth="1"/>
     <col min="13" max="13" width="37.375" style="1" customWidth="1"/>
     <col min="14" max="14" width="21.7666666666667" style="1" customWidth="1"/>
@@ -3456,18 +2242,17 @@
       <c r="I6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J6" s="1"/>
       <c r="K6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O6" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>42</v>
       </c>
       <c r="P6"/>
       <c r="Q6"/>
@@ -3488,7 +2273,7 @@
         <v>19003</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G7" s="1">
         <v>10000</v>
@@ -3497,22 +2282,22 @@
         <v>10000</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="P7"/>
       <c r="Q7"/>
@@ -3533,7 +2318,7 @@
         <v>19004</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G8" s="1">
         <v>10000</v>
@@ -3542,22 +2327,22 @@
         <v>10000</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="P8"/>
       <c r="Q8"/>
@@ -3580,7 +2365,7 @@
         <v>19005</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -3589,22 +2374,22 @@
         <v>10000</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="P9"/>
       <c r="Q9"/>
@@ -3627,7 +2412,7 @@
         <v>19006</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -3636,22 +2421,22 @@
         <v>10000</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="P10"/>
       <c r="Q10"/>
@@ -3674,7 +2459,7 @@
         <v>19007</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -3683,22 +2468,22 @@
         <v>10000</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="P11"/>
       <c r="Q11"/>
@@ -3721,7 +2506,7 @@
         <v>19008</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -3730,22 +2515,22 @@
         <v>10000</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="P12"/>
       <c r="Q12"/>
@@ -3768,7 +2553,7 @@
         <v>19009</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -3777,22 +2562,22 @@
         <v>10000</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="P13"/>
       <c r="Q13"/>
@@ -3810,7 +2595,7 @@
         <v>19010</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -3819,22 +2604,22 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
@@ -3895,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="C4" s="1">
         <f>_xlfn.XLOOKUP(B4,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3905,7 +2690,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F4" s="1">
         <f>_xlfn.XLOOKUP(E4,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3923,7 +2708,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="C5" s="1">
         <f>_xlfn.XLOOKUP(B5,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3933,7 +2718,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F5" s="1">
         <f>_xlfn.XLOOKUP(E5,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3951,7 +2736,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1">
         <f>_xlfn.XLOOKUP(B6,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3961,7 +2746,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F6" s="1">
         <f>_xlfn.XLOOKUP(E6,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3979,7 +2764,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C7" s="1" t="e">
         <f>_xlfn.XLOOKUP(B7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3989,7 +2774,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F7" s="1">
         <f>_xlfn.XLOOKUP(E7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -3999,7 +2784,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="I7" s="1">
         <f>_xlfn.XLOOKUP(H7,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4014,7 +2799,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="C8" s="1" t="e">
         <f>_xlfn.XLOOKUP(B8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4024,7 +2809,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F8" s="1">
         <f>_xlfn.XLOOKUP(E8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4034,7 +2819,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="I8" s="1">
         <f>_xlfn.XLOOKUP(H8,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4049,7 +2834,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C9" s="1" t="e">
         <f>_xlfn.XLOOKUP(B9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4059,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F9" s="1">
         <f>_xlfn.XLOOKUP(E9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4069,7 +2854,7 @@
         <v>10</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="I9" s="1">
         <f>_xlfn.XLOOKUP(H9,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4084,7 +2869,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="C10" s="1" t="e">
         <f>_xlfn.XLOOKUP(B10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4094,7 +2879,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F10" s="1">
         <f>_xlfn.XLOOKUP(E10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4104,7 +2889,7 @@
         <v>10</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="I10" s="1">
         <f>_xlfn.XLOOKUP(H10,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4119,7 +2904,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C11" s="1" t="e">
         <f>_xlfn.XLOOKUP(B11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4129,7 +2914,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F11" s="1">
         <f>_xlfn.XLOOKUP(E11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4139,7 +2924,7 @@
         <v>20</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="I11" s="1">
         <f>_xlfn.XLOOKUP(H11,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4154,7 +2939,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="C12" s="1" t="e">
         <f>_xlfn.XLOOKUP(B12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4164,7 +2949,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F12" s="1">
         <f>_xlfn.XLOOKUP(E12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4174,7 +2959,7 @@
         <v>20</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="I12" s="1">
         <f>_xlfn.XLOOKUP(H12,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4189,7 +2974,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="C13" s="1" t="e">
         <f>_xlfn.XLOOKUP(B13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4199,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F13" s="1">
         <f>_xlfn.XLOOKUP(E13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
@@ -4209,7 +2994,7 @@
         <v>20</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="I13" s="1">
         <f>_xlfn.XLOOKUP(H13,[1]Item!$D:$D,[1]Item!$A:$A)</f>
